--- a/research/traditional_assets/database/data/denmark/denmark_drugs_biotechnology.xlsx
+++ b/research/traditional_assets/database/data/denmark/denmark_drugs_biotechnology.xlsx
@@ -2355,7 +2355,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Z101"/>
+  <dimension ref="A1:Z100"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -2492,22 +2492,22 @@
     </row>
     <row r="2">
       <c r="A2">
-        <v>0</v>
+        <v>0.01</v>
       </c>
       <c r="B2">
-        <v>0.09555508507731093</v>
+        <v>0.09537996389014083</v>
       </c>
       <c r="C2">
-        <v>13264.17555583483</v>
+        <v>13174.58370296923</v>
       </c>
       <c r="D2">
-        <v>12315.67555583483</v>
+        <v>12359.17570296923</v>
       </c>
       <c r="E2">
-        <v>-147.6</v>
+        <v>-14.50799999999998</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>133.092</v>
       </c>
       <c r="G2">
         <v>948.5</v>
@@ -2528,28 +2528,28 @@
         <v>981.6</v>
       </c>
       <c r="M2">
-        <v>0</v>
+        <v>6.694527600000001</v>
       </c>
       <c r="N2">
-        <v>981.6</v>
+        <v>974.9054724</v>
       </c>
       <c r="O2">
-        <v>215.952</v>
+        <v>214.479203928</v>
       </c>
       <c r="P2">
-        <v>765.648</v>
+        <v>760.4262684719999</v>
       </c>
       <c r="Q2">
-        <v>809.348</v>
+        <v>804.1262684719999</v>
       </c>
       <c r="R2">
-        <v>0</v>
+        <v>0.0101010101010101</v>
       </c>
       <c r="S2">
-        <v>0.09555508507731093</v>
+        <v>0.09594709483852609</v>
       </c>
       <c r="T2">
-        <v>1.149078177305102</v>
+        <v>1.158131520520233</v>
       </c>
       <c r="U2">
         <v>0.0503</v>
@@ -2566,7 +2566,7 @@
         </is>
       </c>
       <c r="Y2">
-        <v>10000000</v>
+        <v>146.6272243018312</v>
       </c>
       <c r="Z2">
         <v>0</v>
@@ -2574,22 +2574,22 @@
     </row>
     <row r="3">
       <c r="A3">
-        <v>0.01</v>
+        <v>0.02</v>
       </c>
       <c r="B3">
-        <v>0.09537996389014083</v>
+        <v>0.09520484270297075</v>
       </c>
       <c r="C3">
-        <v>13174.58370296923</v>
+        <v>13085.30023272329</v>
       </c>
       <c r="D3">
-        <v>12359.17570296923</v>
+        <v>12402.98423272329</v>
       </c>
       <c r="E3">
-        <v>-14.50799999999998</v>
+        <v>118.584</v>
       </c>
       <c r="F3">
-        <v>133.092</v>
+        <v>266.184</v>
       </c>
       <c r="G3">
         <v>948.5</v>
@@ -2610,28 +2610,28 @@
         <v>981.6</v>
       </c>
       <c r="M3">
-        <v>6.694527600000001</v>
+        <v>13.3890552</v>
       </c>
       <c r="N3">
-        <v>974.9054724</v>
+        <v>968.2109448</v>
       </c>
       <c r="O3">
-        <v>214.479203928</v>
+        <v>213.006407856</v>
       </c>
       <c r="P3">
-        <v>760.4262684719999</v>
+        <v>755.204536944</v>
       </c>
       <c r="Q3">
-        <v>804.1262684719999</v>
+        <v>798.9045369439999</v>
       </c>
       <c r="R3">
-        <v>0.0101010101010101</v>
+        <v>0.02040816326530612</v>
       </c>
       <c r="S3">
-        <v>0.09594709483852609</v>
+        <v>0.09634710479894976</v>
       </c>
       <c r="T3">
-        <v>1.158131520520233</v>
+        <v>1.167369625841796</v>
       </c>
       <c r="U3">
         <v>0.0503</v>
@@ -2648,7 +2648,7 @@
         </is>
       </c>
       <c r="Y3">
-        <v>146.6272243018312</v>
+        <v>73.31361215091562</v>
       </c>
       <c r="Z3">
         <v>0</v>
@@ -2656,22 +2656,22 @@
     </row>
     <row r="4">
       <c r="A4">
-        <v>0.02</v>
+        <v>0.03</v>
       </c>
       <c r="B4">
-        <v>0.09520484270297075</v>
+        <v>0.09502972151580068</v>
       </c>
       <c r="C4">
-        <v>13085.30023272329</v>
+        <v>12996.32843605593</v>
       </c>
       <c r="D4">
-        <v>12402.98423272329</v>
+        <v>12447.10443605593</v>
       </c>
       <c r="E4">
-        <v>118.584</v>
+        <v>251.676</v>
       </c>
       <c r="F4">
-        <v>266.184</v>
+        <v>399.276</v>
       </c>
       <c r="G4">
         <v>948.5</v>
@@ -2692,28 +2692,28 @@
         <v>981.6</v>
       </c>
       <c r="M4">
-        <v>13.3890552</v>
+        <v>20.0835828</v>
       </c>
       <c r="N4">
-        <v>968.2109448</v>
+        <v>961.5164172</v>
       </c>
       <c r="O4">
-        <v>213.006407856</v>
+        <v>211.533611784</v>
       </c>
       <c r="P4">
-        <v>755.204536944</v>
+        <v>749.982805416</v>
       </c>
       <c r="Q4">
-        <v>798.9045369439999</v>
+        <v>793.682805416</v>
       </c>
       <c r="R4">
-        <v>0.02040816326530612</v>
+        <v>0.03092783505154639</v>
       </c>
       <c r="S4">
-        <v>0.09634710479894976</v>
+        <v>0.09675536238742338</v>
       </c>
       <c r="T4">
-        <v>1.167369625841796</v>
+        <v>1.176798207561741</v>
       </c>
       <c r="U4">
         <v>0.0503</v>
@@ -2730,7 +2730,7 @@
         </is>
       </c>
       <c r="Y4">
-        <v>73.31361215091562</v>
+        <v>48.87574143394375</v>
       </c>
       <c r="Z4">
         <v>0</v>
@@ -2738,22 +2738,22 @@
     </row>
     <row r="5">
       <c r="A5">
-        <v>0.03</v>
+        <v>0.04</v>
       </c>
       <c r="B5">
-        <v>0.09502972151580068</v>
+        <v>0.09485460032863059</v>
       </c>
       <c r="C5">
-        <v>12996.32843605593</v>
+        <v>12907.67165091996</v>
       </c>
       <c r="D5">
-        <v>12447.10443605593</v>
+        <v>12491.53965091996</v>
       </c>
       <c r="E5">
-        <v>251.676</v>
+        <v>384.768</v>
       </c>
       <c r="F5">
-        <v>399.276</v>
+        <v>532.3680000000001</v>
       </c>
       <c r="G5">
         <v>948.5</v>
@@ -2774,28 +2774,28 @@
         <v>981.6</v>
       </c>
       <c r="M5">
-        <v>20.0835828</v>
+        <v>26.7781104</v>
       </c>
       <c r="N5">
-        <v>961.5164172</v>
+        <v>954.8218896000001</v>
       </c>
       <c r="O5">
-        <v>211.533611784</v>
+        <v>210.060815712</v>
       </c>
       <c r="P5">
-        <v>749.982805416</v>
+        <v>744.7610738880001</v>
       </c>
       <c r="Q5">
-        <v>793.682805416</v>
+        <v>788.461073888</v>
       </c>
       <c r="R5">
-        <v>0.03092783505154639</v>
+        <v>0.04166666666666667</v>
       </c>
       <c r="S5">
-        <v>0.09675536238742338</v>
+        <v>0.09717212534232353</v>
       </c>
       <c r="T5">
-        <v>1.176798207561741</v>
+        <v>1.186423218067518</v>
       </c>
       <c r="U5">
         <v>0.0503</v>
@@ -2812,7 +2812,7 @@
         </is>
       </c>
       <c r="Y5">
-        <v>48.87574143394375</v>
+        <v>36.65680607545781</v>
       </c>
       <c r="Z5">
         <v>0</v>
@@ -2820,22 +2820,22 @@
     </row>
     <row r="6">
       <c r="A6">
-        <v>0.04</v>
+        <v>0.05</v>
       </c>
       <c r="B6">
-        <v>0.09485460032863059</v>
+        <v>0.09467947914146051</v>
       </c>
       <c r="C6">
-        <v>12907.67165091996</v>
+        <v>12819.33326310393</v>
       </c>
       <c r="D6">
-        <v>12491.53965091996</v>
+        <v>12536.29326310393</v>
       </c>
       <c r="E6">
-        <v>384.768</v>
+        <v>517.86</v>
       </c>
       <c r="F6">
-        <v>532.3680000000001</v>
+        <v>665.46</v>
       </c>
       <c r="G6">
         <v>948.5</v>
@@ -2856,28 +2856,28 @@
         <v>981.6</v>
       </c>
       <c r="M6">
-        <v>26.7781104</v>
+        <v>33.472638</v>
       </c>
       <c r="N6">
-        <v>954.8218896000001</v>
+        <v>948.1273620000001</v>
       </c>
       <c r="O6">
-        <v>210.060815712</v>
+        <v>208.58801964</v>
       </c>
       <c r="P6">
-        <v>744.7610738880001</v>
+        <v>739.5393423600001</v>
       </c>
       <c r="Q6">
-        <v>788.461073888</v>
+        <v>783.23934236</v>
       </c>
       <c r="R6">
-        <v>0.04166666666666667</v>
+        <v>0.05263157894736843</v>
       </c>
       <c r="S6">
-        <v>0.09717212534232353</v>
+        <v>0.09759766225416897</v>
       </c>
       <c r="T6">
-        <v>1.186423218067518</v>
+        <v>1.196250860373417</v>
       </c>
       <c r="U6">
         <v>0.0503</v>
@@ -2894,7 +2894,7 @@
         </is>
       </c>
       <c r="Y6">
-        <v>36.65680607545781</v>
+        <v>29.32544486036625</v>
       </c>
       <c r="Z6">
         <v>0</v>
@@ -2902,22 +2902,22 @@
     </row>
     <row r="7">
       <c r="A7">
-        <v>0.05</v>
+        <v>0.06</v>
       </c>
       <c r="B7">
-        <v>0.09467947914146051</v>
+        <v>0.09450435795429042</v>
       </c>
       <c r="C7">
-        <v>12819.33326310393</v>
+        <v>12731.31670709207</v>
       </c>
       <c r="D7">
-        <v>12536.29326310393</v>
+        <v>12581.36870709207</v>
       </c>
       <c r="E7">
-        <v>517.86</v>
+        <v>650.9520000000001</v>
       </c>
       <c r="F7">
-        <v>665.46</v>
+        <v>798.5520000000001</v>
       </c>
       <c r="G7">
         <v>948.5</v>
@@ -2938,28 +2938,28 @@
         <v>981.6</v>
       </c>
       <c r="M7">
-        <v>33.472638</v>
+        <v>40.1671656</v>
       </c>
       <c r="N7">
-        <v>948.1273620000001</v>
+        <v>941.4328344</v>
       </c>
       <c r="O7">
-        <v>208.58801964</v>
+        <v>207.115223568</v>
       </c>
       <c r="P7">
-        <v>739.5393423600001</v>
+        <v>734.317610832</v>
       </c>
       <c r="Q7">
-        <v>783.23934236</v>
+        <v>778.0176108319999</v>
       </c>
       <c r="R7">
-        <v>0.05263157894736843</v>
+        <v>0.06382978723404256</v>
       </c>
       <c r="S7">
-        <v>0.09759766225416897</v>
+        <v>0.09803225314286215</v>
       </c>
       <c r="T7">
-        <v>1.196250860373417</v>
+        <v>1.206287601451782</v>
       </c>
       <c r="U7">
         <v>0.0503</v>
@@ -2976,7 +2976,7 @@
         </is>
       </c>
       <c r="Y7">
-        <v>29.32544486036625</v>
+        <v>24.43787071697187</v>
       </c>
       <c r="Z7">
         <v>0</v>
@@ -2984,22 +2984,22 @@
     </row>
     <row r="8">
       <c r="A8">
-        <v>0.06</v>
+        <v>0.06999999999999999</v>
       </c>
       <c r="B8">
-        <v>0.09450435795429042</v>
+        <v>0.09432923676712032</v>
       </c>
       <c r="C8">
-        <v>12731.31670709207</v>
+        <v>12643.62546694296</v>
       </c>
       <c r="D8">
-        <v>12581.36870709207</v>
+        <v>12626.76946694296</v>
       </c>
       <c r="E8">
-        <v>650.952</v>
+        <v>784.044</v>
       </c>
       <c r="F8">
-        <v>798.552</v>
+        <v>931.644</v>
       </c>
       <c r="G8">
         <v>948.5</v>
@@ -3020,28 +3020,28 @@
         <v>981.6</v>
       </c>
       <c r="M8">
-        <v>40.1671656</v>
+        <v>46.8616932</v>
       </c>
       <c r="N8">
-        <v>941.4328344</v>
+        <v>934.7383068</v>
       </c>
       <c r="O8">
-        <v>207.115223568</v>
+        <v>205.642427496</v>
       </c>
       <c r="P8">
-        <v>734.317610832</v>
+        <v>729.0958793040001</v>
       </c>
       <c r="Q8">
-        <v>778.0176108319999</v>
+        <v>772.795879304</v>
       </c>
       <c r="R8">
-        <v>0.06382978723404255</v>
+        <v>0.07526881720430106</v>
       </c>
       <c r="S8">
-        <v>0.09803225314286215</v>
+        <v>0.0984761900721724</v>
       </c>
       <c r="T8">
-        <v>1.206287601451782</v>
+        <v>1.216540186424305</v>
       </c>
       <c r="U8">
         <v>0.0503</v>
@@ -3058,7 +3058,7 @@
         </is>
       </c>
       <c r="Y8">
-        <v>24.43787071697188</v>
+        <v>20.94674632883304</v>
       </c>
       <c r="Z8">
         <v>0</v>
@@ -3066,22 +3066,22 @@
     </row>
     <row r="9">
       <c r="A9">
-        <v>0.07000000000000001</v>
+        <v>0.08</v>
       </c>
       <c r="B9">
-        <v>0.09432923676712035</v>
+        <v>0.09415411557995025</v>
       </c>
       <c r="C9">
-        <v>12643.62546694295</v>
+        <v>12556.26307718715</v>
       </c>
       <c r="D9">
-        <v>12626.76946694295</v>
+        <v>12672.49907718715</v>
       </c>
       <c r="E9">
-        <v>784.0440000000001</v>
+        <v>917.1360000000001</v>
       </c>
       <c r="F9">
-        <v>931.6440000000001</v>
+        <v>1064.736</v>
       </c>
       <c r="G9">
         <v>948.5</v>
@@ -3102,28 +3102,28 @@
         <v>981.6</v>
       </c>
       <c r="M9">
-        <v>46.8616932</v>
+        <v>53.55622080000001</v>
       </c>
       <c r="N9">
-        <v>934.7383068</v>
+        <v>928.0437792</v>
       </c>
       <c r="O9">
-        <v>205.642427496</v>
+        <v>204.169631424</v>
       </c>
       <c r="P9">
-        <v>729.0958793040001</v>
+        <v>723.874147776</v>
       </c>
       <c r="Q9">
-        <v>772.795879304</v>
+        <v>767.5741477759999</v>
       </c>
       <c r="R9">
-        <v>0.07526881720430109</v>
+        <v>0.08695652173913043</v>
       </c>
       <c r="S9">
-        <v>0.09847619007217243</v>
+        <v>0.09892977780429375</v>
       </c>
       <c r="T9">
-        <v>1.216540186424305</v>
+        <v>1.227015653678839</v>
       </c>
       <c r="U9">
         <v>0.0503</v>
@@ -3140,7 +3140,7 @@
         </is>
       </c>
       <c r="Y9">
-        <v>20.94674632883303</v>
+        <v>18.3284030377289</v>
       </c>
       <c r="Z9">
         <v>0</v>
@@ -3148,22 +3148,22 @@
     </row>
     <row r="10">
       <c r="A10">
-        <v>0.08</v>
+        <v>0.09</v>
       </c>
       <c r="B10">
-        <v>0.09415411557995025</v>
+        <v>0.09397899439278018</v>
       </c>
       <c r="C10">
-        <v>12556.26307718715</v>
+        <v>12469.23312374455</v>
       </c>
       <c r="D10">
-        <v>12672.49907718715</v>
+        <v>12718.56112374455</v>
       </c>
       <c r="E10">
-        <v>917.1360000000001</v>
+        <v>1050.228</v>
       </c>
       <c r="F10">
-        <v>1064.736</v>
+        <v>1197.828</v>
       </c>
       <c r="G10">
         <v>948.5</v>
@@ -3184,28 +3184,28 @@
         <v>981.6</v>
       </c>
       <c r="M10">
-        <v>53.55622080000001</v>
+        <v>60.2507484</v>
       </c>
       <c r="N10">
-        <v>928.0437792</v>
+        <v>921.3492516</v>
       </c>
       <c r="O10">
-        <v>204.169631424</v>
+        <v>202.696835352</v>
       </c>
       <c r="P10">
-        <v>723.874147776</v>
+        <v>718.652416248</v>
       </c>
       <c r="Q10">
-        <v>767.5741477759999</v>
+        <v>762.3524162479999</v>
       </c>
       <c r="R10">
-        <v>0.08695652173913043</v>
+        <v>0.0989010989010989</v>
       </c>
       <c r="S10">
-        <v>0.09892977780429375</v>
+        <v>0.09939333449756063</v>
       </c>
       <c r="T10">
-        <v>1.227015653678839</v>
+        <v>1.237721350982924</v>
       </c>
       <c r="U10">
         <v>0.0503</v>
@@ -3222,7 +3222,7 @@
         </is>
       </c>
       <c r="Y10">
-        <v>18.3284030377289</v>
+        <v>16.29191381131458</v>
       </c>
       <c r="Z10">
         <v>0</v>
@@ -3230,22 +3230,22 @@
     </row>
     <row r="11">
       <c r="A11">
-        <v>0.09</v>
+        <v>0.09999999999999999</v>
       </c>
       <c r="B11">
-        <v>0.09397899439278018</v>
+        <v>0.09380387320561008</v>
       </c>
       <c r="C11">
-        <v>12469.23312374455</v>
+        <v>12382.53924486168</v>
       </c>
       <c r="D11">
-        <v>12718.56112374455</v>
+        <v>12764.95924486168</v>
       </c>
       <c r="E11">
-        <v>1050.228</v>
+        <v>1183.32</v>
       </c>
       <c r="F11">
-        <v>1197.828</v>
+        <v>1330.92</v>
       </c>
       <c r="G11">
         <v>948.5</v>
@@ -3266,28 +3266,28 @@
         <v>981.6</v>
       </c>
       <c r="M11">
-        <v>60.2507484</v>
+        <v>66.94527600000001</v>
       </c>
       <c r="N11">
-        <v>921.3492516</v>
+        <v>914.654724</v>
       </c>
       <c r="O11">
-        <v>202.696835352</v>
+        <v>201.22403928</v>
       </c>
       <c r="P11">
-        <v>718.652416248</v>
+        <v>713.43068472</v>
       </c>
       <c r="Q11">
-        <v>762.3524162479999</v>
+        <v>757.13068472</v>
       </c>
       <c r="R11">
-        <v>0.0989010989010989</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="S11">
-        <v>0.09939333449756063</v>
+        <v>0.09986719245067788</v>
       </c>
       <c r="T11">
-        <v>1.237721350982924</v>
+        <v>1.248664952671544</v>
       </c>
       <c r="U11">
         <v>0.0503</v>
@@ -3304,7 +3304,7 @@
         </is>
       </c>
       <c r="Y11">
-        <v>16.29191381131458</v>
+        <v>14.66272243018312</v>
       </c>
       <c r="Z11">
         <v>0</v>
@@ -3312,22 +3312,22 @@
     </row>
     <row r="12">
       <c r="A12">
-        <v>0.1</v>
+        <v>0.11</v>
       </c>
       <c r="B12">
-        <v>0.09380387320561008</v>
+        <v>0.09362875201844002</v>
       </c>
       <c r="C12">
-        <v>12382.53924486168</v>
+        <v>12296.18513206969</v>
       </c>
       <c r="D12">
-        <v>12764.95924486168</v>
+        <v>12811.69713206969</v>
       </c>
       <c r="E12">
-        <v>1183.32</v>
+        <v>1316.412</v>
       </c>
       <c r="F12">
-        <v>1330.92</v>
+        <v>1464.012</v>
       </c>
       <c r="G12">
         <v>948.5</v>
@@ -3348,28 +3348,28 @@
         <v>981.6</v>
       </c>
       <c r="M12">
-        <v>66.94527600000001</v>
+        <v>73.63980360000001</v>
       </c>
       <c r="N12">
-        <v>914.654724</v>
+        <v>907.9601964</v>
       </c>
       <c r="O12">
-        <v>201.22403928</v>
+        <v>199.751243208</v>
       </c>
       <c r="P12">
-        <v>713.43068472</v>
+        <v>708.208953192</v>
       </c>
       <c r="Q12">
-        <v>757.13068472</v>
+        <v>751.9089531919999</v>
       </c>
       <c r="R12">
-        <v>0.1111111111111111</v>
+        <v>0.1235955056179775</v>
       </c>
       <c r="S12">
-        <v>0.09986719245067788</v>
+        <v>0.1003516988971236</v>
       </c>
       <c r="T12">
-        <v>1.248664952671544</v>
+        <v>1.259854477993617</v>
       </c>
       <c r="U12">
         <v>0.0503</v>
@@ -3386,7 +3386,7 @@
         </is>
       </c>
       <c r="Y12">
-        <v>14.66272243018312</v>
+        <v>13.32974766380284</v>
       </c>
       <c r="Z12">
         <v>0</v>
@@ -3394,22 +3394,22 @@
     </row>
     <row r="13">
       <c r="A13">
-        <v>0.11</v>
+        <v>0.12</v>
       </c>
       <c r="B13">
-        <v>0.09362875201844002</v>
+        <v>0.09345363083126992</v>
       </c>
       <c r="C13">
-        <v>12296.18513206969</v>
+        <v>12210.17453116341</v>
       </c>
       <c r="D13">
-        <v>12811.69713206969</v>
+        <v>12858.77853116341</v>
       </c>
       <c r="E13">
-        <v>1316.412</v>
+        <v>1449.504</v>
       </c>
       <c r="F13">
-        <v>1464.012</v>
+        <v>1597.104</v>
       </c>
       <c r="G13">
         <v>948.5</v>
@@ -3430,28 +3430,28 @@
         <v>981.6</v>
       </c>
       <c r="M13">
-        <v>73.63980360000001</v>
+        <v>80.33433119999999</v>
       </c>
       <c r="N13">
-        <v>907.9601964</v>
+        <v>901.2656688000001</v>
       </c>
       <c r="O13">
-        <v>199.751243208</v>
+        <v>198.278447136</v>
       </c>
       <c r="P13">
-        <v>708.208953192</v>
+        <v>702.9872216640001</v>
       </c>
       <c r="Q13">
-        <v>751.9089531919999</v>
+        <v>746.687221664</v>
       </c>
       <c r="R13">
-        <v>0.1235955056179775</v>
+        <v>0.1363636363636364</v>
       </c>
       <c r="S13">
-        <v>0.1003516988971236</v>
+        <v>0.1008472168537158</v>
       </c>
       <c r="T13">
-        <v>1.259854477993617</v>
+        <v>1.271298310709372</v>
       </c>
       <c r="U13">
         <v>0.0503</v>
@@ -3468,7 +3468,7 @@
         </is>
       </c>
       <c r="Y13">
-        <v>13.32974766380284</v>
+        <v>12.21893535848594</v>
       </c>
       <c r="Z13">
         <v>0</v>
@@ -3476,22 +3476,22 @@
     </row>
     <row r="14">
       <c r="A14">
-        <v>0.12</v>
+        <v>0.13</v>
       </c>
       <c r="B14">
-        <v>0.09345363083126992</v>
+        <v>0.09327850964409984</v>
       </c>
       <c r="C14">
-        <v>12210.17453116341</v>
+        <v>12124.51124320206</v>
       </c>
       <c r="D14">
-        <v>12858.77853116341</v>
+        <v>12906.20724320206</v>
       </c>
       <c r="E14">
-        <v>1449.504</v>
+        <v>1582.596</v>
       </c>
       <c r="F14">
-        <v>1597.104</v>
+        <v>1730.196</v>
       </c>
       <c r="G14">
         <v>948.5</v>
@@ -3512,28 +3512,28 @@
         <v>981.6</v>
       </c>
       <c r="M14">
-        <v>80.33433119999999</v>
+        <v>87.02885880000001</v>
       </c>
       <c r="N14">
-        <v>901.2656688000001</v>
+        <v>894.5711412000001</v>
       </c>
       <c r="O14">
-        <v>198.278447136</v>
+        <v>196.805651064</v>
       </c>
       <c r="P14">
-        <v>702.9872216640001</v>
+        <v>697.765490136</v>
       </c>
       <c r="Q14">
-        <v>746.687221664</v>
+        <v>741.465490136</v>
       </c>
       <c r="R14">
-        <v>0.1363636363636364</v>
+        <v>0.1494252873563219</v>
       </c>
       <c r="S14">
-        <v>0.1008472168537158</v>
+        <v>0.101354126027701</v>
       </c>
       <c r="T14">
-        <v>1.271298310709372</v>
+        <v>1.283005220039283</v>
       </c>
       <c r="U14">
         <v>0.0503</v>
@@ -3550,7 +3550,7 @@
         </is>
       </c>
       <c r="Y14">
-        <v>12.21893535848594</v>
+        <v>11.27901725398702</v>
       </c>
       <c r="Z14">
         <v>0</v>
@@ -3558,22 +3558,22 @@
     </row>
     <row r="15">
       <c r="A15">
-        <v>0.13</v>
+        <v>0.14</v>
       </c>
       <c r="B15">
-        <v>0.09327850964409984</v>
+        <v>0.09310338845692975</v>
       </c>
       <c r="C15">
-        <v>12124.51124320206</v>
+        <v>12039.19912553228</v>
       </c>
       <c r="D15">
-        <v>12906.20724320206</v>
+        <v>12953.98712553228</v>
       </c>
       <c r="E15">
-        <v>1582.596</v>
+        <v>1715.688</v>
       </c>
       <c r="F15">
-        <v>1730.196</v>
+        <v>1863.288</v>
       </c>
       <c r="G15">
         <v>948.5</v>
@@ -3594,28 +3594,28 @@
         <v>981.6</v>
       </c>
       <c r="M15">
-        <v>87.02885880000001</v>
+        <v>93.72338640000001</v>
       </c>
       <c r="N15">
-        <v>894.5711412000001</v>
+        <v>887.8766136</v>
       </c>
       <c r="O15">
-        <v>196.805651064</v>
+        <v>195.332854992</v>
       </c>
       <c r="P15">
-        <v>697.765490136</v>
+        <v>692.543758608</v>
       </c>
       <c r="Q15">
-        <v>741.465490136</v>
+        <v>736.2437586079999</v>
       </c>
       <c r="R15">
-        <v>0.1494252873563219</v>
+        <v>0.1627906976744186</v>
       </c>
       <c r="S15">
-        <v>0.101354126027701</v>
+        <v>0.1018728237871276</v>
       </c>
       <c r="T15">
-        <v>1.283005220039283</v>
+        <v>1.294984383074541</v>
       </c>
       <c r="U15">
         <v>0.0503</v>
@@ -3632,7 +3632,7 @@
         </is>
       </c>
       <c r="Y15">
-        <v>11.27901725398702</v>
+        <v>10.47337316441652</v>
       </c>
       <c r="Z15">
         <v>0</v>
@@ -3640,22 +3640,22 @@
     </row>
     <row r="16">
       <c r="A16">
-        <v>0.14</v>
+        <v>0.15</v>
       </c>
       <c r="B16">
-        <v>0.09310338845692975</v>
+        <v>0.09292826726975968</v>
       </c>
       <c r="C16">
-        <v>12039.19912553228</v>
+        <v>11954.24209283384</v>
       </c>
       <c r="D16">
-        <v>12953.98712553228</v>
+        <v>13002.12209283384</v>
       </c>
       <c r="E16">
-        <v>1715.688</v>
+        <v>1848.78</v>
       </c>
       <c r="F16">
-        <v>1863.288</v>
+        <v>1996.38</v>
       </c>
       <c r="G16">
         <v>948.5</v>
@@ -3676,28 +3676,28 @@
         <v>981.6</v>
       </c>
       <c r="M16">
-        <v>93.72338640000001</v>
+        <v>100.417914</v>
       </c>
       <c r="N16">
-        <v>887.8766136</v>
+        <v>881.182086</v>
       </c>
       <c r="O16">
-        <v>195.332854992</v>
+        <v>193.86005892</v>
       </c>
       <c r="P16">
-        <v>692.543758608</v>
+        <v>687.32202708</v>
       </c>
       <c r="Q16">
-        <v>736.2437586079999</v>
+        <v>731.0220270799999</v>
       </c>
       <c r="R16">
-        <v>0.1627906976744186</v>
+        <v>0.1764705882352942</v>
       </c>
       <c r="S16">
-        <v>0.1018728237871276</v>
+        <v>0.1024037261997173</v>
       </c>
       <c r="T16">
-        <v>1.294984383074541</v>
+        <v>1.307245408769452</v>
       </c>
       <c r="U16">
         <v>0.0503</v>
@@ -3714,7 +3714,7 @@
         </is>
       </c>
       <c r="Y16">
-        <v>10.47337316441652</v>
+        <v>9.775148286788749</v>
       </c>
       <c r="Z16">
         <v>0</v>
@@ -3722,22 +3722,22 @@
     </row>
     <row r="17">
       <c r="A17">
-        <v>0.15</v>
+        <v>0.16</v>
       </c>
       <c r="B17">
-        <v>0.09292826726975968</v>
+        <v>0.09275314608258958</v>
       </c>
       <c r="C17">
-        <v>11954.24209283384</v>
+        <v>11869.64411818887</v>
       </c>
       <c r="D17">
-        <v>13002.12209283384</v>
+        <v>13050.61611818887</v>
       </c>
       <c r="E17">
-        <v>1848.78</v>
+        <v>1981.872</v>
       </c>
       <c r="F17">
-        <v>1996.38</v>
+        <v>2129.472</v>
       </c>
       <c r="G17">
         <v>948.5</v>
@@ -3758,28 +3758,28 @@
         <v>981.6</v>
       </c>
       <c r="M17">
-        <v>100.417914</v>
+        <v>107.1124416</v>
       </c>
       <c r="N17">
-        <v>881.182086</v>
+        <v>874.4875584</v>
       </c>
       <c r="O17">
-        <v>193.86005892</v>
+        <v>192.387262848</v>
       </c>
       <c r="P17">
-        <v>687.32202708</v>
+        <v>682.100295552</v>
       </c>
       <c r="Q17">
-        <v>731.0220270799999</v>
+        <v>725.800295552</v>
       </c>
       <c r="R17">
-        <v>0.1764705882352941</v>
+        <v>0.1904761904761905</v>
       </c>
       <c r="S17">
-        <v>0.1024037261997173</v>
+        <v>0.10294726914594</v>
       </c>
       <c r="T17">
-        <v>1.307245408769452</v>
+        <v>1.319798363647575</v>
       </c>
       <c r="U17">
         <v>0.0503</v>
@@ -3796,7 +3796,7 @@
         </is>
       </c>
       <c r="Y17">
-        <v>9.775148286788751</v>
+        <v>9.164201518864452</v>
       </c>
       <c r="Z17">
         <v>0</v>
@@ -3804,22 +3804,22 @@
     </row>
     <row r="18">
       <c r="A18">
-        <v>0.16</v>
+        <v>0.17</v>
       </c>
       <c r="B18">
-        <v>0.09275314608258958</v>
+        <v>0.0927769248954195</v>
       </c>
       <c r="C18">
-        <v>11869.64411818887</v>
+        <v>11729.94614815826</v>
       </c>
       <c r="D18">
-        <v>13050.61611818887</v>
+        <v>13044.01014815826</v>
       </c>
       <c r="E18">
-        <v>1981.872</v>
+        <v>2114.964</v>
       </c>
       <c r="F18">
-        <v>2129.472</v>
+        <v>2262.564</v>
       </c>
       <c r="G18">
         <v>948.5</v>
@@ -3840,45 +3840,45 @@
         <v>981.6</v>
       </c>
       <c r="M18">
-        <v>107.1124416</v>
+        <v>117.2008152</v>
       </c>
       <c r="N18">
-        <v>874.4875584</v>
+        <v>864.3991848000001</v>
       </c>
       <c r="O18">
-        <v>192.387262848</v>
+        <v>190.167820656</v>
       </c>
       <c r="P18">
-        <v>682.100295552</v>
+        <v>674.2313641440001</v>
       </c>
       <c r="Q18">
-        <v>725.800295552</v>
+        <v>717.931364144</v>
       </c>
       <c r="R18">
-        <v>0.1904761904761905</v>
+        <v>0.2048192771084338</v>
       </c>
       <c r="S18">
-        <v>0.10294726914594</v>
+        <v>0.1035039095125536</v>
       </c>
       <c r="T18">
-        <v>1.319798363647575</v>
+        <v>1.332653799366134</v>
       </c>
       <c r="U18">
-        <v>0.0503</v>
+        <v>0.0518</v>
       </c>
       <c r="V18">
         <v>0.22</v>
       </c>
       <c r="W18">
-        <v>0.039234</v>
+        <v>0.040404</v>
       </c>
       <c r="X18" t="inlineStr">
         <is>
-          <t>Aaa/AAA</t>
+          <t>Aa2/AA</t>
         </is>
       </c>
       <c r="Y18">
-        <v>9.164201518864452</v>
+        <v>8.375368365185228</v>
       </c>
       <c r="Z18">
         <v>0</v>
@@ -3886,22 +3886,22 @@
     </row>
     <row r="19">
       <c r="A19">
-        <v>0.17</v>
+        <v>0.18</v>
       </c>
       <c r="B19">
-        <v>0.0927769248954195</v>
+        <v>0.09261350370824942</v>
       </c>
       <c r="C19">
-        <v>11729.94614815826</v>
+        <v>11642.3894628648</v>
       </c>
       <c r="D19">
-        <v>13044.01014815826</v>
+        <v>13089.5454628648</v>
       </c>
       <c r="E19">
-        <v>2114.964</v>
+        <v>2248.056</v>
       </c>
       <c r="F19">
-        <v>2262.564</v>
+        <v>2395.656</v>
       </c>
       <c r="G19">
         <v>948.5</v>
@@ -3922,28 +3922,28 @@
         <v>981.6</v>
       </c>
       <c r="M19">
-        <v>117.2008152</v>
+        <v>124.0949808</v>
       </c>
       <c r="N19">
-        <v>864.3991848000001</v>
+        <v>857.5050192</v>
       </c>
       <c r="O19">
-        <v>190.167820656</v>
+        <v>188.651104224</v>
       </c>
       <c r="P19">
-        <v>674.2313641440001</v>
+        <v>668.8539149759999</v>
       </c>
       <c r="Q19">
-        <v>717.931364144</v>
+        <v>712.5539149759999</v>
       </c>
       <c r="R19">
-        <v>0.2048192771084338</v>
+        <v>0.2195121951219512</v>
       </c>
       <c r="S19">
-        <v>0.1035039095125536</v>
+        <v>0.1040741264734749</v>
       </c>
       <c r="T19">
-        <v>1.332653799366134</v>
+        <v>1.345822782297342</v>
       </c>
       <c r="U19">
         <v>0.0518</v>
@@ -3960,7 +3960,7 @@
         </is>
       </c>
       <c r="Y19">
-        <v>8.375368365185228</v>
+        <v>7.910070122674936</v>
       </c>
       <c r="Z19">
         <v>0</v>
@@ -3968,22 +3968,22 @@
     </row>
     <row r="20">
       <c r="A20">
-        <v>0.18</v>
+        <v>0.19</v>
       </c>
       <c r="B20">
-        <v>0.09261350370824942</v>
+        <v>0.09245008252107935</v>
       </c>
       <c r="C20">
-        <v>11642.3894628648</v>
+        <v>11555.15180959808</v>
       </c>
       <c r="D20">
-        <v>13089.5454628648</v>
+        <v>13135.39980959808</v>
       </c>
       <c r="E20">
-        <v>2248.056</v>
+        <v>2381.148</v>
       </c>
       <c r="F20">
-        <v>2395.656</v>
+        <v>2528.748</v>
       </c>
       <c r="G20">
         <v>948.5</v>
@@ -4004,28 +4004,28 @@
         <v>981.6</v>
       </c>
       <c r="M20">
-        <v>124.0949808</v>
+        <v>130.9891464</v>
       </c>
       <c r="N20">
-        <v>857.5050192</v>
+        <v>850.6108536</v>
       </c>
       <c r="O20">
-        <v>188.651104224</v>
+        <v>187.134387792</v>
       </c>
       <c r="P20">
-        <v>668.8539149759999</v>
+        <v>663.4764658080001</v>
       </c>
       <c r="Q20">
-        <v>712.5539149759999</v>
+        <v>707.176465808</v>
       </c>
       <c r="R20">
-        <v>0.2195121951219512</v>
+        <v>0.2345679012345679</v>
       </c>
       <c r="S20">
-        <v>0.1040741264734749</v>
+        <v>0.1046584228655301</v>
       </c>
       <c r="T20">
-        <v>1.345822782297342</v>
+        <v>1.359316925300925</v>
       </c>
       <c r="U20">
         <v>0.0518</v>
@@ -4042,7 +4042,7 @@
         </is>
       </c>
       <c r="Y20">
-        <v>7.910070122674938</v>
+        <v>7.493750642534151</v>
       </c>
       <c r="Z20">
         <v>0</v>
@@ -4050,22 +4050,22 @@
     </row>
     <row r="21">
       <c r="A21">
-        <v>0.19</v>
+        <v>0.2</v>
       </c>
       <c r="B21">
-        <v>0.09245008252107935</v>
+        <v>0.09228666133390927</v>
       </c>
       <c r="C21">
-        <v>11555.15180959808</v>
+        <v>11468.23655297441</v>
       </c>
       <c r="D21">
-        <v>13135.39980959808</v>
+        <v>13181.57655297441</v>
       </c>
       <c r="E21">
-        <v>2381.148</v>
+        <v>2514.24</v>
       </c>
       <c r="F21">
-        <v>2528.748</v>
+        <v>2661.84</v>
       </c>
       <c r="G21">
         <v>948.5</v>
@@ -4086,28 +4086,28 @@
         <v>981.6</v>
       </c>
       <c r="M21">
-        <v>130.9891464</v>
+        <v>137.883312</v>
       </c>
       <c r="N21">
-        <v>850.6108536</v>
+        <v>843.716688</v>
       </c>
       <c r="O21">
-        <v>187.134387792</v>
+        <v>185.61767136</v>
       </c>
       <c r="P21">
-        <v>663.4764658080001</v>
+        <v>658.0990166399999</v>
       </c>
       <c r="Q21">
-        <v>707.176465808</v>
+        <v>701.7990166399999</v>
       </c>
       <c r="R21">
-        <v>0.2345679012345679</v>
+        <v>0.25</v>
       </c>
       <c r="S21">
-        <v>0.1046584228655301</v>
+        <v>0.1052573266673866</v>
       </c>
       <c r="T21">
-        <v>1.359316925300925</v>
+        <v>1.373148421879597</v>
       </c>
       <c r="U21">
         <v>0.0518</v>
@@ -4124,7 +4124,7 @@
         </is>
       </c>
       <c r="Y21">
-        <v>7.493750642534151</v>
+        <v>7.119063110407443</v>
       </c>
       <c r="Z21">
         <v>0</v>
@@ -4132,22 +4132,22 @@
     </row>
     <row r="22">
       <c r="A22">
-        <v>0.2</v>
+        <v>0.21</v>
       </c>
       <c r="B22">
-        <v>0.09228666133390927</v>
+        <v>0.09212324014673919</v>
       </c>
       <c r="C22">
-        <v>11468.23655297441</v>
+        <v>11381.64710508943</v>
       </c>
       <c r="D22">
-        <v>13181.57655297441</v>
+        <v>13228.07910508943</v>
       </c>
       <c r="E22">
-        <v>2514.24</v>
+        <v>2647.332</v>
       </c>
       <c r="F22">
-        <v>2661.84</v>
+        <v>2794.932</v>
       </c>
       <c r="G22">
         <v>948.5</v>
@@ -4168,28 +4168,28 @@
         <v>981.6</v>
       </c>
       <c r="M22">
-        <v>137.883312</v>
+        <v>144.7774776</v>
       </c>
       <c r="N22">
-        <v>843.716688</v>
+        <v>836.8225224</v>
       </c>
       <c r="O22">
-        <v>185.61767136</v>
+        <v>184.100954928</v>
       </c>
       <c r="P22">
-        <v>658.0990166399999</v>
+        <v>652.7215674720001</v>
       </c>
       <c r="Q22">
-        <v>701.7990166399999</v>
+        <v>696.421567472</v>
       </c>
       <c r="R22">
-        <v>0.25</v>
+        <v>0.2658227848101266</v>
       </c>
       <c r="S22">
-        <v>0.1052573266673866</v>
+        <v>0.1058713925908091</v>
       </c>
       <c r="T22">
-        <v>1.373148421879597</v>
+        <v>1.387330082928616</v>
       </c>
       <c r="U22">
         <v>0.0518</v>
@@ -4206,7 +4206,7 @@
         </is>
       </c>
       <c r="Y22">
-        <v>7.119063110407443</v>
+        <v>6.780060105149946</v>
       </c>
       <c r="Z22">
         <v>0</v>
@@ -4214,22 +4214,22 @@
     </row>
     <row r="23">
       <c r="A23">
-        <v>0.21</v>
+        <v>0.22</v>
       </c>
       <c r="B23">
-        <v>0.09212324014673917</v>
+        <v>0.09225153895956908</v>
       </c>
       <c r="C23">
-        <v>11381.64710508943</v>
+        <v>11212.01924679031</v>
       </c>
       <c r="D23">
-        <v>13228.07910508943</v>
+        <v>13191.54324679031</v>
       </c>
       <c r="E23">
-        <v>2647.332</v>
+        <v>2780.424</v>
       </c>
       <c r="F23">
-        <v>2794.932</v>
+        <v>2928.024</v>
       </c>
       <c r="G23">
         <v>948.5</v>
@@ -4250,45 +4250,45 @@
         <v>981.6</v>
       </c>
       <c r="M23">
-        <v>144.7774776</v>
+        <v>156.649284</v>
       </c>
       <c r="N23">
-        <v>836.8225224</v>
+        <v>824.9507160000001</v>
       </c>
       <c r="O23">
-        <v>184.100954928</v>
+        <v>181.48915752</v>
       </c>
       <c r="P23">
-        <v>652.7215674720001</v>
+        <v>643.46155848</v>
       </c>
       <c r="Q23">
-        <v>696.421567472</v>
+        <v>687.1615584799999</v>
       </c>
       <c r="R23">
-        <v>0.2658227848101266</v>
+        <v>0.282051282051282</v>
       </c>
       <c r="S23">
-        <v>0.1058713925908091</v>
+        <v>0.1065012037943193</v>
       </c>
       <c r="T23">
-        <v>1.387330082928616</v>
+        <v>1.401875376312225</v>
       </c>
       <c r="U23">
-        <v>0.0518</v>
+        <v>0.0535</v>
       </c>
       <c r="V23">
         <v>0.22</v>
       </c>
       <c r="W23">
-        <v>0.040404</v>
+        <v>0.04173</v>
       </c>
       <c r="X23" t="inlineStr">
         <is>
-          <t>Aa2/AA</t>
+          <t>A1/A+</t>
         </is>
       </c>
       <c r="Y23">
-        <v>6.780060105149946</v>
+        <v>6.266227172797036</v>
       </c>
       <c r="Z23">
         <v>0</v>
@@ -4296,22 +4296,22 @@
     </row>
     <row r="24">
       <c r="A24">
-        <v>0.22</v>
+        <v>0.23</v>
       </c>
       <c r="B24">
-        <v>0.09225153895956908</v>
+        <v>0.092101377772399</v>
       </c>
       <c r="C24">
-        <v>11212.01924679031</v>
+        <v>11121.70907942347</v>
       </c>
       <c r="D24">
-        <v>13191.54324679031</v>
+        <v>13234.32507942347</v>
       </c>
       <c r="E24">
-        <v>2780.424</v>
+        <v>2913.516000000001</v>
       </c>
       <c r="F24">
-        <v>2928.024</v>
+        <v>3061.116</v>
       </c>
       <c r="G24">
         <v>948.5</v>
@@ -4332,28 +4332,28 @@
         <v>981.6</v>
       </c>
       <c r="M24">
-        <v>156.649284</v>
+        <v>163.769706</v>
       </c>
       <c r="N24">
-        <v>824.9507160000001</v>
+        <v>817.830294</v>
       </c>
       <c r="O24">
-        <v>181.48915752</v>
+        <v>179.92266468</v>
       </c>
       <c r="P24">
-        <v>643.46155848</v>
+        <v>637.90762932</v>
       </c>
       <c r="Q24">
-        <v>687.1615584799999</v>
+        <v>681.6076293199999</v>
       </c>
       <c r="R24">
-        <v>0.282051282051282</v>
+        <v>0.2987012987012987</v>
       </c>
       <c r="S24">
-        <v>0.1065012037943193</v>
+        <v>0.1071473737303883</v>
       </c>
       <c r="T24">
-        <v>1.401875376312225</v>
+        <v>1.416798469523979</v>
       </c>
       <c r="U24">
         <v>0.0535</v>
@@ -4370,7 +4370,7 @@
         </is>
       </c>
       <c r="Y24">
-        <v>6.266227172797036</v>
+        <v>5.993782513110208</v>
       </c>
       <c r="Z24">
         <v>0</v>
@@ -4378,22 +4378,22 @@
     </row>
     <row r="25">
       <c r="A25">
-        <v>0.23</v>
+        <v>0.24</v>
       </c>
       <c r="B25">
-        <v>0.092101377772399</v>
+        <v>0.09195121658522892</v>
       </c>
       <c r="C25">
-        <v>11121.70907942347</v>
+        <v>11031.67730865168</v>
       </c>
       <c r="D25">
-        <v>13234.32507942347</v>
+        <v>13277.38530865168</v>
       </c>
       <c r="E25">
-        <v>2913.516000000001</v>
+        <v>3046.608000000001</v>
       </c>
       <c r="F25">
-        <v>3061.116</v>
+        <v>3194.208000000001</v>
       </c>
       <c r="G25">
         <v>948.5</v>
@@ -4414,28 +4414,28 @@
         <v>981.6</v>
       </c>
       <c r="M25">
-        <v>163.769706</v>
+        <v>170.890128</v>
       </c>
       <c r="N25">
-        <v>817.830294</v>
+        <v>810.709872</v>
       </c>
       <c r="O25">
-        <v>179.92266468</v>
+        <v>178.35617184</v>
       </c>
       <c r="P25">
-        <v>637.90762932</v>
+        <v>632.35370016</v>
       </c>
       <c r="Q25">
-        <v>681.6076293199999</v>
+        <v>676.0537001599999</v>
       </c>
       <c r="R25">
-        <v>0.2987012987012987</v>
+        <v>0.3157894736842106</v>
       </c>
       <c r="S25">
-        <v>0.1071473737303883</v>
+        <v>0.1078105481384591</v>
       </c>
       <c r="T25">
-        <v>1.416798469523979</v>
+        <v>1.432114275714991</v>
       </c>
       <c r="U25">
         <v>0.0535</v>
@@ -4452,7 +4452,7 @@
         </is>
       </c>
       <c r="Y25">
-        <v>5.993782513110208</v>
+        <v>5.744041575063949</v>
       </c>
       <c r="Z25">
         <v>0</v>
@@ -4460,22 +4460,22 @@
     </row>
     <row r="26">
       <c r="A26">
-        <v>0.24</v>
+        <v>0.25</v>
       </c>
       <c r="B26">
-        <v>0.09195121658522892</v>
+        <v>0.09195705539805882</v>
       </c>
       <c r="C26">
-        <v>11031.67730865168</v>
+        <v>10896.90573513862</v>
       </c>
       <c r="D26">
-        <v>13277.38530865168</v>
+        <v>13275.70573513862</v>
       </c>
       <c r="E26">
-        <v>3046.608</v>
+        <v>3179.7</v>
       </c>
       <c r="F26">
-        <v>3194.208</v>
+        <v>3327.3</v>
       </c>
       <c r="G26">
         <v>948.5</v>
@@ -4496,45 +4496,45 @@
         <v>981.6</v>
       </c>
       <c r="M26">
-        <v>170.890128</v>
+        <v>180.67239</v>
       </c>
       <c r="N26">
-        <v>810.709872</v>
+        <v>800.92761</v>
       </c>
       <c r="O26">
-        <v>178.35617184</v>
+        <v>176.2040742</v>
       </c>
       <c r="P26">
-        <v>632.35370016</v>
+        <v>624.7235358</v>
       </c>
       <c r="Q26">
-        <v>676.0537001599999</v>
+        <v>668.4235358</v>
       </c>
       <c r="R26">
-        <v>0.3157894736842105</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="S26">
-        <v>0.1078105481384591</v>
+        <v>0.1084914071974118</v>
       </c>
       <c r="T26">
-        <v>1.432114275714991</v>
+        <v>1.447838503404429</v>
       </c>
       <c r="U26">
-        <v>0.0535</v>
+        <v>0.0543</v>
       </c>
       <c r="V26">
         <v>0.22</v>
       </c>
       <c r="W26">
-        <v>0.04173</v>
+        <v>0.042354</v>
       </c>
       <c r="X26" t="inlineStr">
         <is>
-          <t>A1/A+</t>
+          <t>A2/A</t>
         </is>
       </c>
       <c r="Y26">
-        <v>5.74404157506395</v>
+        <v>5.433038219066012</v>
       </c>
       <c r="Z26">
         <v>0</v>
@@ -4542,22 +4542,22 @@
     </row>
     <row r="27">
       <c r="A27">
-        <v>0.25</v>
+        <v>0.26</v>
       </c>
       <c r="B27">
-        <v>0.09195705539805882</v>
+        <v>0.09181313421088874</v>
       </c>
       <c r="C27">
-        <v>10896.90573513862</v>
+        <v>10805.33786433975</v>
       </c>
       <c r="D27">
-        <v>13275.70573513862</v>
+        <v>13317.22986433975</v>
       </c>
       <c r="E27">
-        <v>3179.7</v>
+        <v>3312.792</v>
       </c>
       <c r="F27">
-        <v>3327.3</v>
+        <v>3460.392</v>
       </c>
       <c r="G27">
         <v>948.5</v>
@@ -4578,28 +4578,28 @@
         <v>981.6</v>
       </c>
       <c r="M27">
-        <v>180.67239</v>
+        <v>187.8992856</v>
       </c>
       <c r="N27">
-        <v>800.92761</v>
+        <v>793.7007144</v>
       </c>
       <c r="O27">
-        <v>176.2040742</v>
+        <v>174.614157168</v>
       </c>
       <c r="P27">
-        <v>624.7235358</v>
+        <v>619.086557232</v>
       </c>
       <c r="Q27">
-        <v>668.4235358</v>
+        <v>662.786557232</v>
       </c>
       <c r="R27">
-        <v>0.3333333333333333</v>
+        <v>0.3513513513513514</v>
       </c>
       <c r="S27">
-        <v>0.1084914071974118</v>
+        <v>0.1091906678525524</v>
       </c>
       <c r="T27">
-        <v>1.447838503404429</v>
+        <v>1.463987710220609</v>
       </c>
       <c r="U27">
         <v>0.0543</v>
@@ -4616,7 +4616,7 @@
         </is>
       </c>
       <c r="Y27">
-        <v>5.433038219066012</v>
+        <v>5.224075210640397</v>
       </c>
       <c r="Z27">
         <v>0</v>
@@ -4624,22 +4624,22 @@
     </row>
     <row r="28">
       <c r="A28">
-        <v>0.26</v>
+        <v>0.27</v>
       </c>
       <c r="B28">
-        <v>0.09181313421088874</v>
+        <v>0.09166921302371867</v>
       </c>
       <c r="C28">
-        <v>10805.33786433975</v>
+        <v>10714.03056927683</v>
       </c>
       <c r="D28">
-        <v>13317.22986433975</v>
+        <v>13359.01456927683</v>
       </c>
       <c r="E28">
-        <v>3312.792</v>
+        <v>3445.884</v>
       </c>
       <c r="F28">
-        <v>3460.392</v>
+        <v>3593.484</v>
       </c>
       <c r="G28">
         <v>948.5</v>
@@ -4660,28 +4660,28 @@
         <v>981.6</v>
       </c>
       <c r="M28">
-        <v>187.8992856</v>
+        <v>195.1261812</v>
       </c>
       <c r="N28">
-        <v>793.7007144</v>
+        <v>786.4738188</v>
       </c>
       <c r="O28">
-        <v>174.614157168</v>
+        <v>173.024240136</v>
       </c>
       <c r="P28">
-        <v>619.086557232</v>
+        <v>613.449578664</v>
       </c>
       <c r="Q28">
-        <v>662.786557232</v>
+        <v>657.1495786639999</v>
       </c>
       <c r="R28">
-        <v>0.3513513513513514</v>
+        <v>0.3698630136986302</v>
       </c>
       <c r="S28">
-        <v>0.1091906678525524</v>
+        <v>0.1099090863338612</v>
       </c>
       <c r="T28">
-        <v>1.463987710220609</v>
+        <v>1.48057936105915</v>
       </c>
       <c r="U28">
         <v>0.0543</v>
@@ -4698,7 +4698,7 @@
         </is>
       </c>
       <c r="Y28">
-        <v>5.224075210640397</v>
+        <v>5.03059094357964</v>
       </c>
       <c r="Z28">
         <v>0</v>
@@ -4706,22 +4706,22 @@
     </row>
     <row r="29">
       <c r="A29">
-        <v>0.27</v>
+        <v>0.28</v>
       </c>
       <c r="B29">
-        <v>0.09166921302371867</v>
+        <v>0.09152529183654858</v>
       </c>
       <c r="C29">
-        <v>10714.03056927683</v>
+        <v>10622.98631045049</v>
       </c>
       <c r="D29">
-        <v>13359.01456927683</v>
+        <v>13401.06231045049</v>
       </c>
       <c r="E29">
-        <v>3445.884</v>
+        <v>3578.976000000001</v>
       </c>
       <c r="F29">
-        <v>3593.484</v>
+        <v>3726.576</v>
       </c>
       <c r="G29">
         <v>948.5</v>
@@ -4742,28 +4742,28 @@
         <v>981.6</v>
       </c>
       <c r="M29">
-        <v>195.1261812</v>
+        <v>202.3530768</v>
       </c>
       <c r="N29">
-        <v>786.4738188</v>
+        <v>779.2469232</v>
       </c>
       <c r="O29">
-        <v>173.024240136</v>
+        <v>171.434323104</v>
       </c>
       <c r="P29">
-        <v>613.449578664</v>
+        <v>607.812600096</v>
       </c>
       <c r="Q29">
-        <v>657.1495786639999</v>
+        <v>651.5126000959999</v>
       </c>
       <c r="R29">
-        <v>0.3698630136986302</v>
+        <v>0.388888888888889</v>
       </c>
       <c r="S29">
-        <v>0.1099090863338612</v>
+        <v>0.1106474608840952</v>
       </c>
       <c r="T29">
-        <v>1.48057936105915</v>
+        <v>1.49763189108765</v>
       </c>
       <c r="U29">
         <v>0.0543</v>
@@ -4780,7 +4780,7 @@
         </is>
       </c>
       <c r="Y29">
-        <v>5.03059094357964</v>
+        <v>4.850926981308939</v>
       </c>
       <c r="Z29">
         <v>0</v>
@@ -4788,22 +4788,22 @@
     </row>
     <row r="30">
       <c r="A30">
-        <v>0.28</v>
+        <v>0.29</v>
       </c>
       <c r="B30">
-        <v>0.09152529183654858</v>
+        <v>0.0913813706493785</v>
       </c>
       <c r="C30">
-        <v>10622.98631045049</v>
+        <v>10532.20757943698</v>
       </c>
       <c r="D30">
-        <v>13401.06231045049</v>
+        <v>13443.37557943698</v>
       </c>
       <c r="E30">
-        <v>3578.976000000001</v>
+        <v>3712.068000000001</v>
       </c>
       <c r="F30">
-        <v>3726.576</v>
+        <v>3859.668000000001</v>
       </c>
       <c r="G30">
         <v>948.5</v>
@@ -4824,28 +4824,28 @@
         <v>981.6</v>
       </c>
       <c r="M30">
-        <v>202.3530768</v>
+        <v>209.5799724</v>
       </c>
       <c r="N30">
-        <v>779.2469232</v>
+        <v>772.0200276</v>
       </c>
       <c r="O30">
-        <v>171.434323104</v>
+        <v>169.844406072</v>
       </c>
       <c r="P30">
-        <v>607.812600096</v>
+        <v>602.1756215280001</v>
       </c>
       <c r="Q30">
-        <v>651.5126000959999</v>
+        <v>645.875621528</v>
       </c>
       <c r="R30">
-        <v>0.388888888888889</v>
+        <v>0.4084507042253522</v>
       </c>
       <c r="S30">
-        <v>0.1106474608840952</v>
+        <v>0.1114066347174345</v>
       </c>
       <c r="T30">
-        <v>1.49763189108765</v>
+        <v>1.5151647740747</v>
       </c>
       <c r="U30">
         <v>0.0543</v>
@@ -4862,7 +4862,7 @@
         </is>
       </c>
       <c r="Y30">
-        <v>4.850926981308939</v>
+        <v>4.683653637125872</v>
       </c>
       <c r="Z30">
         <v>0</v>
@@ -4870,22 +4870,22 @@
     </row>
     <row r="31">
       <c r="A31">
-        <v>0.29</v>
+        <v>0.3</v>
       </c>
       <c r="B31">
-        <v>0.0913813706493785</v>
+        <v>0.09123744946220841</v>
       </c>
       <c r="C31">
-        <v>10532.20757943698</v>
+        <v>10441.69689938046</v>
       </c>
       <c r="D31">
-        <v>13443.37557943698</v>
+        <v>13485.95689938046</v>
       </c>
       <c r="E31">
-        <v>3712.068</v>
+        <v>3845.16</v>
       </c>
       <c r="F31">
-        <v>3859.668</v>
+        <v>3992.76</v>
       </c>
       <c r="G31">
         <v>948.5</v>
@@ -4906,28 +4906,28 @@
         <v>981.6</v>
       </c>
       <c r="M31">
-        <v>209.5799724</v>
+        <v>216.806868</v>
       </c>
       <c r="N31">
-        <v>772.0200276</v>
+        <v>764.793132</v>
       </c>
       <c r="O31">
-        <v>169.844406072</v>
+        <v>168.25448904</v>
       </c>
       <c r="P31">
-        <v>602.1756215280001</v>
+        <v>596.5386429600001</v>
       </c>
       <c r="Q31">
-        <v>645.875621528</v>
+        <v>640.23864296</v>
       </c>
       <c r="R31">
-        <v>0.4084507042253521</v>
+        <v>0.4285714285714286</v>
       </c>
       <c r="S31">
-        <v>0.1114066347174345</v>
+        <v>0.1121874992317263</v>
       </c>
       <c r="T31">
-        <v>1.5151647740747</v>
+        <v>1.533198596575665</v>
       </c>
       <c r="U31">
         <v>0.0543</v>
@@ -4944,7 +4944,7 @@
         </is>
       </c>
       <c r="Y31">
-        <v>4.683653637125873</v>
+        <v>4.527531849221677</v>
       </c>
       <c r="Z31">
         <v>0</v>
@@ -4952,22 +4952,22 @@
     </row>
     <row r="32">
       <c r="A32">
-        <v>0.3</v>
+        <v>0.31</v>
       </c>
       <c r="B32">
-        <v>0.09123744946220841</v>
+        <v>0.09109352827503833</v>
       </c>
       <c r="C32">
-        <v>10441.69689938046</v>
+        <v>10351.45682549444</v>
       </c>
       <c r="D32">
-        <v>13485.95689938046</v>
+        <v>13528.80882549444</v>
       </c>
       <c r="E32">
-        <v>3845.16</v>
+        <v>3978.252</v>
       </c>
       <c r="F32">
-        <v>3992.76</v>
+        <v>4125.852</v>
       </c>
       <c r="G32">
         <v>948.5</v>
@@ -4988,28 +4988,28 @@
         <v>981.6</v>
       </c>
       <c r="M32">
-        <v>216.806868</v>
+        <v>224.0337636</v>
       </c>
       <c r="N32">
-        <v>764.793132</v>
+        <v>757.5662364</v>
       </c>
       <c r="O32">
-        <v>168.25448904</v>
+        <v>166.664572008</v>
       </c>
       <c r="P32">
-        <v>596.5386429600001</v>
+        <v>590.9016643919999</v>
       </c>
       <c r="Q32">
-        <v>640.23864296</v>
+        <v>634.6016643919999</v>
       </c>
       <c r="R32">
-        <v>0.4285714285714286</v>
+        <v>0.4492753623188406</v>
       </c>
       <c r="S32">
-        <v>0.1121874992317263</v>
+        <v>0.1129909975000556</v>
       </c>
       <c r="T32">
-        <v>1.533198596575665</v>
+        <v>1.551755138569412</v>
       </c>
       <c r="U32">
         <v>0.0543</v>
@@ -5026,7 +5026,7 @@
         </is>
       </c>
       <c r="Y32">
-        <v>4.527531849221677</v>
+        <v>4.381482434730655</v>
       </c>
       <c r="Z32">
         <v>0</v>
@@ -5034,22 +5034,22 @@
     </row>
     <row r="33">
       <c r="A33">
-        <v>0.31</v>
+        <v>0.32</v>
       </c>
       <c r="B33">
-        <v>0.09109352827503833</v>
+        <v>0.09119920708786824</v>
       </c>
       <c r="C33">
-        <v>10351.45682549444</v>
+        <v>10186.87289981138</v>
       </c>
       <c r="D33">
-        <v>13528.80882549444</v>
+        <v>13497.31689981138</v>
       </c>
       <c r="E33">
-        <v>3978.252</v>
+        <v>4111.344</v>
       </c>
       <c r="F33">
-        <v>4125.852</v>
+        <v>4258.944</v>
       </c>
       <c r="G33">
         <v>948.5</v>
@@ -5070,45 +5070,45 @@
         <v>981.6</v>
       </c>
       <c r="M33">
-        <v>224.0337636</v>
+        <v>235.5196032</v>
       </c>
       <c r="N33">
-        <v>757.5662364</v>
+        <v>746.0803968</v>
       </c>
       <c r="O33">
-        <v>166.664572008</v>
+        <v>164.137687296</v>
       </c>
       <c r="P33">
-        <v>590.9016643919999</v>
+        <v>581.942709504</v>
       </c>
       <c r="Q33">
-        <v>634.6016643919999</v>
+        <v>625.642709504</v>
       </c>
       <c r="R33">
-        <v>0.4492753623188406</v>
+        <v>0.4705882352941177</v>
       </c>
       <c r="S33">
-        <v>0.1129909975000556</v>
+        <v>0.1138181280703945</v>
       </c>
       <c r="T33">
-        <v>1.551755138569412</v>
+        <v>1.570857461210034</v>
       </c>
       <c r="U33">
-        <v>0.0543</v>
+        <v>0.0553</v>
       </c>
       <c r="V33">
         <v>0.22</v>
       </c>
       <c r="W33">
-        <v>0.042354</v>
+        <v>0.04313400000000001</v>
       </c>
       <c r="X33" t="inlineStr">
         <is>
-          <t>A2/A</t>
+          <t>A3/A-</t>
         </is>
       </c>
       <c r="Y33">
-        <v>4.381482434730655</v>
+        <v>4.167805934890433</v>
       </c>
       <c r="Z33">
         <v>0</v>
@@ -5116,22 +5116,22 @@
     </row>
     <row r="34">
       <c r="A34">
-        <v>0.32</v>
+        <v>0.33</v>
       </c>
       <c r="B34">
-        <v>0.09119920708786824</v>
+        <v>0.09106308590069816</v>
       </c>
       <c r="C34">
-        <v>10186.87289981138</v>
+        <v>10094.37183088585</v>
       </c>
       <c r="D34">
-        <v>13497.31689981138</v>
+        <v>13537.90783088585</v>
       </c>
       <c r="E34">
-        <v>4111.344</v>
+        <v>4244.436</v>
       </c>
       <c r="F34">
-        <v>4258.944</v>
+        <v>4392.036</v>
       </c>
       <c r="G34">
         <v>948.5</v>
@@ -5152,28 +5152,28 @@
         <v>981.6</v>
       </c>
       <c r="M34">
-        <v>235.5196032</v>
+        <v>242.8795908</v>
       </c>
       <c r="N34">
-        <v>746.0803968</v>
+        <v>738.7204091999999</v>
       </c>
       <c r="O34">
-        <v>164.137687296</v>
+        <v>162.518490024</v>
       </c>
       <c r="P34">
-        <v>581.942709504</v>
+        <v>576.2019191759999</v>
       </c>
       <c r="Q34">
-        <v>625.642709504</v>
+        <v>619.9019191759999</v>
       </c>
       <c r="R34">
-        <v>0.4705882352941177</v>
+        <v>0.4925373134328359</v>
       </c>
       <c r="S34">
-        <v>0.1138181280703945</v>
+        <v>0.1146699491055196</v>
       </c>
       <c r="T34">
-        <v>1.570857461210034</v>
+        <v>1.590530002436943</v>
       </c>
       <c r="U34">
         <v>0.0553</v>
@@ -5190,7 +5190,7 @@
         </is>
       </c>
       <c r="Y34">
-        <v>4.167805934890433</v>
+        <v>4.041508785348299</v>
       </c>
       <c r="Z34">
         <v>0</v>
@@ -5198,22 +5198,22 @@
     </row>
     <row r="35">
       <c r="A35">
-        <v>0.33</v>
+        <v>0.34</v>
       </c>
       <c r="B35">
-        <v>0.09106308590069816</v>
+        <v>0.09092696471352807</v>
       </c>
       <c r="C35">
-        <v>10094.37183088585</v>
+        <v>10002.11563930855</v>
       </c>
       <c r="D35">
-        <v>13537.90783088585</v>
+        <v>13578.74363930855</v>
       </c>
       <c r="E35">
-        <v>4244.436</v>
+        <v>4377.528</v>
       </c>
       <c r="F35">
-        <v>4392.036</v>
+        <v>4525.128000000001</v>
       </c>
       <c r="G35">
         <v>948.5</v>
@@ -5234,28 +5234,28 @@
         <v>981.6</v>
       </c>
       <c r="M35">
-        <v>242.8795908</v>
+        <v>250.2395784000001</v>
       </c>
       <c r="N35">
-        <v>738.7204091999999</v>
+        <v>731.3604216</v>
       </c>
       <c r="O35">
-        <v>162.518490024</v>
+        <v>160.899292752</v>
       </c>
       <c r="P35">
-        <v>576.2019191759999</v>
+        <v>570.461128848</v>
       </c>
       <c r="Q35">
-        <v>619.9019191759999</v>
+        <v>614.161128848</v>
       </c>
       <c r="R35">
-        <v>0.4925373134328359</v>
+        <v>0.5151515151515152</v>
       </c>
       <c r="S35">
-        <v>0.1146699491055196</v>
+        <v>0.115547582899285</v>
       </c>
       <c r="T35">
-        <v>1.590530002436943</v>
+        <v>1.610798681276789</v>
       </c>
       <c r="U35">
         <v>0.0553</v>
@@ -5272,7 +5272,7 @@
         </is>
       </c>
       <c r="Y35">
-        <v>4.041508785348299</v>
+        <v>3.922640879896878</v>
       </c>
       <c r="Z35">
         <v>0</v>
@@ -5280,22 +5280,22 @@
     </row>
     <row r="36">
       <c r="A36">
-        <v>0.34</v>
+        <v>0.35</v>
       </c>
       <c r="B36">
-        <v>0.09092696471352807</v>
+        <v>0.09079084352635799</v>
       </c>
       <c r="C36">
-        <v>10002.11563930855</v>
+        <v>9910.106547731411</v>
       </c>
       <c r="D36">
-        <v>13578.74363930855</v>
+        <v>13619.82654773141</v>
       </c>
       <c r="E36">
-        <v>4377.528</v>
+        <v>4510.62</v>
       </c>
       <c r="F36">
-        <v>4525.128000000001</v>
+        <v>4658.22</v>
       </c>
       <c r="G36">
         <v>948.5</v>
@@ -5316,28 +5316,28 @@
         <v>981.6</v>
       </c>
       <c r="M36">
-        <v>250.2395784000001</v>
+        <v>257.599566</v>
       </c>
       <c r="N36">
-        <v>731.3604216</v>
+        <v>724.000434</v>
       </c>
       <c r="O36">
-        <v>160.899292752</v>
+        <v>159.28009548</v>
       </c>
       <c r="P36">
-        <v>570.461128848</v>
+        <v>564.72033852</v>
       </c>
       <c r="Q36">
-        <v>614.161128848</v>
+        <v>608.42033852</v>
       </c>
       <c r="R36">
-        <v>0.5151515151515152</v>
+        <v>0.5384615384615385</v>
       </c>
       <c r="S36">
-        <v>0.115547582899285</v>
+        <v>0.1164522208097815</v>
       </c>
       <c r="T36">
-        <v>1.610798681276789</v>
+        <v>1.631691011773245</v>
       </c>
       <c r="U36">
         <v>0.0553</v>
@@ -5354,7 +5354,7 @@
         </is>
       </c>
       <c r="Y36">
-        <v>3.922640879896878</v>
+        <v>3.810565426185539</v>
       </c>
       <c r="Z36">
         <v>0</v>
@@ -5362,22 +5362,22 @@
     </row>
     <row r="37">
       <c r="A37">
-        <v>0.35</v>
+        <v>0.36</v>
       </c>
       <c r="B37">
-        <v>0.09079084352635799</v>
+        <v>0.09065472233918789</v>
       </c>
       <c r="C37">
-        <v>9910.106547731411</v>
+        <v>9818.346805786841</v>
       </c>
       <c r="D37">
-        <v>13619.82654773141</v>
+        <v>13661.15880578684</v>
       </c>
       <c r="E37">
-        <v>4510.62</v>
+        <v>4643.712</v>
       </c>
       <c r="F37">
-        <v>4658.22</v>
+        <v>4791.312000000001</v>
       </c>
       <c r="G37">
         <v>948.5</v>
@@ -5398,28 +5398,28 @@
         <v>981.6</v>
       </c>
       <c r="M37">
-        <v>257.599566</v>
+        <v>264.9595536</v>
       </c>
       <c r="N37">
-        <v>724.000434</v>
+        <v>716.6404464</v>
       </c>
       <c r="O37">
-        <v>159.28009548</v>
+        <v>157.660898208</v>
       </c>
       <c r="P37">
-        <v>564.72033852</v>
+        <v>558.979548192</v>
       </c>
       <c r="Q37">
-        <v>608.42033852</v>
+        <v>602.679548192</v>
       </c>
       <c r="R37">
-        <v>0.5384615384615385</v>
+        <v>0.5625000000000001</v>
       </c>
       <c r="S37">
-        <v>0.1164522208097815</v>
+        <v>0.1173851286549811</v>
       </c>
       <c r="T37">
-        <v>1.631691011773245</v>
+        <v>1.653236227597716</v>
       </c>
       <c r="U37">
         <v>0.0553</v>
@@ -5436,7 +5436,7 @@
         </is>
       </c>
       <c r="Y37">
-        <v>3.810565426185539</v>
+        <v>3.704716386569274</v>
       </c>
       <c r="Z37">
         <v>0</v>
@@ -5444,22 +5444,22 @@
     </row>
     <row r="38">
       <c r="A38">
-        <v>0.36</v>
+        <v>0.37</v>
       </c>
       <c r="B38">
-        <v>0.09065472233918791</v>
+        <v>0.09051860115201782</v>
       </c>
       <c r="C38">
-        <v>9818.346805786836</v>
+        <v>9726.838690498285</v>
       </c>
       <c r="D38">
-        <v>13661.15880578684</v>
+        <v>13702.74269049829</v>
       </c>
       <c r="E38">
-        <v>4643.712</v>
+        <v>4776.804</v>
       </c>
       <c r="F38">
-        <v>4791.312</v>
+        <v>4924.404</v>
       </c>
       <c r="G38">
         <v>948.5</v>
@@ -5480,28 +5480,28 @@
         <v>981.6</v>
       </c>
       <c r="M38">
-        <v>264.9595536</v>
+        <v>272.3195412000001</v>
       </c>
       <c r="N38">
-        <v>716.6404464</v>
+        <v>709.2804587999999</v>
       </c>
       <c r="O38">
-        <v>157.660898208</v>
+        <v>156.041700936</v>
       </c>
       <c r="P38">
-        <v>558.979548192</v>
+        <v>553.2387578639999</v>
       </c>
       <c r="Q38">
-        <v>602.679548192</v>
+        <v>596.9387578639999</v>
       </c>
       <c r="R38">
-        <v>0.5625</v>
+        <v>0.5873015873015873</v>
       </c>
       <c r="S38">
-        <v>0.1173851286549811</v>
+        <v>0.1183476526222505</v>
       </c>
       <c r="T38">
-        <v>1.653236227597716</v>
+        <v>1.675465418527725</v>
       </c>
       <c r="U38">
         <v>0.0553</v>
@@ -5518,7 +5518,7 @@
         </is>
       </c>
       <c r="Y38">
-        <v>3.704716386569274</v>
+        <v>3.604588916661996</v>
       </c>
       <c r="Z38">
         <v>0</v>
@@ -5526,22 +5526,22 @@
     </row>
     <row r="39">
       <c r="A39">
-        <v>0.37</v>
+        <v>0.38</v>
       </c>
       <c r="B39">
-        <v>0.09051860115201782</v>
+        <v>0.09038247996484775</v>
       </c>
       <c r="C39">
-        <v>9726.838690498285</v>
+        <v>9635.584506698448</v>
       </c>
       <c r="D39">
-        <v>13702.74269049829</v>
+        <v>13744.58050669845</v>
       </c>
       <c r="E39">
-        <v>4776.804</v>
+        <v>4909.896</v>
       </c>
       <c r="F39">
-        <v>4924.404</v>
+        <v>5057.496</v>
       </c>
       <c r="G39">
         <v>948.5</v>
@@ -5562,28 +5562,28 @@
         <v>981.6</v>
       </c>
       <c r="M39">
-        <v>272.3195412000001</v>
+        <v>279.6795288</v>
       </c>
       <c r="N39">
-        <v>709.2804587999999</v>
+        <v>701.9204712000001</v>
       </c>
       <c r="O39">
-        <v>156.041700936</v>
+        <v>154.422503664</v>
       </c>
       <c r="P39">
-        <v>553.2387578639999</v>
+        <v>547.497967536</v>
       </c>
       <c r="Q39">
-        <v>596.9387578639999</v>
+        <v>591.197967536</v>
       </c>
       <c r="R39">
-        <v>0.5873015873015873</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="S39">
-        <v>0.1183476526222505</v>
+        <v>0.1193412257497544</v>
       </c>
       <c r="T39">
-        <v>1.675465418527725</v>
+        <v>1.698411680132896</v>
       </c>
       <c r="U39">
         <v>0.0553</v>
@@ -5600,7 +5600,7 @@
         </is>
       </c>
       <c r="Y39">
-        <v>3.604588916661996</v>
+        <v>3.509731313591944</v>
       </c>
       <c r="Z39">
         <v>0</v>
@@ -5608,22 +5608,22 @@
     </row>
     <row r="40">
       <c r="A40">
-        <v>0.38</v>
+        <v>0.39</v>
       </c>
       <c r="B40">
-        <v>0.09038247996484775</v>
+        <v>0.09024635877767766</v>
       </c>
       <c r="C40">
-        <v>9635.584506698448</v>
+        <v>9544.586587455098</v>
       </c>
       <c r="D40">
-        <v>13744.58050669845</v>
+        <v>13786.6745874551</v>
       </c>
       <c r="E40">
-        <v>4909.896</v>
+        <v>5042.988</v>
       </c>
       <c r="F40">
-        <v>5057.496</v>
+        <v>5190.588000000001</v>
       </c>
       <c r="G40">
         <v>948.5</v>
@@ -5644,28 +5644,28 @@
         <v>981.6</v>
       </c>
       <c r="M40">
-        <v>279.6795288</v>
+        <v>287.0395164</v>
       </c>
       <c r="N40">
-        <v>701.9204712000001</v>
+        <v>694.5604836</v>
       </c>
       <c r="O40">
-        <v>154.422503664</v>
+        <v>152.803306392</v>
       </c>
       <c r="P40">
-        <v>547.497967536</v>
+        <v>541.757177208</v>
       </c>
       <c r="Q40">
-        <v>591.197967536</v>
+        <v>585.457177208</v>
       </c>
       <c r="R40">
-        <v>0.6129032258064516</v>
+        <v>0.639344262295082</v>
       </c>
       <c r="S40">
-        <v>0.1193412257497544</v>
+        <v>0.1203673750453732</v>
       </c>
       <c r="T40">
-        <v>1.698411680132896</v>
+        <v>1.722110278184138</v>
       </c>
       <c r="U40">
         <v>0.0553</v>
@@ -5682,7 +5682,7 @@
         </is>
       </c>
       <c r="Y40">
-        <v>3.509731313591944</v>
+        <v>3.419738202987022</v>
       </c>
       <c r="Z40">
         <v>0</v>
@@ -5690,22 +5690,22 @@
     </row>
     <row r="41">
       <c r="A41">
-        <v>0.39</v>
+        <v>0.4</v>
       </c>
       <c r="B41">
-        <v>0.09024635877767766</v>
+        <v>0.09011023759050757</v>
       </c>
       <c r="C41">
-        <v>9544.586587455098</v>
+        <v>9453.847294504771</v>
       </c>
       <c r="D41">
-        <v>13786.6745874551</v>
+        <v>13829.02729450477</v>
       </c>
       <c r="E41">
-        <v>5042.988</v>
+        <v>5176.08</v>
       </c>
       <c r="F41">
-        <v>5190.588000000001</v>
+        <v>5323.68</v>
       </c>
       <c r="G41">
         <v>948.5</v>
@@ -5726,28 +5726,28 @@
         <v>981.6</v>
       </c>
       <c r="M41">
-        <v>287.0395164</v>
+        <v>294.399504</v>
       </c>
       <c r="N41">
-        <v>694.5604836</v>
+        <v>687.2004959999999</v>
       </c>
       <c r="O41">
-        <v>152.803306392</v>
+        <v>151.18410912</v>
       </c>
       <c r="P41">
-        <v>541.757177208</v>
+        <v>536.0163868799999</v>
       </c>
       <c r="Q41">
-        <v>585.457177208</v>
+        <v>579.7163868799998</v>
       </c>
       <c r="R41">
-        <v>0.639344262295082</v>
+        <v>0.6666666666666667</v>
       </c>
       <c r="S41">
-        <v>0.1203673750453732</v>
+        <v>0.1214277293175126</v>
       </c>
       <c r="T41">
-        <v>1.722110278184138</v>
+        <v>1.746598829503755</v>
       </c>
       <c r="U41">
         <v>0.0553</v>
@@ -5764,7 +5764,7 @@
         </is>
       </c>
       <c r="Y41">
-        <v>3.419738202987022</v>
+        <v>3.334244747912347</v>
       </c>
       <c r="Z41">
         <v>0</v>
@@ -5772,22 +5772,22 @@
     </row>
     <row r="42">
       <c r="A42">
-        <v>0.4</v>
+        <v>0.41</v>
       </c>
       <c r="B42">
-        <v>0.09011023759050757</v>
+        <v>0.0899741164033375</v>
       </c>
       <c r="C42">
-        <v>9453.847294504771</v>
+        <v>9363.369018694464</v>
       </c>
       <c r="D42">
-        <v>13829.02729450477</v>
+        <v>13871.64101869446</v>
       </c>
       <c r="E42">
-        <v>5176.08</v>
+        <v>5309.172</v>
       </c>
       <c r="F42">
-        <v>5323.68</v>
+        <v>5456.772000000001</v>
       </c>
       <c r="G42">
         <v>948.5</v>
@@ -5808,28 +5808,28 @@
         <v>981.6</v>
       </c>
       <c r="M42">
-        <v>294.399504</v>
+        <v>301.7594916</v>
       </c>
       <c r="N42">
-        <v>687.2004959999999</v>
+        <v>679.8405084</v>
       </c>
       <c r="O42">
-        <v>151.18410912</v>
+        <v>149.564911848</v>
       </c>
       <c r="P42">
-        <v>536.0163868799999</v>
+        <v>530.275596552</v>
       </c>
       <c r="Q42">
-        <v>579.7163868799998</v>
+        <v>573.975596552</v>
       </c>
       <c r="R42">
-        <v>0.6666666666666667</v>
+        <v>0.6949152542372882</v>
       </c>
       <c r="S42">
-        <v>0.1214277293175126</v>
+        <v>0.1225240278022669</v>
       </c>
       <c r="T42">
-        <v>1.746598829503755</v>
+        <v>1.771917501207088</v>
       </c>
       <c r="U42">
         <v>0.0553</v>
@@ -5846,7 +5846,7 @@
         </is>
       </c>
       <c r="Y42">
-        <v>3.334244747912347</v>
+        <v>3.252921705280338</v>
       </c>
       <c r="Z42">
         <v>0</v>
@@ -5854,22 +5854,22 @@
     </row>
     <row r="43">
       <c r="A43">
-        <v>0.41</v>
+        <v>0.42</v>
       </c>
       <c r="B43">
-        <v>0.0899741164033375</v>
+        <v>0.08983799521616739</v>
       </c>
       <c r="C43">
-        <v>9363.369018694464</v>
+        <v>9273.154180431586</v>
       </c>
       <c r="D43">
-        <v>13871.64101869446</v>
+        <v>13914.51818043159</v>
       </c>
       <c r="E43">
-        <v>5309.172</v>
+        <v>5442.264</v>
       </c>
       <c r="F43">
-        <v>5456.772000000001</v>
+        <v>5589.864</v>
       </c>
       <c r="G43">
         <v>948.5</v>
@@ -5890,28 +5890,28 @@
         <v>981.6</v>
       </c>
       <c r="M43">
-        <v>301.7594916</v>
+        <v>309.1194792000001</v>
       </c>
       <c r="N43">
-        <v>679.8405084</v>
+        <v>672.4805208</v>
       </c>
       <c r="O43">
-        <v>149.564911848</v>
+        <v>147.945714576</v>
       </c>
       <c r="P43">
-        <v>530.275596552</v>
+        <v>524.534806224</v>
       </c>
       <c r="Q43">
-        <v>573.975596552</v>
+        <v>568.234806224</v>
       </c>
       <c r="R43">
-        <v>0.6949152542372882</v>
+        <v>0.7241379310344829</v>
       </c>
       <c r="S43">
-        <v>0.1225240278022669</v>
+        <v>0.1236581296830472</v>
       </c>
       <c r="T43">
-        <v>1.771917501207088</v>
+        <v>1.798109230555363</v>
       </c>
       <c r="U43">
         <v>0.0553</v>
@@ -5928,7 +5928,7 @@
         </is>
       </c>
       <c r="Y43">
-        <v>3.252921705280338</v>
+        <v>3.175471188487949</v>
       </c>
       <c r="Z43">
         <v>0</v>
@@ -5936,22 +5936,22 @@
     </row>
     <row r="44">
       <c r="A44">
-        <v>0.42</v>
+        <v>0.43</v>
       </c>
       <c r="B44">
-        <v>0.08983799521616741</v>
+        <v>0.08970187402899732</v>
       </c>
       <c r="C44">
-        <v>9273.154180431582</v>
+        <v>9183.20523014215</v>
       </c>
       <c r="D44">
-        <v>13914.51818043158</v>
+        <v>13957.66123014215</v>
       </c>
       <c r="E44">
-        <v>5442.264</v>
+        <v>5575.356</v>
       </c>
       <c r="F44">
-        <v>5589.864</v>
+        <v>5722.956</v>
       </c>
       <c r="G44">
         <v>948.5</v>
@@ -5972,28 +5972,28 @@
         <v>981.6</v>
       </c>
       <c r="M44">
-        <v>309.1194792000001</v>
+        <v>316.4794668</v>
       </c>
       <c r="N44">
-        <v>672.4805208</v>
+        <v>665.1205332</v>
       </c>
       <c r="O44">
-        <v>147.945714576</v>
+        <v>146.326517304</v>
       </c>
       <c r="P44">
-        <v>524.534806224</v>
+        <v>518.794015896</v>
       </c>
       <c r="Q44">
-        <v>568.234806224</v>
+        <v>562.494015896</v>
       </c>
       <c r="R44">
-        <v>0.7241379310344827</v>
+        <v>0.7543859649122806</v>
       </c>
       <c r="S44">
-        <v>0.1236581296830472</v>
+        <v>0.124832024612276</v>
       </c>
       <c r="T44">
-        <v>1.798109230555363</v>
+        <v>1.825219967950947</v>
       </c>
       <c r="U44">
         <v>0.0553</v>
@@ -6010,7 +6010,7 @@
         </is>
       </c>
       <c r="Y44">
-        <v>3.175471188487949</v>
+        <v>3.101623021313811</v>
       </c>
       <c r="Z44">
         <v>0</v>
@@ -6018,22 +6018,22 @@
     </row>
     <row r="45">
       <c r="A45">
-        <v>0.43</v>
+        <v>0.44</v>
       </c>
       <c r="B45">
-        <v>0.08970187402899732</v>
+        <v>0.08956575284182725</v>
       </c>
       <c r="C45">
-        <v>9183.20523014215</v>
+        <v>9093.52464873767</v>
       </c>
       <c r="D45">
-        <v>13957.66123014215</v>
+        <v>14001.07264873767</v>
       </c>
       <c r="E45">
-        <v>5575.356</v>
+        <v>5708.448</v>
       </c>
       <c r="F45">
-        <v>5722.956</v>
+        <v>5856.048000000001</v>
       </c>
       <c r="G45">
         <v>948.5</v>
@@ -6054,28 +6054,28 @@
         <v>981.6</v>
       </c>
       <c r="M45">
-        <v>316.4794668</v>
+        <v>323.8394544</v>
       </c>
       <c r="N45">
-        <v>665.1205332</v>
+        <v>657.7605456</v>
       </c>
       <c r="O45">
-        <v>146.326517304</v>
+        <v>144.707320032</v>
       </c>
       <c r="P45">
-        <v>518.794015896</v>
+        <v>513.053225568</v>
       </c>
       <c r="Q45">
-        <v>562.494015896</v>
+        <v>556.7532255679999</v>
       </c>
       <c r="R45">
-        <v>0.7543859649122806</v>
+        <v>0.7857142857142857</v>
       </c>
       <c r="S45">
-        <v>0.124832024612276</v>
+        <v>0.1260478443604058</v>
       </c>
       <c r="T45">
-        <v>1.825219967950947</v>
+        <v>1.853298945967801</v>
       </c>
       <c r="U45">
         <v>0.0553</v>
@@ -6092,7 +6092,7 @@
         </is>
       </c>
       <c r="Y45">
-        <v>3.101623021313811</v>
+        <v>3.031131589011224</v>
       </c>
       <c r="Z45">
         <v>0</v>
@@ -6100,22 +6100,22 @@
     </row>
     <row r="46">
       <c r="A46">
-        <v>0.44</v>
+        <v>0.45</v>
       </c>
       <c r="B46">
-        <v>0.08956575284182725</v>
+        <v>0.09030713165465715</v>
       </c>
       <c r="C46">
-        <v>9093.52464873767</v>
+        <v>8727.209382425917</v>
       </c>
       <c r="D46">
-        <v>14001.07264873767</v>
+        <v>13767.84938242592</v>
       </c>
       <c r="E46">
-        <v>5708.448</v>
+        <v>5841.54</v>
       </c>
       <c r="F46">
-        <v>5856.048000000001</v>
+        <v>5989.14</v>
       </c>
       <c r="G46">
         <v>948.5</v>
@@ -6136,45 +6136,45 @@
         <v>981.6</v>
       </c>
       <c r="M46">
-        <v>323.8394544</v>
+        <v>346.172292</v>
       </c>
       <c r="N46">
-        <v>657.7605456</v>
+        <v>635.4277079999999</v>
       </c>
       <c r="O46">
-        <v>144.707320032</v>
+        <v>139.79409576</v>
       </c>
       <c r="P46">
-        <v>513.053225568</v>
+        <v>495.6336122399999</v>
       </c>
       <c r="Q46">
-        <v>556.7532255679999</v>
+        <v>539.3336122399999</v>
       </c>
       <c r="R46">
-        <v>0.7857142857142857</v>
+        <v>0.8181818181818181</v>
       </c>
       <c r="S46">
-        <v>0.1260478443604058</v>
+        <v>0.1273078757357403</v>
       </c>
       <c r="T46">
-        <v>1.853298945967801</v>
+        <v>1.882398977730722</v>
       </c>
       <c r="U46">
-        <v>0.0553</v>
+        <v>0.0578</v>
       </c>
       <c r="V46">
         <v>0.22</v>
       </c>
       <c r="W46">
-        <v>0.04313400000000001</v>
+        <v>0.04508400000000001</v>
       </c>
       <c r="X46" t="inlineStr">
         <is>
-          <t>A3/A-</t>
+          <t>Baa2/BBB</t>
         </is>
       </c>
       <c r="Y46">
-        <v>3.031131589011224</v>
+        <v>2.835582230827417</v>
       </c>
       <c r="Z46">
         <v>0</v>
@@ -6182,22 +6182,22 @@
     </row>
     <row r="47">
       <c r="A47">
-        <v>0.45</v>
+        <v>0.46</v>
       </c>
       <c r="B47">
-        <v>0.09030713165465715</v>
+        <v>0.09019051046748708</v>
       </c>
       <c r="C47">
-        <v>8727.209382425917</v>
+        <v>8630.287791886138</v>
       </c>
       <c r="D47">
-        <v>13767.84938242592</v>
+        <v>13804.01979188614</v>
       </c>
       <c r="E47">
-        <v>5841.54</v>
+        <v>5974.632000000001</v>
       </c>
       <c r="F47">
-        <v>5989.14</v>
+        <v>6122.232000000001</v>
       </c>
       <c r="G47">
         <v>948.5</v>
@@ -6218,28 +6218,28 @@
         <v>981.6</v>
       </c>
       <c r="M47">
-        <v>346.172292</v>
+        <v>353.8650096000001</v>
       </c>
       <c r="N47">
-        <v>635.4277079999999</v>
+        <v>627.7349904</v>
       </c>
       <c r="O47">
-        <v>139.79409576</v>
+        <v>138.101697888</v>
       </c>
       <c r="P47">
-        <v>495.6336122399999</v>
+        <v>489.633292512</v>
       </c>
       <c r="Q47">
-        <v>539.3336122399999</v>
+        <v>533.333292512</v>
       </c>
       <c r="R47">
-        <v>0.8181818181818181</v>
+        <v>0.8518518518518519</v>
       </c>
       <c r="S47">
-        <v>0.1273078757357403</v>
+        <v>0.1286145749397909</v>
       </c>
       <c r="T47">
-        <v>1.882398977730722</v>
+        <v>1.912576788447826</v>
       </c>
       <c r="U47">
         <v>0.0578</v>
@@ -6256,7 +6256,7 @@
         </is>
       </c>
       <c r="Y47">
-        <v>2.835582230827417</v>
+        <v>2.773939138852907</v>
       </c>
       <c r="Z47">
         <v>0</v>
@@ -6264,22 +6264,22 @@
     </row>
     <row r="48">
       <c r="A48">
-        <v>0.46</v>
+        <v>0.47</v>
       </c>
       <c r="B48">
-        <v>0.09019051046748708</v>
+        <v>0.09007388928031698</v>
       </c>
       <c r="C48">
-        <v>8630.287791886138</v>
+        <v>8533.556753211598</v>
       </c>
       <c r="D48">
-        <v>13804.01979188614</v>
+        <v>13840.3807532116</v>
       </c>
       <c r="E48">
-        <v>5974.632000000001</v>
+        <v>6107.724</v>
       </c>
       <c r="F48">
-        <v>6122.232000000001</v>
+        <v>6255.324000000001</v>
       </c>
       <c r="G48">
         <v>948.5</v>
@@ -6300,28 +6300,28 @@
         <v>981.6</v>
       </c>
       <c r="M48">
-        <v>353.8650096000001</v>
+        <v>361.5577272</v>
       </c>
       <c r="N48">
-        <v>627.7349904</v>
+        <v>620.0422728</v>
       </c>
       <c r="O48">
-        <v>138.101697888</v>
+        <v>136.409300016</v>
       </c>
       <c r="P48">
-        <v>489.633292512</v>
+        <v>483.632972784</v>
       </c>
       <c r="Q48">
-        <v>533.333292512</v>
+        <v>527.3329727839999</v>
       </c>
       <c r="R48">
-        <v>0.8518518518518519</v>
+        <v>0.8867924528301887</v>
       </c>
       <c r="S48">
-        <v>0.1286145749397909</v>
+        <v>0.1299705835477679</v>
       </c>
       <c r="T48">
-        <v>1.912576788447826</v>
+        <v>1.943893384475009</v>
       </c>
       <c r="U48">
         <v>0.0578</v>
@@ -6338,7 +6338,7 @@
         </is>
       </c>
       <c r="Y48">
-        <v>2.773939138852907</v>
+        <v>2.714919157175186</v>
       </c>
       <c r="Z48">
         <v>0</v>
@@ -6346,22 +6346,22 @@
     </row>
     <row r="49">
       <c r="A49">
-        <v>0.47</v>
+        <v>0.48</v>
       </c>
       <c r="B49">
-        <v>0.09007388928031698</v>
+        <v>0.0899572680931469</v>
       </c>
       <c r="C49">
-        <v>8533.556753211598</v>
+        <v>8437.017776168557</v>
       </c>
       <c r="D49">
-        <v>13840.3807532116</v>
+        <v>13876.93377616856</v>
       </c>
       <c r="E49">
-        <v>6107.724</v>
+        <v>6240.816000000001</v>
       </c>
       <c r="F49">
-        <v>6255.324000000001</v>
+        <v>6388.416000000001</v>
       </c>
       <c r="G49">
         <v>948.5</v>
@@ -6382,28 +6382,28 @@
         <v>981.6</v>
       </c>
       <c r="M49">
-        <v>361.5577272</v>
+        <v>369.2504448000001</v>
       </c>
       <c r="N49">
-        <v>620.0422728</v>
+        <v>612.3495551999999</v>
       </c>
       <c r="O49">
-        <v>136.409300016</v>
+        <v>134.716902144</v>
       </c>
       <c r="P49">
-        <v>483.632972784</v>
+        <v>477.632653056</v>
       </c>
       <c r="Q49">
-        <v>527.3329727839999</v>
+        <v>521.3326530559999</v>
       </c>
       <c r="R49">
-        <v>0.8867924528301887</v>
+        <v>0.9230769230769231</v>
       </c>
       <c r="S49">
-        <v>0.1299705835477679</v>
+        <v>0.1313787463329748</v>
       </c>
       <c r="T49">
-        <v>1.943893384475009</v>
+        <v>1.976414464964776</v>
       </c>
       <c r="U49">
         <v>0.0578</v>
@@ -6420,7 +6420,7 @@
         </is>
       </c>
       <c r="Y49">
-        <v>2.714919157175186</v>
+        <v>2.658358341400703</v>
       </c>
       <c r="Z49">
         <v>0</v>
@@ -6428,22 +6428,22 @@
     </row>
     <row r="50">
       <c r="A50">
-        <v>0.48</v>
+        <v>0.49</v>
       </c>
       <c r="B50">
-        <v>0.0899572680931469</v>
+        <v>0.08984064690597682</v>
       </c>
       <c r="C50">
-        <v>8437.017776168559</v>
+        <v>8340.672386514962</v>
       </c>
       <c r="D50">
-        <v>13876.93377616856</v>
+        <v>13913.68038651496</v>
       </c>
       <c r="E50">
-        <v>6240.816</v>
+        <v>6373.907999999999</v>
       </c>
       <c r="F50">
-        <v>6388.416</v>
+        <v>6521.508</v>
       </c>
       <c r="G50">
         <v>948.5</v>
@@ -6464,28 +6464,28 @@
         <v>981.6</v>
       </c>
       <c r="M50">
-        <v>369.2504448</v>
+        <v>376.9431624</v>
       </c>
       <c r="N50">
-        <v>612.3495551999999</v>
+        <v>604.6568376</v>
       </c>
       <c r="O50">
-        <v>134.716902144</v>
+        <v>133.024504272</v>
       </c>
       <c r="P50">
-        <v>477.632653056</v>
+        <v>471.632333328</v>
       </c>
       <c r="Q50">
-        <v>521.3326530559999</v>
+        <v>515.332333328</v>
       </c>
       <c r="R50">
-        <v>0.923076923076923</v>
+        <v>0.9607843137254901</v>
       </c>
       <c r="S50">
-        <v>0.1313787463329748</v>
+        <v>0.1328421311881898</v>
       </c>
       <c r="T50">
-        <v>1.976414464964776</v>
+        <v>2.010210881944338</v>
       </c>
       <c r="U50">
         <v>0.0578</v>
@@ -6502,7 +6502,7 @@
         </is>
       </c>
       <c r="Y50">
-        <v>2.658358341400703</v>
+        <v>2.60410613035171</v>
       </c>
       <c r="Z50">
         <v>0</v>
@@ -6510,22 +6510,22 @@
     </row>
     <row r="51">
       <c r="A51">
-        <v>0.49</v>
+        <v>0.5</v>
       </c>
       <c r="B51">
-        <v>0.08984064690597682</v>
+        <v>0.08972402571880674</v>
       </c>
       <c r="C51">
-        <v>8340.672386514962</v>
+        <v>8244.522126212689</v>
       </c>
       <c r="D51">
-        <v>13913.68038651496</v>
+        <v>13950.62212621269</v>
       </c>
       <c r="E51">
-        <v>6373.907999999999</v>
+        <v>6507</v>
       </c>
       <c r="F51">
-        <v>6521.508</v>
+        <v>6654.6</v>
       </c>
       <c r="G51">
         <v>948.5</v>
@@ -6546,28 +6546,28 @@
         <v>981.6</v>
       </c>
       <c r="M51">
-        <v>376.9431624</v>
+        <v>384.63588</v>
       </c>
       <c r="N51">
-        <v>604.6568376</v>
+        <v>596.96412</v>
       </c>
       <c r="O51">
-        <v>133.024504272</v>
+        <v>131.3321064</v>
       </c>
       <c r="P51">
-        <v>471.632333328</v>
+        <v>465.6320136</v>
       </c>
       <c r="Q51">
-        <v>515.332333328</v>
+        <v>509.3320135999999</v>
       </c>
       <c r="R51">
-        <v>0.9607843137254901</v>
+        <v>1</v>
       </c>
       <c r="S51">
-        <v>0.1328421311881898</v>
+        <v>0.1343640514376135</v>
       </c>
       <c r="T51">
-        <v>2.010210881944338</v>
+        <v>2.045359155603082</v>
       </c>
       <c r="U51">
         <v>0.0578</v>
@@ -6584,7 +6584,7 @@
         </is>
       </c>
       <c r="Y51">
-        <v>2.60410613035171</v>
+        <v>2.552024007744675</v>
       </c>
       <c r="Z51">
         <v>0</v>
@@ -6592,22 +6592,22 @@
     </row>
     <row r="52">
       <c r="A52">
-        <v>0.5</v>
+        <v>0.51</v>
       </c>
       <c r="B52">
-        <v>0.08972402571880674</v>
+        <v>0.08960740453163665</v>
       </c>
       <c r="C52">
-        <v>8244.522126212689</v>
+        <v>8148.568553643265</v>
       </c>
       <c r="D52">
-        <v>13950.62212621269</v>
+        <v>13987.76055364327</v>
       </c>
       <c r="E52">
-        <v>6507</v>
+        <v>6640.092000000001</v>
       </c>
       <c r="F52">
-        <v>6654.6</v>
+        <v>6787.692000000001</v>
       </c>
       <c r="G52">
         <v>948.5</v>
@@ -6628,28 +6628,28 @@
         <v>981.6</v>
       </c>
       <c r="M52">
-        <v>384.63588</v>
+        <v>392.3285976000001</v>
       </c>
       <c r="N52">
-        <v>596.96412</v>
+        <v>589.2714023999999</v>
       </c>
       <c r="O52">
-        <v>131.3321064</v>
+        <v>129.639708528</v>
       </c>
       <c r="P52">
-        <v>465.6320136</v>
+        <v>459.6316938719999</v>
       </c>
       <c r="Q52">
-        <v>509.3320135999999</v>
+        <v>503.3316938719998</v>
       </c>
       <c r="R52">
-        <v>1</v>
+        <v>1.040816326530612</v>
       </c>
       <c r="S52">
-        <v>0.1343640514376135</v>
+        <v>0.1359480908808911</v>
       </c>
       <c r="T52">
-        <v>2.045359155603082</v>
+        <v>2.081942052676469</v>
       </c>
       <c r="U52">
         <v>0.0578</v>
@@ -6666,7 +6666,7 @@
         </is>
       </c>
       <c r="Y52">
-        <v>2.552024007744675</v>
+        <v>2.501984321318309</v>
       </c>
       <c r="Z52">
         <v>0</v>
@@ -6674,22 +6674,22 @@
     </row>
     <row r="53">
       <c r="A53">
-        <v>0.51</v>
+        <v>0.52</v>
       </c>
       <c r="B53">
-        <v>0.08960740453163665</v>
+        <v>0.09091038334446656</v>
       </c>
       <c r="C53">
-        <v>8148.568553643265</v>
+        <v>7611.450821891846</v>
       </c>
       <c r="D53">
-        <v>13987.76055364327</v>
+        <v>13583.73482189185</v>
       </c>
       <c r="E53">
-        <v>6640.092000000001</v>
+        <v>6773.184</v>
       </c>
       <c r="F53">
-        <v>6787.692000000001</v>
+        <v>6920.784000000001</v>
       </c>
       <c r="G53">
         <v>948.5</v>
@@ -6710,45 +6710,45 @@
         <v>981.6</v>
       </c>
       <c r="M53">
-        <v>392.3285976000001</v>
+        <v>424.2440592</v>
       </c>
       <c r="N53">
-        <v>589.2714023999999</v>
+        <v>557.3559408</v>
       </c>
       <c r="O53">
-        <v>129.639708528</v>
+        <v>122.618306976</v>
       </c>
       <c r="P53">
-        <v>459.6316938719999</v>
+        <v>434.737633824</v>
       </c>
       <c r="Q53">
-        <v>503.3316938719998</v>
+        <v>478.4376338239999</v>
       </c>
       <c r="R53">
-        <v>1.040816326530612</v>
+        <v>1.083333333333333</v>
       </c>
       <c r="S53">
-        <v>0.1359480908808911</v>
+        <v>0.1375981319676387</v>
       </c>
       <c r="T53">
-        <v>2.081942052676469</v>
+        <v>2.120049237127914</v>
       </c>
       <c r="U53">
-        <v>0.0578</v>
+        <v>0.0613</v>
       </c>
       <c r="V53">
         <v>0.22</v>
       </c>
       <c r="W53">
-        <v>0.04508400000000001</v>
+        <v>0.047814</v>
       </c>
       <c r="X53" t="inlineStr">
         <is>
-          <t>Baa2/BBB</t>
+          <t>Ba1/BB+</t>
         </is>
       </c>
       <c r="Y53">
-        <v>2.501984321318309</v>
+        <v>2.313762511727353</v>
       </c>
       <c r="Z53">
         <v>0</v>
@@ -6756,22 +6756,22 @@
     </row>
     <row r="54">
       <c r="A54">
-        <v>0.52</v>
+        <v>0.53</v>
       </c>
       <c r="B54">
-        <v>0.09091038334446656</v>
+        <v>0.09082106215729649</v>
       </c>
       <c r="C54">
-        <v>7611.450821891846</v>
+        <v>7505.308770701487</v>
       </c>
       <c r="D54">
-        <v>13583.73482189185</v>
+        <v>13610.68477070149</v>
       </c>
       <c r="E54">
-        <v>6773.184</v>
+        <v>6906.276000000001</v>
       </c>
       <c r="F54">
-        <v>6920.784000000001</v>
+        <v>7053.876000000001</v>
       </c>
       <c r="G54">
         <v>948.5</v>
@@ -6792,28 +6792,28 @@
         <v>981.6</v>
       </c>
       <c r="M54">
-        <v>424.2440592</v>
+        <v>432.4025988000001</v>
       </c>
       <c r="N54">
-        <v>557.3559408</v>
+        <v>549.1974011999999</v>
       </c>
       <c r="O54">
-        <v>122.618306976</v>
+        <v>120.823428264</v>
       </c>
       <c r="P54">
-        <v>434.737633824</v>
+        <v>428.373972936</v>
       </c>
       <c r="Q54">
-        <v>478.4376338239999</v>
+        <v>472.0739729359999</v>
       </c>
       <c r="R54">
-        <v>1.083333333333333</v>
+        <v>1.127659574468085</v>
       </c>
       <c r="S54">
-        <v>0.1375981319676387</v>
+        <v>0.1393183875687159</v>
       </c>
       <c r="T54">
-        <v>2.120049237127914</v>
+        <v>2.159778003896441</v>
       </c>
       <c r="U54">
         <v>0.0613</v>
@@ -6830,7 +6830,7 @@
         </is>
       </c>
       <c r="Y54">
-        <v>2.313762511727353</v>
+        <v>2.270106615279667</v>
       </c>
       <c r="Z54">
         <v>0</v>
@@ -6838,22 +6838,22 @@
     </row>
     <row r="55">
       <c r="A55">
-        <v>0.53</v>
+        <v>0.54</v>
       </c>
       <c r="B55">
-        <v>0.09082106215729649</v>
+        <v>0.09191110097012641</v>
       </c>
       <c r="C55">
-        <v>7505.308770701487</v>
+        <v>7050.468333619721</v>
       </c>
       <c r="D55">
-        <v>13610.68477070149</v>
+        <v>13288.93633361972</v>
       </c>
       <c r="E55">
-        <v>6906.276000000001</v>
+        <v>7039.368</v>
       </c>
       <c r="F55">
-        <v>7053.876000000001</v>
+        <v>7186.968000000001</v>
       </c>
       <c r="G55">
         <v>948.5</v>
@@ -6874,45 +6874,45 @@
         <v>981.6</v>
       </c>
       <c r="M55">
-        <v>432.4025988000001</v>
+        <v>460.6846488000001</v>
       </c>
       <c r="N55">
-        <v>549.1974011999999</v>
+        <v>520.9153511999999</v>
       </c>
       <c r="O55">
-        <v>120.823428264</v>
+        <v>114.601377264</v>
       </c>
       <c r="P55">
-        <v>428.373972936</v>
+        <v>406.3139739359999</v>
       </c>
       <c r="Q55">
-        <v>472.0739729359999</v>
+        <v>450.0139739359998</v>
       </c>
       <c r="R55">
-        <v>1.127659574468085</v>
+        <v>1.173913043478261</v>
       </c>
       <c r="S55">
-        <v>0.1393183875687159</v>
+        <v>0.1411134368915791</v>
       </c>
       <c r="T55">
-        <v>2.159778003896441</v>
+        <v>2.201234108350557</v>
       </c>
       <c r="U55">
-        <v>0.0613</v>
+        <v>0.0641</v>
       </c>
       <c r="V55">
         <v>0.22</v>
       </c>
       <c r="W55">
-        <v>0.047814</v>
+        <v>0.04999800000000001</v>
       </c>
       <c r="X55" t="inlineStr">
         <is>
-          <t>Ba1/BB+</t>
+          <t>Ba2/BB</t>
         </is>
       </c>
       <c r="Y55">
-        <v>2.270106615279667</v>
+        <v>2.130741717912437</v>
       </c>
       <c r="Z55">
         <v>0</v>
@@ -6920,22 +6920,22 @@
     </row>
     <row r="56">
       <c r="A56">
-        <v>0.54</v>
+        <v>0.55</v>
       </c>
       <c r="B56">
-        <v>0.09191110097012641</v>
+        <v>0.09184361978295631</v>
       </c>
       <c r="C56">
-        <v>7050.468333619721</v>
+        <v>6936.852500008194</v>
       </c>
       <c r="D56">
-        <v>13288.93633361972</v>
+        <v>13308.41250000819</v>
       </c>
       <c r="E56">
-        <v>7039.368</v>
+        <v>7172.460000000001</v>
       </c>
       <c r="F56">
-        <v>7186.968000000001</v>
+        <v>7320.060000000001</v>
       </c>
       <c r="G56">
         <v>948.5</v>
@@ -6956,28 +6956,28 @@
         <v>981.6</v>
       </c>
       <c r="M56">
-        <v>460.6846488000001</v>
+        <v>469.2158460000001</v>
       </c>
       <c r="N56">
-        <v>520.9153511999999</v>
+        <v>512.3841539999999</v>
       </c>
       <c r="O56">
-        <v>114.601377264</v>
+        <v>112.72451388</v>
       </c>
       <c r="P56">
-        <v>406.3139739359999</v>
+        <v>399.6596401199999</v>
       </c>
       <c r="Q56">
-        <v>450.0139739359998</v>
+        <v>443.3596401199998</v>
       </c>
       <c r="R56">
-        <v>1.173913043478261</v>
+        <v>1.222222222222223</v>
       </c>
       <c r="S56">
-        <v>0.1411134368915791</v>
+        <v>0.1429882661843474</v>
       </c>
       <c r="T56">
-        <v>2.201234108350557</v>
+        <v>2.244532706335967</v>
       </c>
       <c r="U56">
         <v>0.0641</v>
@@ -6994,7 +6994,7 @@
         </is>
       </c>
       <c r="Y56">
-        <v>2.130741717912437</v>
+        <v>2.092000959404938</v>
       </c>
       <c r="Z56">
         <v>0</v>
@@ -7002,22 +7002,22 @@
     </row>
     <row r="57">
       <c r="A57">
-        <v>0.55</v>
+        <v>0.5600000000000001</v>
       </c>
       <c r="B57">
-        <v>0.09184361978295631</v>
+        <v>0.09177613859578622</v>
       </c>
       <c r="C57">
-        <v>6936.852500008194</v>
+        <v>6823.293838437189</v>
       </c>
       <c r="D57">
-        <v>13308.41250000819</v>
+        <v>13327.94583843719</v>
       </c>
       <c r="E57">
-        <v>7172.460000000001</v>
+        <v>7305.552000000001</v>
       </c>
       <c r="F57">
-        <v>7320.060000000001</v>
+        <v>7453.152000000001</v>
       </c>
       <c r="G57">
         <v>948.5</v>
@@ -7038,28 +7038,28 @@
         <v>981.6</v>
       </c>
       <c r="M57">
-        <v>469.2158460000001</v>
+        <v>477.7470432000001</v>
       </c>
       <c r="N57">
-        <v>512.3841539999999</v>
+        <v>503.8529568</v>
       </c>
       <c r="O57">
-        <v>112.72451388</v>
+        <v>110.847650496</v>
       </c>
       <c r="P57">
-        <v>399.6596401199999</v>
+        <v>393.005306304</v>
       </c>
       <c r="Q57">
-        <v>443.3596401199998</v>
+        <v>436.7053063039999</v>
       </c>
       <c r="R57">
-        <v>1.222222222222223</v>
+        <v>1.272727272727273</v>
       </c>
       <c r="S57">
-        <v>0.1429882661843474</v>
+        <v>0.1449483149904232</v>
       </c>
       <c r="T57">
-        <v>2.244532706335967</v>
+        <v>2.289799422411622</v>
       </c>
       <c r="U57">
         <v>0.0641</v>
@@ -7076,7 +7076,7 @@
         </is>
       </c>
       <c r="Y57">
-        <v>2.092000959404938</v>
+        <v>2.054643799415564</v>
       </c>
       <c r="Z57">
         <v>0</v>
@@ -7084,22 +7084,22 @@
     </row>
     <row r="58">
       <c r="A58">
-        <v>0.5600000000000001</v>
+        <v>0.5700000000000001</v>
       </c>
       <c r="B58">
-        <v>0.09177613859578622</v>
+        <v>0.09170865740861614</v>
       </c>
       <c r="C58">
-        <v>6823.293838437189</v>
+        <v>6709.792601018443</v>
       </c>
       <c r="D58">
-        <v>13327.94583843719</v>
+        <v>13347.53660101844</v>
       </c>
       <c r="E58">
-        <v>7305.552000000001</v>
+        <v>7438.644000000001</v>
       </c>
       <c r="F58">
-        <v>7453.152000000001</v>
+        <v>7586.244000000002</v>
       </c>
       <c r="G58">
         <v>948.5</v>
@@ -7120,28 +7120,28 @@
         <v>981.6</v>
       </c>
       <c r="M58">
-        <v>477.7470432000001</v>
+        <v>486.2782404000001</v>
       </c>
       <c r="N58">
-        <v>503.8529568</v>
+        <v>495.3217595999999</v>
       </c>
       <c r="O58">
-        <v>110.847650496</v>
+        <v>108.970787112</v>
       </c>
       <c r="P58">
-        <v>393.005306304</v>
+        <v>386.3509724879999</v>
       </c>
       <c r="Q58">
-        <v>436.7053063039999</v>
+        <v>430.0509724879998</v>
       </c>
       <c r="R58">
-        <v>1.272727272727273</v>
+        <v>1.325581395348838</v>
       </c>
       <c r="S58">
-        <v>0.1449483149904232</v>
+        <v>0.1469995288572468</v>
       </c>
       <c r="T58">
-        <v>2.289799422411622</v>
+        <v>2.337171567141959</v>
       </c>
       <c r="U58">
         <v>0.0641</v>
@@ -7158,7 +7158,7 @@
         </is>
       </c>
       <c r="Y58">
-        <v>2.054643799415564</v>
+        <v>2.018597416969677</v>
       </c>
       <c r="Z58">
         <v>0</v>
@@ -7166,22 +7166,22 @@
     </row>
     <row r="59">
       <c r="A59">
-        <v>0.5700000000000001</v>
+        <v>0.5800000000000001</v>
       </c>
       <c r="B59">
-        <v>0.09170865740861614</v>
+        <v>0.09516989622144606</v>
       </c>
       <c r="C59">
-        <v>6709.792601018443</v>
+        <v>5640.927685234099</v>
       </c>
       <c r="D59">
-        <v>13347.53660101844</v>
+        <v>12411.7636852341</v>
       </c>
       <c r="E59">
-        <v>7438.644000000001</v>
+        <v>7571.736000000001</v>
       </c>
       <c r="F59">
-        <v>7586.244000000002</v>
+        <v>7719.336000000001</v>
       </c>
       <c r="G59">
         <v>948.5</v>
@@ -7202,45 +7202,45 @@
         <v>981.6</v>
       </c>
       <c r="M59">
-        <v>486.2782404000001</v>
+        <v>555.0202584000001</v>
       </c>
       <c r="N59">
-        <v>495.3217595999999</v>
+        <v>426.5797415999999</v>
       </c>
       <c r="O59">
-        <v>108.970787112</v>
+        <v>93.84754315199999</v>
       </c>
       <c r="P59">
-        <v>386.3509724879999</v>
+        <v>332.732198448</v>
       </c>
       <c r="Q59">
-        <v>430.0509724879998</v>
+        <v>376.4321984479999</v>
       </c>
       <c r="R59">
-        <v>1.325581395348838</v>
+        <v>1.380952380952381</v>
       </c>
       <c r="S59">
-        <v>0.1469995288572468</v>
+        <v>0.1491484195748716</v>
       </c>
       <c r="T59">
-        <v>2.337171567141959</v>
+        <v>2.386799528288027</v>
       </c>
       <c r="U59">
-        <v>0.0641</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="V59">
         <v>0.22</v>
       </c>
       <c r="W59">
-        <v>0.04999800000000001</v>
+        <v>0.05608200000000001</v>
       </c>
       <c r="X59" t="inlineStr">
         <is>
-          <t>Ba2/BB</t>
+          <t>B1/B+</t>
         </is>
       </c>
       <c r="Y59">
-        <v>2.018597416969677</v>
+        <v>1.768584092461299</v>
       </c>
       <c r="Z59">
         <v>0</v>
@@ -7248,22 +7248,22 @@
     </row>
     <row r="60">
       <c r="A60">
-        <v>0.58</v>
+        <v>0.59</v>
       </c>
       <c r="B60">
-        <v>0.09516989622144606</v>
+        <v>0.09695803503427597</v>
       </c>
       <c r="C60">
-        <v>5640.9276852341</v>
+        <v>5074.004394286943</v>
       </c>
       <c r="D60">
-        <v>12411.7636852341</v>
+        <v>11977.93239428694</v>
       </c>
       <c r="E60">
-        <v>7571.736</v>
+        <v>7704.828</v>
       </c>
       <c r="F60">
-        <v>7719.336</v>
+        <v>7852.428</v>
       </c>
       <c r="G60">
         <v>948.5</v>
@@ -7284,45 +7284,45 @@
         <v>981.6</v>
       </c>
       <c r="M60">
-        <v>555.0202584000001</v>
+        <v>595.2140424</v>
       </c>
       <c r="N60">
-        <v>426.5797415999999</v>
+        <v>386.3859576</v>
       </c>
       <c r="O60">
-        <v>93.84754315199999</v>
+        <v>85.00491067199999</v>
       </c>
       <c r="P60">
-        <v>332.732198448</v>
+        <v>301.381046928</v>
       </c>
       <c r="Q60">
-        <v>376.4321984479999</v>
+        <v>345.0810469279999</v>
       </c>
       <c r="R60">
-        <v>1.380952380952381</v>
+        <v>1.439024390243902</v>
       </c>
       <c r="S60">
-        <v>0.1491484195748716</v>
+        <v>0.1514021342299414</v>
       </c>
       <c r="T60">
-        <v>2.386799528288027</v>
+        <v>2.43884836558756</v>
       </c>
       <c r="U60">
-        <v>0.07190000000000001</v>
+        <v>0.07580000000000001</v>
       </c>
       <c r="V60">
         <v>0.22</v>
       </c>
       <c r="W60">
-        <v>0.05608200000000001</v>
+        <v>0.05912400000000001</v>
       </c>
       <c r="X60" t="inlineStr">
         <is>
-          <t>B1/B+</t>
+          <t>B2/B</t>
         </is>
       </c>
       <c r="Y60">
-        <v>1.768584092461299</v>
+        <v>1.649154640307256</v>
       </c>
       <c r="Z60">
         <v>0</v>
@@ -7330,22 +7330,22 @@
     </row>
     <row r="61">
       <c r="A61">
-        <v>0.59</v>
+        <v>0.6</v>
       </c>
       <c r="B61">
-        <v>0.09695803503427597</v>
+        <v>0.09698181384710589</v>
       </c>
       <c r="C61">
-        <v>5074.004394286943</v>
+        <v>4935.347507248276</v>
       </c>
       <c r="D61">
-        <v>11977.93239428694</v>
+        <v>11972.36750724828</v>
       </c>
       <c r="E61">
-        <v>7704.828</v>
+        <v>7837.92</v>
       </c>
       <c r="F61">
-        <v>7852.428</v>
+        <v>7985.52</v>
       </c>
       <c r="G61">
         <v>948.5</v>
@@ -7366,28 +7366,28 @@
         <v>981.6</v>
       </c>
       <c r="M61">
-        <v>595.2140424</v>
+        <v>605.3024160000001</v>
       </c>
       <c r="N61">
-        <v>386.3859576</v>
+        <v>376.2975839999999</v>
       </c>
       <c r="O61">
-        <v>85.00491067199999</v>
+        <v>82.78546847999998</v>
       </c>
       <c r="P61">
-        <v>301.381046928</v>
+        <v>293.51211552</v>
       </c>
       <c r="Q61">
-        <v>345.0810469279999</v>
+        <v>337.2121155199999</v>
       </c>
       <c r="R61">
-        <v>1.439024390243902</v>
+        <v>1.5</v>
       </c>
       <c r="S61">
-        <v>0.1514021342299414</v>
+        <v>0.1537685346177647</v>
       </c>
       <c r="T61">
-        <v>2.43884836558756</v>
+        <v>2.493499644752072</v>
       </c>
       <c r="U61">
         <v>0.07580000000000001</v>
@@ -7404,7 +7404,7 @@
         </is>
       </c>
       <c r="Y61">
-        <v>1.649154640307256</v>
+        <v>1.621668729635469</v>
       </c>
       <c r="Z61">
         <v>0</v>
@@ -7412,22 +7412,22 @@
     </row>
     <row r="62">
       <c r="A62">
-        <v>0.6</v>
+        <v>0.61</v>
       </c>
       <c r="B62">
-        <v>0.09698181384710589</v>
+        <v>0.0970055926599358</v>
       </c>
       <c r="C62">
-        <v>4935.347507248276</v>
+        <v>4796.695788645339</v>
       </c>
       <c r="D62">
-        <v>11972.36750724828</v>
+        <v>11966.80778864534</v>
       </c>
       <c r="E62">
-        <v>7837.92</v>
+        <v>7971.012</v>
       </c>
       <c r="F62">
-        <v>7985.52</v>
+        <v>8118.612</v>
       </c>
       <c r="G62">
         <v>948.5</v>
@@ -7448,28 +7448,28 @@
         <v>981.6</v>
       </c>
       <c r="M62">
-        <v>605.3024160000001</v>
+        <v>615.3907896000001</v>
       </c>
       <c r="N62">
-        <v>376.2975839999999</v>
+        <v>366.2092104</v>
       </c>
       <c r="O62">
-        <v>82.78546847999998</v>
+        <v>80.56602628799999</v>
       </c>
       <c r="P62">
-        <v>293.51211552</v>
+        <v>285.643184112</v>
       </c>
       <c r="Q62">
-        <v>337.2121155199999</v>
+        <v>329.3431841119999</v>
       </c>
       <c r="R62">
-        <v>1.5</v>
+        <v>1.564102564102564</v>
       </c>
       <c r="S62">
-        <v>0.1537685346177647</v>
+        <v>0.1562562888716303</v>
       </c>
       <c r="T62">
-        <v>2.493499644752072</v>
+        <v>2.550953553617326</v>
       </c>
       <c r="U62">
         <v>0.07580000000000001</v>
@@ -7486,7 +7486,7 @@
         </is>
       </c>
       <c r="Y62">
-        <v>1.621668729635469</v>
+        <v>1.595083996362756</v>
       </c>
       <c r="Z62">
         <v>0</v>
@@ -7494,22 +7494,22 @@
     </row>
     <row r="63">
       <c r="A63">
-        <v>0.61</v>
+        <v>0.62</v>
       </c>
       <c r="B63">
-        <v>0.0970055926599358</v>
+        <v>0.09702937147276572</v>
       </c>
       <c r="C63">
-        <v>4796.695788645339</v>
+        <v>4658.049231281133</v>
       </c>
       <c r="D63">
-        <v>11966.80778864534</v>
+        <v>11961.25323128113</v>
       </c>
       <c r="E63">
-        <v>7971.012</v>
+        <v>8104.103999999999</v>
       </c>
       <c r="F63">
-        <v>8118.612</v>
+        <v>8251.704</v>
       </c>
       <c r="G63">
         <v>948.5</v>
@@ -7530,28 +7530,28 @@
         <v>981.6</v>
       </c>
       <c r="M63">
-        <v>615.3907896000001</v>
+        <v>625.4791632</v>
       </c>
       <c r="N63">
-        <v>366.2092104</v>
+        <v>356.1208368</v>
       </c>
       <c r="O63">
-        <v>80.56602628799999</v>
+        <v>78.346584096</v>
       </c>
       <c r="P63">
-        <v>285.643184112</v>
+        <v>277.774252704</v>
       </c>
       <c r="Q63">
-        <v>329.3431841119999</v>
+        <v>321.4742527039999</v>
       </c>
       <c r="R63">
-        <v>1.564102564102564</v>
+        <v>1.631578947368421</v>
       </c>
       <c r="S63">
-        <v>0.1562562888716303</v>
+        <v>0.1588749775599098</v>
       </c>
       <c r="T63">
-        <v>2.550953553617326</v>
+        <v>2.611431352422859</v>
       </c>
       <c r="U63">
         <v>0.07580000000000001</v>
@@ -7568,7 +7568,7 @@
         </is>
       </c>
       <c r="Y63">
-        <v>1.595083996362756</v>
+        <v>1.569356835131099</v>
       </c>
       <c r="Z63">
         <v>0</v>
@@ -7576,22 +7576,22 @@
     </row>
     <row r="64">
       <c r="A64">
-        <v>0.62</v>
+        <v>0.63</v>
       </c>
       <c r="B64">
-        <v>0.09702937147276572</v>
+        <v>0.09705315028559564</v>
       </c>
       <c r="C64">
-        <v>4658.049231281133</v>
+        <v>4519.407827972009</v>
       </c>
       <c r="D64">
-        <v>11961.25323128113</v>
+        <v>11955.70382797201</v>
       </c>
       <c r="E64">
-        <v>8104.103999999999</v>
+        <v>8237.196</v>
       </c>
       <c r="F64">
-        <v>8251.704</v>
+        <v>8384.796</v>
       </c>
       <c r="G64">
         <v>948.5</v>
@@ -7612,28 +7612,28 @@
         <v>981.6</v>
       </c>
       <c r="M64">
-        <v>625.4791632</v>
+        <v>635.5675368000001</v>
       </c>
       <c r="N64">
-        <v>356.1208368</v>
+        <v>346.0324631999999</v>
       </c>
       <c r="O64">
-        <v>78.346584096</v>
+        <v>76.12714190399998</v>
       </c>
       <c r="P64">
-        <v>277.774252704</v>
+        <v>269.905321296</v>
       </c>
       <c r="Q64">
-        <v>321.4742527039999</v>
+        <v>313.6053212959999</v>
       </c>
       <c r="R64">
-        <v>1.631578947368421</v>
+        <v>1.702702702702703</v>
       </c>
       <c r="S64">
-        <v>0.1588749775599098</v>
+        <v>0.1616352169880963</v>
       </c>
       <c r="T64">
-        <v>2.611431352422859</v>
+        <v>2.675178221434094</v>
       </c>
       <c r="U64">
         <v>0.07580000000000001</v>
@@ -7650,7 +7650,7 @@
         </is>
       </c>
       <c r="Y64">
-        <v>1.569356835131099</v>
+        <v>1.544446409176637</v>
       </c>
       <c r="Z64">
         <v>0</v>
@@ -7658,22 +7658,22 @@
     </row>
     <row r="65">
       <c r="A65">
-        <v>0.63</v>
+        <v>0.64</v>
       </c>
       <c r="B65">
-        <v>0.09705315028559564</v>
+        <v>0.09707692909842555</v>
       </c>
       <c r="C65">
-        <v>4519.407827972009</v>
+        <v>4380.771571547652</v>
       </c>
       <c r="D65">
-        <v>11955.70382797201</v>
+        <v>11950.15957154765</v>
       </c>
       <c r="E65">
-        <v>8237.196</v>
+        <v>8370.288</v>
       </c>
       <c r="F65">
-        <v>8384.796</v>
+        <v>8517.888000000001</v>
       </c>
       <c r="G65">
         <v>948.5</v>
@@ -7694,28 +7694,28 @@
         <v>981.6</v>
       </c>
       <c r="M65">
-        <v>635.5675368000001</v>
+        <v>645.6559104000002</v>
       </c>
       <c r="N65">
-        <v>346.0324631999999</v>
+        <v>335.9440895999999</v>
       </c>
       <c r="O65">
-        <v>76.12714190399998</v>
+        <v>73.90769971199997</v>
       </c>
       <c r="P65">
-        <v>269.905321296</v>
+        <v>262.0363898879999</v>
       </c>
       <c r="Q65">
-        <v>313.6053212959999</v>
+        <v>305.7363898879998</v>
       </c>
       <c r="R65">
-        <v>1.702702702702703</v>
+        <v>1.777777777777778</v>
       </c>
       <c r="S65">
-        <v>0.1616352169880963</v>
+        <v>0.1645488030511821</v>
       </c>
       <c r="T65">
-        <v>2.675178221434094</v>
+        <v>2.742466583168177</v>
       </c>
       <c r="U65">
         <v>0.07580000000000001</v>
@@ -7732,7 +7732,7 @@
         </is>
       </c>
       <c r="Y65">
-        <v>1.544446409176637</v>
+        <v>1.520314434033252</v>
       </c>
       <c r="Z65">
         <v>0</v>
@@ -7740,22 +7740,22 @@
     </row>
     <row r="66">
       <c r="A66">
-        <v>0.64</v>
+        <v>0.65</v>
       </c>
       <c r="B66">
-        <v>0.09707692909842555</v>
+        <v>0.1043001079112555</v>
       </c>
       <c r="C66">
-        <v>4380.771571547652</v>
+        <v>2772.158542456829</v>
       </c>
       <c r="D66">
-        <v>11950.15957154765</v>
+        <v>10474.63854245683</v>
       </c>
       <c r="E66">
-        <v>8370.288</v>
+        <v>8503.380000000001</v>
       </c>
       <c r="F66">
-        <v>8517.888000000001</v>
+        <v>8650.980000000001</v>
       </c>
       <c r="G66">
         <v>948.5</v>
@@ -7776,45 +7776,45 @@
         <v>981.6</v>
       </c>
       <c r="M66">
-        <v>645.6559104000002</v>
+        <v>778.5882000000001</v>
       </c>
       <c r="N66">
-        <v>335.9440895999999</v>
+        <v>203.0117999999999</v>
       </c>
       <c r="O66">
-        <v>73.90769971199997</v>
+        <v>44.66259599999997</v>
       </c>
       <c r="P66">
-        <v>262.0363898879999</v>
+        <v>158.3492039999999</v>
       </c>
       <c r="Q66">
-        <v>305.7363898879998</v>
+        <v>202.0492039999998</v>
       </c>
       <c r="R66">
-        <v>1.777777777777778</v>
+        <v>1.857142857142857</v>
       </c>
       <c r="S66">
-        <v>0.1645488030511821</v>
+        <v>0.1676288797464442</v>
       </c>
       <c r="T66">
-        <v>2.742466583168177</v>
+        <v>2.813599994144208</v>
       </c>
       <c r="U66">
-        <v>0.07580000000000001</v>
+        <v>0.09</v>
       </c>
       <c r="V66">
         <v>0.22</v>
       </c>
       <c r="W66">
-        <v>0.05912400000000001</v>
+        <v>0.0702</v>
       </c>
       <c r="X66" t="inlineStr">
         <is>
-          <t>B2/B</t>
+          <t>B3/B-</t>
         </is>
       </c>
       <c r="Y66">
-        <v>1.520314434033252</v>
+        <v>1.260743484167882</v>
       </c>
       <c r="Z66">
         <v>0</v>
@@ -7822,22 +7822,22 @@
     </row>
     <row r="67">
       <c r="A67">
-        <v>0.65</v>
+        <v>0.66</v>
       </c>
       <c r="B67">
-        <v>0.1043001079112555</v>
+        <v>0.1205702801865788</v>
       </c>
       <c r="C67">
-        <v>2772.158542456829</v>
+        <v>359.7628781901694</v>
       </c>
       <c r="D67">
-        <v>10474.63854245683</v>
+        <v>8195.33487819017</v>
       </c>
       <c r="E67">
-        <v>8503.380000000001</v>
+        <v>8636.472</v>
       </c>
       <c r="F67">
-        <v>8650.980000000001</v>
+        <v>8784.072</v>
       </c>
       <c r="G67">
         <v>948.5</v>
@@ -7858,45 +7858,45 @@
         <v>981.6</v>
       </c>
       <c r="M67">
-        <v>778.5882000000001</v>
+        <v>1041.7909392</v>
       </c>
       <c r="N67">
-        <v>203.0117999999999</v>
+        <v>-60.19093920000012</v>
       </c>
       <c r="O67">
-        <v>44.66259599999997</v>
+        <v>-13.24200662400002</v>
       </c>
       <c r="P67">
-        <v>158.3492039999999</v>
+        <v>-46.94893257600009</v>
       </c>
       <c r="Q67">
-        <v>202.0492039999998</v>
+        <v>-3.248932576000158</v>
       </c>
       <c r="R67">
-        <v>1.857142857142857</v>
+        <v>1.941176470588236</v>
       </c>
       <c r="S67">
-        <v>0.1676288797464442</v>
+        <v>0.1721177906700572</v>
       </c>
       <c r="T67">
-        <v>2.813599994144208</v>
+        <v>2.917269992380072</v>
       </c>
       <c r="U67">
-        <v>0.09</v>
+        <v>0.1186</v>
       </c>
       <c r="V67">
-        <v>0.22</v>
+        <v>0.2072891900613297</v>
       </c>
       <c r="W67">
-        <v>0.0702</v>
+        <v>0.0940155020587263</v>
       </c>
       <c r="X67" t="inlineStr">
         <is>
-          <t>B3/B-</t>
+          <t>Caa/CCC</t>
         </is>
       </c>
       <c r="Y67">
-        <v>1.260743484167882</v>
+        <v>0.9422235911878623</v>
       </c>
       <c r="Z67">
         <v>0</v>
@@ -7904,22 +7904,22 @@
     </row>
     <row r="68">
       <c r="A68">
-        <v>0.66</v>
+        <v>0.67</v>
       </c>
       <c r="B68">
-        <v>0.1205702801865788</v>
+        <v>0.1212982801865788</v>
       </c>
       <c r="C68">
-        <v>359.7628781901694</v>
+        <v>147.6465113227605</v>
       </c>
       <c r="D68">
-        <v>8195.33487819017</v>
+        <v>8116.310511322761</v>
       </c>
       <c r="E68">
-        <v>8636.472</v>
+        <v>8769.564</v>
       </c>
       <c r="F68">
-        <v>8784.072</v>
+        <v>8917.164000000001</v>
       </c>
       <c r="G68">
         <v>948.5</v>
@@ -7940,37 +7940,37 @@
         <v>981.6</v>
       </c>
       <c r="M68">
-        <v>1041.7909392</v>
+        <v>1057.5756504</v>
       </c>
       <c r="N68">
-        <v>-60.19093920000012</v>
+        <v>-75.97565040000006</v>
       </c>
       <c r="O68">
-        <v>-13.24200662400002</v>
+        <v>-16.71464308800001</v>
       </c>
       <c r="P68">
-        <v>-46.94893257600009</v>
+        <v>-59.26100731200005</v>
       </c>
       <c r="Q68">
-        <v>-3.248932576000158</v>
+        <v>-15.56100731200011</v>
       </c>
       <c r="R68">
-        <v>1.941176470588236</v>
+        <v>2.030303030303031</v>
       </c>
       <c r="S68">
-        <v>0.1721177906700572</v>
+        <v>0.1759456025085437</v>
       </c>
       <c r="T68">
-        <v>2.917269992380072</v>
+        <v>3.005672113361287</v>
       </c>
       <c r="U68">
         <v>0.1186</v>
       </c>
       <c r="V68">
-        <v>0.2072891900613297</v>
+        <v>0.2041953215529517</v>
       </c>
       <c r="W68">
-        <v>0.0940155020587263</v>
+        <v>0.09438243486381993</v>
       </c>
       <c r="X68" t="inlineStr">
         <is>
@@ -7978,7 +7978,7 @@
         </is>
       </c>
       <c r="Y68">
-        <v>0.9422235911878623</v>
+        <v>0.9281605525134167</v>
       </c>
       <c r="Z68">
         <v>0</v>
@@ -7986,22 +7986,22 @@
     </row>
     <row r="69">
       <c r="A69">
-        <v>0.67</v>
+        <v>0.68</v>
       </c>
       <c r="B69">
-        <v>0.1212982801865788</v>
+        <v>0.1220262801865788</v>
       </c>
       <c r="C69">
-        <v>147.6465113227605</v>
+        <v>-62.96040922406974</v>
       </c>
       <c r="D69">
-        <v>8116.310511322761</v>
+        <v>8038.795590775932</v>
       </c>
       <c r="E69">
-        <v>8769.564</v>
+        <v>8902.656000000001</v>
       </c>
       <c r="F69">
-        <v>8917.164000000001</v>
+        <v>9050.256000000001</v>
       </c>
       <c r="G69">
         <v>948.5</v>
@@ -8022,37 +8022,37 @@
         <v>981.6</v>
       </c>
       <c r="M69">
-        <v>1057.5756504</v>
+        <v>1073.3603616</v>
       </c>
       <c r="N69">
-        <v>-75.97565040000006</v>
+        <v>-91.76036160000024</v>
       </c>
       <c r="O69">
-        <v>-16.71464308800001</v>
+        <v>-20.18727955200005</v>
       </c>
       <c r="P69">
-        <v>-59.26100731200005</v>
+        <v>-71.57308204800019</v>
       </c>
       <c r="Q69">
-        <v>-15.56100731200011</v>
+        <v>-27.87308204800026</v>
       </c>
       <c r="R69">
-        <v>2.030303030303031</v>
+        <v>2.125</v>
       </c>
       <c r="S69">
-        <v>0.1759456025085437</v>
+        <v>0.1800126525869357</v>
       </c>
       <c r="T69">
-        <v>3.005672113361287</v>
+        <v>3.099599366903827</v>
       </c>
       <c r="U69">
         <v>0.1186</v>
       </c>
       <c r="V69">
-        <v>0.2041953215529517</v>
+        <v>0.2011924491771729</v>
       </c>
       <c r="W69">
-        <v>0.09438243486381993</v>
+        <v>0.0947385755275873</v>
       </c>
       <c r="X69" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         </is>
       </c>
       <c r="Y69">
-        <v>0.9281605525134167</v>
+        <v>0.9145111326235132</v>
       </c>
       <c r="Z69">
         <v>0</v>
@@ -8068,22 +8068,22 @@
     </row>
     <row r="70">
       <c r="A70">
-        <v>0.68</v>
+        <v>0.6900000000000001</v>
       </c>
       <c r="B70">
-        <v>0.1220262801865788</v>
+        <v>0.1227542801865788</v>
       </c>
       <c r="C70">
-        <v>-62.96040922406974</v>
+        <v>-272.1007222730113</v>
       </c>
       <c r="D70">
-        <v>8038.795590775932</v>
+        <v>7962.74727772699</v>
       </c>
       <c r="E70">
-        <v>8902.656000000001</v>
+        <v>9035.748000000001</v>
       </c>
       <c r="F70">
-        <v>9050.256000000001</v>
+        <v>9183.348000000002</v>
       </c>
       <c r="G70">
         <v>948.5</v>
@@ -8104,37 +8104,37 @@
         <v>981.6</v>
       </c>
       <c r="M70">
-        <v>1073.3603616</v>
+        <v>1089.1450728</v>
       </c>
       <c r="N70">
-        <v>-91.76036160000024</v>
+        <v>-107.5450728000002</v>
       </c>
       <c r="O70">
-        <v>-20.18727955200005</v>
+        <v>-23.65991601600004</v>
       </c>
       <c r="P70">
-        <v>-71.57308204800019</v>
+        <v>-83.88515678400015</v>
       </c>
       <c r="Q70">
-        <v>-27.87308204800026</v>
+        <v>-40.18515678400021</v>
       </c>
       <c r="R70">
-        <v>2.125</v>
+        <v>2.225806451612904</v>
       </c>
       <c r="S70">
-        <v>0.1800126525869357</v>
+        <v>0.1843420929929659</v>
       </c>
       <c r="T70">
-        <v>3.099599366903827</v>
+        <v>3.199586443255564</v>
       </c>
       <c r="U70">
         <v>0.1186</v>
       </c>
       <c r="V70">
-        <v>0.2011924491771729</v>
+        <v>0.1982766165804023</v>
       </c>
       <c r="W70">
-        <v>0.0947385755275873</v>
+        <v>0.0950843932735643</v>
       </c>
       <c r="X70" t="inlineStr">
         <is>
@@ -8142,7 +8142,7 @@
         </is>
       </c>
       <c r="Y70">
-        <v>0.9145111326235132</v>
+        <v>0.9012573480927378</v>
       </c>
       <c r="Z70">
         <v>0</v>
@@ -8150,22 +8150,22 @@
     </row>
     <row r="71">
       <c r="A71">
-        <v>0.6900000000000001</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="B71">
-        <v>0.1227542801865788</v>
+        <v>0.1234822801865788</v>
       </c>
       <c r="C71">
-        <v>-272.1007222730113</v>
+        <v>-479.8156607895162</v>
       </c>
       <c r="D71">
-        <v>7962.74727772699</v>
+        <v>7888.124339210483</v>
       </c>
       <c r="E71">
-        <v>9035.748000000001</v>
+        <v>9168.84</v>
       </c>
       <c r="F71">
-        <v>9183.348000000002</v>
+        <v>9316.440000000001</v>
       </c>
       <c r="G71">
         <v>948.5</v>
@@ -8186,37 +8186,37 @@
         <v>981.6</v>
       </c>
       <c r="M71">
-        <v>1089.1450728</v>
+        <v>1104.929784</v>
       </c>
       <c r="N71">
-        <v>-107.5450728000002</v>
+        <v>-123.3297840000001</v>
       </c>
       <c r="O71">
-        <v>-23.65991601600004</v>
+        <v>-27.13255248000003</v>
       </c>
       <c r="P71">
-        <v>-83.88515678400015</v>
+        <v>-96.1972315200001</v>
       </c>
       <c r="Q71">
-        <v>-40.18515678400021</v>
+        <v>-52.49723152000017</v>
       </c>
       <c r="R71">
-        <v>2.225806451612904</v>
+        <v>2.333333333333334</v>
       </c>
       <c r="S71">
-        <v>0.1843420929929659</v>
+        <v>0.1889601627593981</v>
       </c>
       <c r="T71">
-        <v>3.199586443255564</v>
+        <v>3.306239324697416</v>
       </c>
       <c r="U71">
         <v>0.1186</v>
       </c>
       <c r="V71">
-        <v>0.1982766165804023</v>
+        <v>0.1954440934863966</v>
       </c>
       <c r="W71">
-        <v>0.0950843932735643</v>
+        <v>0.09542033051251338</v>
       </c>
       <c r="X71" t="inlineStr">
         <is>
@@ -8224,7 +8224,7 @@
         </is>
       </c>
       <c r="Y71">
-        <v>0.9012573480927378</v>
+        <v>0.8883822431199844</v>
       </c>
       <c r="Z71">
         <v>0</v>
@@ -8232,22 +8232,22 @@
     </row>
     <row r="72">
       <c r="A72">
-        <v>0.7000000000000001</v>
+        <v>0.7100000000000001</v>
       </c>
       <c r="B72">
-        <v>0.1234822801865788</v>
+        <v>0.1242102801865788</v>
       </c>
       <c r="C72">
-        <v>-479.8156607895162</v>
+        <v>-686.1449264296953</v>
       </c>
       <c r="D72">
-        <v>7888.124339210483</v>
+        <v>7814.887073570305</v>
       </c>
       <c r="E72">
-        <v>9168.84</v>
+        <v>9301.932000000001</v>
       </c>
       <c r="F72">
-        <v>9316.440000000001</v>
+        <v>9449.532000000001</v>
       </c>
       <c r="G72">
         <v>948.5</v>
@@ -8268,37 +8268,37 @@
         <v>981.6</v>
       </c>
       <c r="M72">
-        <v>1104.929784</v>
+        <v>1120.7144952</v>
       </c>
       <c r="N72">
-        <v>-123.3297840000001</v>
+        <v>-139.1144952000003</v>
       </c>
       <c r="O72">
-        <v>-27.13255248000003</v>
+        <v>-30.60518894400007</v>
       </c>
       <c r="P72">
-        <v>-96.1972315200001</v>
+        <v>-108.5093062560002</v>
       </c>
       <c r="Q72">
-        <v>-52.49723152000017</v>
+        <v>-64.80930625600031</v>
       </c>
       <c r="R72">
-        <v>2.333333333333334</v>
+        <v>2.448275862068967</v>
       </c>
       <c r="S72">
-        <v>0.1889601627593981</v>
+        <v>0.1938967200959291</v>
       </c>
       <c r="T72">
-        <v>3.306239324697416</v>
+        <v>3.420247577273189</v>
       </c>
       <c r="U72">
         <v>0.1186</v>
       </c>
       <c r="V72">
-        <v>0.1954440934863966</v>
+        <v>0.1926913597753205</v>
       </c>
       <c r="W72">
-        <v>0.09542033051251338</v>
+        <v>0.09574680473064699</v>
       </c>
       <c r="X72" t="inlineStr">
         <is>
@@ -8306,7 +8306,7 @@
         </is>
       </c>
       <c r="Y72">
-        <v>0.8883822431199844</v>
+        <v>0.8758698171605479</v>
       </c>
       <c r="Z72">
         <v>0</v>
@@ -8314,22 +8314,22 @@
     </row>
     <row r="73">
       <c r="A73">
-        <v>0.71</v>
+        <v>0.72</v>
       </c>
       <c r="B73">
-        <v>0.1242102801865788</v>
+        <v>0.1249382801865788</v>
       </c>
       <c r="C73">
-        <v>-686.1449264296934</v>
+        <v>-891.1267599735384</v>
       </c>
       <c r="D73">
-        <v>7814.887073570305</v>
+        <v>7742.997240026461</v>
       </c>
       <c r="E73">
-        <v>9301.931999999999</v>
+        <v>9435.023999999999</v>
       </c>
       <c r="F73">
-        <v>9449.531999999999</v>
+        <v>9582.624</v>
       </c>
       <c r="G73">
         <v>948.5</v>
@@ -8350,37 +8350,37 @@
         <v>981.6</v>
       </c>
       <c r="M73">
-        <v>1120.7144952</v>
+        <v>1136.4992064</v>
       </c>
       <c r="N73">
-        <v>-139.1144952000001</v>
+        <v>-154.8992064</v>
       </c>
       <c r="O73">
-        <v>-30.60518894400002</v>
+        <v>-34.077825408</v>
       </c>
       <c r="P73">
-        <v>-108.5093062560001</v>
+        <v>-120.821380992</v>
       </c>
       <c r="Q73">
-        <v>-64.80930625600013</v>
+        <v>-77.1213809920001</v>
       </c>
       <c r="R73">
-        <v>2.448275862068965</v>
+        <v>2.571428571428571</v>
       </c>
       <c r="S73">
-        <v>0.1938967200959291</v>
+        <v>0.1991858886707837</v>
       </c>
       <c r="T73">
-        <v>3.420247577273188</v>
+        <v>3.542399276461516</v>
       </c>
       <c r="U73">
         <v>0.1186</v>
       </c>
       <c r="V73">
-        <v>0.1926913597753206</v>
+        <v>0.1900150908895523</v>
       </c>
       <c r="W73">
-        <v>0.09574680473064699</v>
+        <v>0.09606421022049912</v>
       </c>
       <c r="X73" t="inlineStr">
         <is>
@@ -8388,7 +8388,7 @@
         </is>
       </c>
       <c r="Y73">
-        <v>0.8758698171605481</v>
+        <v>0.8637049585888739</v>
       </c>
       <c r="Z73">
         <v>0</v>
@@ -8396,22 +8396,22 @@
     </row>
     <row r="74">
       <c r="A74">
-        <v>0.72</v>
+        <v>0.73</v>
       </c>
       <c r="B74">
-        <v>0.1249382801865788</v>
+        <v>0.1256662801865788</v>
       </c>
       <c r="C74">
-        <v>-891.1267599735384</v>
+        <v>-1094.798007906089</v>
       </c>
       <c r="D74">
-        <v>7742.997240026461</v>
+        <v>7672.417992093911</v>
       </c>
       <c r="E74">
-        <v>9435.023999999999</v>
+        <v>9568.116</v>
       </c>
       <c r="F74">
-        <v>9582.624</v>
+        <v>9715.716</v>
       </c>
       <c r="G74">
         <v>948.5</v>
@@ -8432,37 +8432,37 @@
         <v>981.6</v>
       </c>
       <c r="M74">
-        <v>1136.4992064</v>
+        <v>1152.2839176</v>
       </c>
       <c r="N74">
-        <v>-154.8992064</v>
+        <v>-170.6839176000002</v>
       </c>
       <c r="O74">
-        <v>-34.077825408</v>
+        <v>-37.55046187200004</v>
       </c>
       <c r="P74">
-        <v>-120.821380992</v>
+        <v>-133.1334557280002</v>
       </c>
       <c r="Q74">
-        <v>-77.1213809920001</v>
+        <v>-89.43345572800024</v>
       </c>
       <c r="R74">
-        <v>2.571428571428571</v>
+        <v>2.703703703703703</v>
       </c>
       <c r="S74">
-        <v>0.1991858886707837</v>
+        <v>0.2048668475104423</v>
       </c>
       <c r="T74">
-        <v>3.542399276461516</v>
+        <v>3.673599249663794</v>
       </c>
       <c r="U74">
         <v>0.1186</v>
       </c>
       <c r="V74">
-        <v>0.1900150908895523</v>
+        <v>0.1874121444390104</v>
       </c>
       <c r="W74">
-        <v>0.09606421022049912</v>
+        <v>0.09637291966953337</v>
       </c>
       <c r="X74" t="inlineStr">
         <is>
@@ -8470,7 +8470,7 @@
         </is>
       </c>
       <c r="Y74">
-        <v>0.8637049585888739</v>
+        <v>0.8518733838136836</v>
       </c>
       <c r="Z74">
         <v>0</v>
@@ -8478,22 +8478,22 @@
     </row>
     <row r="75">
       <c r="A75">
-        <v>0.73</v>
+        <v>0.74</v>
       </c>
       <c r="B75">
-        <v>0.1256662801865788</v>
+        <v>0.1263942801865788</v>
       </c>
       <c r="C75">
-        <v>-1094.798007906089</v>
+        <v>-1297.194185390072</v>
       </c>
       <c r="D75">
-        <v>7672.417992093911</v>
+        <v>7603.113814609929</v>
       </c>
       <c r="E75">
-        <v>9568.116</v>
+        <v>9701.208000000001</v>
       </c>
       <c r="F75">
-        <v>9715.716</v>
+        <v>9848.808000000001</v>
       </c>
       <c r="G75">
         <v>948.5</v>
@@ -8514,37 +8514,37 @@
         <v>981.6</v>
       </c>
       <c r="M75">
-        <v>1152.2839176</v>
+        <v>1168.0686288</v>
       </c>
       <c r="N75">
-        <v>-170.6839176000002</v>
+        <v>-186.4686288000001</v>
       </c>
       <c r="O75">
-        <v>-37.55046187200004</v>
+        <v>-41.02309833600003</v>
       </c>
       <c r="P75">
-        <v>-133.1334557280002</v>
+        <v>-145.4455304640001</v>
       </c>
       <c r="Q75">
-        <v>-89.43345572800024</v>
+        <v>-101.7455304640002</v>
       </c>
       <c r="R75">
-        <v>2.703703703703703</v>
+        <v>2.846153846153846</v>
       </c>
       <c r="S75">
-        <v>0.2048668475104423</v>
+        <v>0.2109848031839209</v>
       </c>
       <c r="T75">
-        <v>3.673599249663794</v>
+        <v>3.814891528497017</v>
       </c>
       <c r="U75">
         <v>0.1186</v>
       </c>
       <c r="V75">
-        <v>0.1874121444390104</v>
+        <v>0.1848795478925373</v>
       </c>
       <c r="W75">
-        <v>0.09637291966953337</v>
+        <v>0.09667328561994508</v>
       </c>
       <c r="X75" t="inlineStr">
         <is>
@@ -8552,7 +8552,7 @@
         </is>
       </c>
       <c r="Y75">
-        <v>0.8518733838136836</v>
+        <v>0.8403615813297149</v>
       </c>
       <c r="Z75">
         <v>0</v>
@@ -8560,22 +8560,22 @@
     </row>
     <row r="76">
       <c r="A76">
-        <v>0.74</v>
+        <v>0.75</v>
       </c>
       <c r="B76">
-        <v>0.1263942801865788</v>
+        <v>0.1271222801865788</v>
       </c>
       <c r="C76">
-        <v>-1297.194185390072</v>
+        <v>-1498.349535856105</v>
       </c>
       <c r="D76">
-        <v>7603.113814609929</v>
+        <v>7535.050464143896</v>
       </c>
       <c r="E76">
-        <v>9701.208000000001</v>
+        <v>9834.300000000001</v>
       </c>
       <c r="F76">
-        <v>9848.808000000001</v>
+        <v>9981.900000000001</v>
       </c>
       <c r="G76">
         <v>948.5</v>
@@ -8596,37 +8596,37 @@
         <v>981.6</v>
       </c>
       <c r="M76">
-        <v>1168.0686288</v>
+        <v>1183.85334</v>
       </c>
       <c r="N76">
-        <v>-186.4686288000001</v>
+        <v>-202.2533400000003</v>
       </c>
       <c r="O76">
-        <v>-41.02309833600003</v>
+        <v>-44.49573480000007</v>
       </c>
       <c r="P76">
-        <v>-145.4455304640001</v>
+        <v>-157.7576052000003</v>
       </c>
       <c r="Q76">
-        <v>-101.7455304640002</v>
+        <v>-114.0576052000003</v>
       </c>
       <c r="R76">
-        <v>2.846153846153846</v>
+        <v>3</v>
       </c>
       <c r="S76">
-        <v>0.2109848031839209</v>
+        <v>0.2175921953112777</v>
       </c>
       <c r="T76">
-        <v>3.814891528497017</v>
+        <v>3.967487189636898</v>
       </c>
       <c r="U76">
         <v>0.1186</v>
       </c>
       <c r="V76">
-        <v>0.1848795478925373</v>
+        <v>0.1824144872539701</v>
       </c>
       <c r="W76">
-        <v>0.09667328561994508</v>
+        <v>0.09696564181167915</v>
       </c>
       <c r="X76" t="inlineStr">
         <is>
@@ -8634,7 +8634,7 @@
         </is>
       </c>
       <c r="Y76">
-        <v>0.8403615813297149</v>
+        <v>0.8291567602453187</v>
       </c>
       <c r="Z76">
         <v>0</v>
@@ -8642,22 +8642,22 @@
     </row>
     <row r="77">
       <c r="A77">
-        <v>0.75</v>
+        <v>0.76</v>
       </c>
       <c r="B77">
-        <v>0.1271222801865788</v>
+        <v>0.1278502801865788</v>
       </c>
       <c r="C77">
-        <v>-1498.349535856105</v>
+        <v>-1698.29708742062</v>
       </c>
       <c r="D77">
-        <v>7535.050464143896</v>
+        <v>7468.19491257938</v>
       </c>
       <c r="E77">
-        <v>9834.300000000001</v>
+        <v>9967.392</v>
       </c>
       <c r="F77">
-        <v>9981.900000000001</v>
+        <v>10114.992</v>
       </c>
       <c r="G77">
         <v>948.5</v>
@@ -8678,37 +8678,37 @@
         <v>981.6</v>
       </c>
       <c r="M77">
-        <v>1183.85334</v>
+        <v>1199.6380512</v>
       </c>
       <c r="N77">
-        <v>-202.2533400000003</v>
+        <v>-218.0380512</v>
       </c>
       <c r="O77">
-        <v>-44.49573480000007</v>
+        <v>-47.96837126400001</v>
       </c>
       <c r="P77">
-        <v>-157.7576052000003</v>
+        <v>-170.069679936</v>
       </c>
       <c r="Q77">
-        <v>-114.0576052000003</v>
+        <v>-126.3696799360001</v>
       </c>
       <c r="R77">
-        <v>3</v>
+        <v>3.166666666666667</v>
       </c>
       <c r="S77">
-        <v>0.2175921953112777</v>
+        <v>0.2247502034492476</v>
       </c>
       <c r="T77">
-        <v>3.967487189636898</v>
+        <v>4.132799155871769</v>
       </c>
       <c r="U77">
         <v>0.1186</v>
       </c>
       <c r="V77">
-        <v>0.1824144872539701</v>
+        <v>0.1800142966322074</v>
       </c>
       <c r="W77">
-        <v>0.09696564181167915</v>
+        <v>0.09725030441942022</v>
       </c>
       <c r="X77" t="inlineStr">
         <is>
@@ -8716,7 +8716,7 @@
         </is>
       </c>
       <c r="Y77">
-        <v>0.8291567602453187</v>
+        <v>0.8182468028736699</v>
       </c>
       <c r="Z77">
         <v>0</v>
@@ -8724,22 +8724,22 @@
     </row>
     <row r="78">
       <c r="A78">
-        <v>0.76</v>
+        <v>0.77</v>
       </c>
       <c r="B78">
-        <v>0.1278502801865788</v>
+        <v>0.1285782801865788</v>
       </c>
       <c r="C78">
-        <v>-1698.29708742062</v>
+        <v>-1897.068706326734</v>
       </c>
       <c r="D78">
-        <v>7468.19491257938</v>
+        <v>7402.515293673267</v>
       </c>
       <c r="E78">
-        <v>9967.392</v>
+        <v>10100.484</v>
       </c>
       <c r="F78">
-        <v>10114.992</v>
+        <v>10248.084</v>
       </c>
       <c r="G78">
         <v>948.5</v>
@@ -8760,37 +8760,37 @@
         <v>981.6</v>
       </c>
       <c r="M78">
-        <v>1199.6380512</v>
+        <v>1215.4227624</v>
       </c>
       <c r="N78">
-        <v>-218.0380512</v>
+        <v>-233.8227624000002</v>
       </c>
       <c r="O78">
-        <v>-47.96837126400001</v>
+        <v>-51.44100772800005</v>
       </c>
       <c r="P78">
-        <v>-170.069679936</v>
+        <v>-182.3817546720002</v>
       </c>
       <c r="Q78">
-        <v>-126.3696799360001</v>
+        <v>-138.6817546720002</v>
       </c>
       <c r="R78">
-        <v>3.166666666666667</v>
+        <v>3.347826086956522</v>
       </c>
       <c r="S78">
-        <v>0.2247502034492476</v>
+        <v>0.2325306470774758</v>
       </c>
       <c r="T78">
-        <v>4.132799155871769</v>
+        <v>4.312486075692281</v>
       </c>
       <c r="U78">
         <v>0.1186</v>
       </c>
       <c r="V78">
-        <v>0.1800142966322074</v>
+        <v>0.1776764486239969</v>
       </c>
       <c r="W78">
-        <v>0.09725030441942022</v>
+        <v>0.09752757319319398</v>
       </c>
       <c r="X78" t="inlineStr">
         <is>
@@ -8798,7 +8798,7 @@
         </is>
       </c>
       <c r="Y78">
-        <v>0.8182468028736699</v>
+        <v>0.8076202210181677</v>
       </c>
       <c r="Z78">
         <v>0</v>
@@ -8806,22 +8806,22 @@
     </row>
     <row r="79">
       <c r="A79">
-        <v>0.77</v>
+        <v>0.78</v>
       </c>
       <c r="B79">
-        <v>0.1285782801865788</v>
+        <v>0.1962088259022571</v>
       </c>
       <c r="C79">
-        <v>-1897.068706326734</v>
+        <v>-5358.663179347267</v>
       </c>
       <c r="D79">
-        <v>7402.515293673267</v>
+        <v>4074.012820652734</v>
       </c>
       <c r="E79">
-        <v>10100.484</v>
+        <v>10233.576</v>
       </c>
       <c r="F79">
-        <v>10248.084</v>
+        <v>10381.176</v>
       </c>
       <c r="G79">
         <v>948.5</v>
@@ -8842,45 +8842,45 @@
         <v>981.6</v>
       </c>
       <c r="M79">
-        <v>1215.4227624</v>
+        <v>2084.5401408</v>
       </c>
       <c r="N79">
-        <v>-233.8227624000002</v>
+        <v>-1102.9401408</v>
       </c>
       <c r="O79">
-        <v>-51.44100772800005</v>
+        <v>-242.6468309760001</v>
       </c>
       <c r="P79">
-        <v>-182.3817546720002</v>
+        <v>-860.2933098240003</v>
       </c>
       <c r="Q79">
-        <v>-138.6817546720002</v>
+        <v>-816.5933098240004</v>
       </c>
       <c r="R79">
-        <v>3.347826086956522</v>
+        <v>3.545454545454546</v>
       </c>
       <c r="S79">
-        <v>0.2325306470774758</v>
+        <v>0.2536845206522624</v>
       </c>
       <c r="T79">
-        <v>4.312486075692281</v>
+        <v>4.801028190583427</v>
       </c>
       <c r="U79">
-        <v>0.1186</v>
+        <v>0.2008</v>
       </c>
       <c r="V79">
-        <v>0.1776764486239969</v>
+        <v>0.1035969496452692</v>
       </c>
       <c r="W79">
-        <v>0.09752757319319398</v>
+        <v>0.1799977325112299</v>
       </c>
       <c r="X79" t="inlineStr">
         <is>
-          <t>Caa/CCC</t>
+          <t>C2/C</t>
         </is>
       </c>
       <c r="Y79">
-        <v>0.8076202210181677</v>
+        <v>0.4708952256603145</v>
       </c>
       <c r="Z79">
         <v>0</v>
@@ -8888,22 +8888,22 @@
     </row>
     <row r="80">
       <c r="A80">
-        <v>0.78</v>
+        <v>0.79</v>
       </c>
       <c r="B80">
-        <v>0.1962088259022571</v>
+        <v>0.1977588259022571</v>
       </c>
       <c r="C80">
-        <v>-5358.663179347267</v>
+        <v>-5533.310645668607</v>
       </c>
       <c r="D80">
-        <v>4074.012820652734</v>
+        <v>4032.457354331394</v>
       </c>
       <c r="E80">
-        <v>10233.576</v>
+        <v>10366.668</v>
       </c>
       <c r="F80">
-        <v>10381.176</v>
+        <v>10514.268</v>
       </c>
       <c r="G80">
         <v>948.5</v>
@@ -8924,37 +8924,37 @@
         <v>981.6</v>
       </c>
       <c r="M80">
-        <v>2084.5401408</v>
+        <v>2111.2650144</v>
       </c>
       <c r="N80">
-        <v>-1102.9401408</v>
+        <v>-1129.6650144</v>
       </c>
       <c r="O80">
-        <v>-242.6468309760001</v>
+        <v>-248.5263031680001</v>
       </c>
       <c r="P80">
-        <v>-860.2933098240003</v>
+        <v>-881.1387112320003</v>
       </c>
       <c r="Q80">
-        <v>-816.5933098240004</v>
+        <v>-837.4387112320004</v>
       </c>
       <c r="R80">
-        <v>3.545454545454546</v>
+        <v>3.761904761904763</v>
       </c>
       <c r="S80">
-        <v>0.2536845206522624</v>
+        <v>0.2635837835404654</v>
       </c>
       <c r="T80">
-        <v>4.801028190583427</v>
+        <v>5.02964858061121</v>
       </c>
       <c r="U80">
         <v>0.2008</v>
       </c>
       <c r="V80">
-        <v>0.1035969496452692</v>
+        <v>0.1022855958522911</v>
       </c>
       <c r="W80">
-        <v>0.1799977325112299</v>
+        <v>0.1802610523528599</v>
       </c>
       <c r="X80" t="inlineStr">
         <is>
@@ -8962,7 +8962,7 @@
         </is>
       </c>
       <c r="Y80">
-        <v>0.4708952256603145</v>
+        <v>0.4649345266013232</v>
       </c>
       <c r="Z80">
         <v>0</v>
@@ -8970,22 +8970,22 @@
     </row>
     <row r="81">
       <c r="A81">
-        <v>0.79</v>
+        <v>0.8</v>
       </c>
       <c r="B81">
-        <v>0.1977588259022571</v>
+        <v>0.1993088259022571</v>
       </c>
       <c r="C81">
-        <v>-5533.310645668607</v>
+        <v>-5707.118929325115</v>
       </c>
       <c r="D81">
-        <v>4032.457354331394</v>
+        <v>3991.741070674885</v>
       </c>
       <c r="E81">
-        <v>10366.668</v>
+        <v>10499.76</v>
       </c>
       <c r="F81">
-        <v>10514.268</v>
+        <v>10647.36</v>
       </c>
       <c r="G81">
         <v>948.5</v>
@@ -9006,37 +9006,37 @@
         <v>981.6</v>
       </c>
       <c r="M81">
-        <v>2111.2650144</v>
+        <v>2137.989888</v>
       </c>
       <c r="N81">
-        <v>-1129.6650144</v>
+        <v>-1156.389888</v>
       </c>
       <c r="O81">
-        <v>-248.5263031680001</v>
+        <v>-254.40577536</v>
       </c>
       <c r="P81">
-        <v>-881.1387112320003</v>
+        <v>-901.9841126400001</v>
       </c>
       <c r="Q81">
-        <v>-837.4387112320004</v>
+        <v>-858.2841126400002</v>
       </c>
       <c r="R81">
-        <v>3.761904761904763</v>
+        <v>4.000000000000001</v>
       </c>
       <c r="S81">
-        <v>0.2635837835404654</v>
+        <v>0.2744729727174887</v>
       </c>
       <c r="T81">
-        <v>5.02964858061121</v>
+        <v>5.28113100964177</v>
       </c>
       <c r="U81">
         <v>0.2008</v>
       </c>
       <c r="V81">
-        <v>0.1022855958522911</v>
+        <v>0.1010070259041375</v>
       </c>
       <c r="W81">
-        <v>0.1802610523528599</v>
+        <v>0.1805177891984492</v>
       </c>
       <c r="X81" t="inlineStr">
         <is>
@@ -9044,7 +9044,7 @@
         </is>
       </c>
       <c r="Y81">
-        <v>0.4649345266013232</v>
+        <v>0.4591228450188067</v>
       </c>
       <c r="Z81">
         <v>0</v>
@@ -9052,22 +9052,22 @@
     </row>
     <row r="82">
       <c r="A82">
-        <v>0.8</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="B82">
-        <v>0.1993088259022571</v>
+        <v>0.2008588259022571</v>
       </c>
       <c r="C82">
-        <v>-5707.118929325115</v>
+        <v>-5880.113196245711</v>
       </c>
       <c r="D82">
-        <v>3991.741070674885</v>
+        <v>3951.83880375429</v>
       </c>
       <c r="E82">
-        <v>10499.76</v>
+        <v>10632.852</v>
       </c>
       <c r="F82">
-        <v>10647.36</v>
+        <v>10780.452</v>
       </c>
       <c r="G82">
         <v>948.5</v>
@@ -9088,37 +9088,37 @@
         <v>981.6</v>
       </c>
       <c r="M82">
-        <v>2137.989888</v>
+        <v>2164.7147616</v>
       </c>
       <c r="N82">
-        <v>-1156.389888</v>
+        <v>-1183.1147616</v>
       </c>
       <c r="O82">
-        <v>-254.40577536</v>
+        <v>-260.285247552</v>
       </c>
       <c r="P82">
-        <v>-901.9841126400001</v>
+        <v>-922.8295140480002</v>
       </c>
       <c r="Q82">
-        <v>-858.2841126400002</v>
+        <v>-879.1295140480003</v>
       </c>
       <c r="R82">
-        <v>4.000000000000001</v>
+        <v>4.263157894736843</v>
       </c>
       <c r="S82">
-        <v>0.2744729727174887</v>
+        <v>0.2865083923341986</v>
       </c>
       <c r="T82">
-        <v>5.28113100964177</v>
+        <v>5.559085273307127</v>
       </c>
       <c r="U82">
         <v>0.2008</v>
       </c>
       <c r="V82">
-        <v>0.1010070259041375</v>
+        <v>0.09976002558433331</v>
       </c>
       <c r="W82">
-        <v>0.1805177891984492</v>
+        <v>0.1807681868626659</v>
       </c>
       <c r="X82" t="inlineStr">
         <is>
@@ -9126,7 +9126,7 @@
         </is>
       </c>
       <c r="Y82">
-        <v>0.4591228450188067</v>
+        <v>0.4534546617469696</v>
       </c>
       <c r="Z82">
         <v>0</v>
@@ -9134,22 +9134,22 @@
     </row>
     <row r="83">
       <c r="A83">
-        <v>0.8100000000000001</v>
+        <v>0.8200000000000001</v>
       </c>
       <c r="B83">
-        <v>0.2008588259022571</v>
+        <v>0.2024088259022571</v>
       </c>
       <c r="C83">
-        <v>-5880.113196245711</v>
+        <v>-6052.317616063239</v>
       </c>
       <c r="D83">
-        <v>3951.83880375429</v>
+        <v>3912.726383936763</v>
       </c>
       <c r="E83">
-        <v>10632.852</v>
+        <v>10765.944</v>
       </c>
       <c r="F83">
-        <v>10780.452</v>
+        <v>10913.544</v>
       </c>
       <c r="G83">
         <v>948.5</v>
@@ -9170,37 +9170,37 @@
         <v>981.6</v>
       </c>
       <c r="M83">
-        <v>2164.7147616</v>
+        <v>2191.4396352</v>
       </c>
       <c r="N83">
-        <v>-1183.1147616</v>
+        <v>-1209.8396352</v>
       </c>
       <c r="O83">
-        <v>-260.285247552</v>
+        <v>-266.1647197440001</v>
       </c>
       <c r="P83">
-        <v>-922.8295140480002</v>
+        <v>-943.6749154560003</v>
       </c>
       <c r="Q83">
-        <v>-879.1295140480003</v>
+        <v>-899.9749154560004</v>
       </c>
       <c r="R83">
-        <v>4.263157894736843</v>
+        <v>4.555555555555557</v>
       </c>
       <c r="S83">
-        <v>0.2865083923341986</v>
+        <v>0.2998810807972097</v>
       </c>
       <c r="T83">
-        <v>5.559085273307127</v>
+        <v>5.867923344046412</v>
       </c>
       <c r="U83">
         <v>0.2008</v>
       </c>
       <c r="V83">
-        <v>0.09976002558433331</v>
+        <v>0.09854343990647559</v>
       </c>
       <c r="W83">
-        <v>0.1807681868626659</v>
+        <v>0.1810124772667797</v>
       </c>
       <c r="X83" t="inlineStr">
         <is>
@@ -9208,7 +9208,7 @@
         </is>
       </c>
       <c r="Y83">
-        <v>0.4534546617469696</v>
+        <v>0.4479247268476162</v>
       </c>
       <c r="Z83">
         <v>0</v>
@@ -9216,22 +9216,22 @@
     </row>
     <row r="84">
       <c r="A84">
-        <v>0.8200000000000001</v>
+        <v>0.8300000000000001</v>
       </c>
       <c r="B84">
-        <v>0.2024088259022571</v>
+        <v>0.2039588259022571</v>
       </c>
       <c r="C84">
-        <v>-6052.317616063239</v>
+        <v>-6223.75541093434</v>
       </c>
       <c r="D84">
-        <v>3912.726383936763</v>
+        <v>3874.380589065662</v>
       </c>
       <c r="E84">
-        <v>10765.944</v>
+        <v>10899.036</v>
       </c>
       <c r="F84">
-        <v>10913.544</v>
+        <v>11046.636</v>
       </c>
       <c r="G84">
         <v>948.5</v>
@@ -9252,37 +9252,37 @@
         <v>981.6</v>
       </c>
       <c r="M84">
-        <v>2191.4396352</v>
+        <v>2218.1645088</v>
       </c>
       <c r="N84">
-        <v>-1209.8396352</v>
+        <v>-1236.564508800001</v>
       </c>
       <c r="O84">
-        <v>-266.1647197440001</v>
+        <v>-272.0441919360001</v>
       </c>
       <c r="P84">
-        <v>-943.6749154560003</v>
+        <v>-964.5203168640005</v>
       </c>
       <c r="Q84">
-        <v>-899.9749154560004</v>
+        <v>-920.8203168640006</v>
       </c>
       <c r="R84">
-        <v>4.555555555555557</v>
+        <v>4.882352941176473</v>
       </c>
       <c r="S84">
-        <v>0.2998810807972097</v>
+        <v>0.3148270267264573</v>
       </c>
       <c r="T84">
-        <v>5.867923344046412</v>
+        <v>6.213095305460907</v>
       </c>
       <c r="U84">
         <v>0.2008</v>
       </c>
       <c r="V84">
-        <v>0.09854343990647559</v>
+        <v>0.0973561695461566</v>
       </c>
       <c r="W84">
-        <v>0.1810124772667797</v>
+        <v>0.1812508811551318</v>
       </c>
       <c r="X84" t="inlineStr">
         <is>
@@ -9290,7 +9290,7 @@
         </is>
       </c>
       <c r="Y84">
-        <v>0.4479247268476162</v>
+        <v>0.4425280433916208</v>
       </c>
       <c r="Z84">
         <v>0</v>
@@ -9298,22 +9298,22 @@
     </row>
     <row r="85">
       <c r="A85">
-        <v>0.8300000000000001</v>
+        <v>0.8400000000000001</v>
       </c>
       <c r="B85">
-        <v>0.2039588259022571</v>
+        <v>0.2055088259022571</v>
       </c>
       <c r="C85">
-        <v>-6223.75541093434</v>
+        <v>-6394.4489015165</v>
       </c>
       <c r="D85">
-        <v>3874.380589065662</v>
+        <v>3836.779098483501</v>
       </c>
       <c r="E85">
-        <v>10899.036</v>
+        <v>11032.128</v>
       </c>
       <c r="F85">
-        <v>11046.636</v>
+        <v>11179.728</v>
       </c>
       <c r="G85">
         <v>948.5</v>
@@ -9334,37 +9334,37 @@
         <v>981.6</v>
       </c>
       <c r="M85">
-        <v>2218.1645088</v>
+        <v>2244.8893824</v>
       </c>
       <c r="N85">
-        <v>-1236.564508800001</v>
+        <v>-1263.2893824</v>
       </c>
       <c r="O85">
-        <v>-272.0441919360001</v>
+        <v>-277.923664128</v>
       </c>
       <c r="P85">
-        <v>-964.5203168640005</v>
+        <v>-985.3657182720002</v>
       </c>
       <c r="Q85">
-        <v>-920.8203168640006</v>
+        <v>-941.6657182720003</v>
       </c>
       <c r="R85">
-        <v>4.882352941176473</v>
+        <v>5.250000000000004</v>
       </c>
       <c r="S85">
-        <v>0.3148270267264573</v>
+        <v>0.3316412158968609</v>
       </c>
       <c r="T85">
-        <v>6.213095305460907</v>
+        <v>6.601413762052214</v>
       </c>
       <c r="U85">
         <v>0.2008</v>
       </c>
       <c r="V85">
-        <v>0.0973561695461566</v>
+        <v>0.09619716752774998</v>
       </c>
       <c r="W85">
-        <v>0.1812508811551318</v>
+        <v>0.1814836087604278</v>
       </c>
       <c r="X85" t="inlineStr">
         <is>
@@ -9372,7 +9372,7 @@
         </is>
       </c>
       <c r="Y85">
-        <v>0.4425280433916208</v>
+        <v>0.4372598523988634</v>
       </c>
       <c r="Z85">
         <v>0</v>
@@ -9380,22 +9380,22 @@
     </row>
     <row r="86">
       <c r="A86">
-        <v>0.84</v>
+        <v>0.85</v>
       </c>
       <c r="B86">
-        <v>0.2055088259022571</v>
+        <v>0.2070588259022571</v>
       </c>
       <c r="C86">
-        <v>-6394.4489015165</v>
+        <v>-6564.419550293553</v>
       </c>
       <c r="D86">
-        <v>3836.779098483501</v>
+        <v>3799.900449706447</v>
       </c>
       <c r="E86">
-        <v>11032.128</v>
+        <v>11165.22</v>
       </c>
       <c r="F86">
-        <v>11179.728</v>
+        <v>11312.82</v>
       </c>
       <c r="G86">
         <v>948.5</v>
@@ -9416,37 +9416,37 @@
         <v>981.6</v>
       </c>
       <c r="M86">
-        <v>2244.8893824</v>
+        <v>2271.614256</v>
       </c>
       <c r="N86">
-        <v>-1263.2893824</v>
+        <v>-1290.014256</v>
       </c>
       <c r="O86">
-        <v>-277.923664128</v>
+        <v>-283.80313632</v>
       </c>
       <c r="P86">
-        <v>-985.3657182720002</v>
+        <v>-1006.21111968</v>
       </c>
       <c r="Q86">
-        <v>-941.6657182720003</v>
+        <v>-962.51111968</v>
       </c>
       <c r="R86">
-        <v>5.249999999999999</v>
+        <v>5.666666666666666</v>
       </c>
       <c r="S86">
-        <v>0.3316412158968607</v>
+        <v>0.3506972969566515</v>
       </c>
       <c r="T86">
-        <v>6.601413762052211</v>
+        <v>7.041508012855691</v>
       </c>
       <c r="U86">
         <v>0.2008</v>
       </c>
       <c r="V86">
-        <v>0.09619716752774998</v>
+        <v>0.09506543614507058</v>
       </c>
       <c r="W86">
-        <v>0.1814836087604278</v>
+        <v>0.1817108604220698</v>
       </c>
       <c r="X86" t="inlineStr">
         <is>
@@ -9454,7 +9454,7 @@
         </is>
       </c>
       <c r="Y86">
-        <v>0.4372598523988634</v>
+        <v>0.4321156188412298</v>
       </c>
       <c r="Z86">
         <v>0</v>
@@ -9462,22 +9462,22 @@
     </row>
     <row r="87">
       <c r="A87">
-        <v>0.85</v>
+        <v>0.86</v>
       </c>
       <c r="B87">
-        <v>0.2070588259022571</v>
+        <v>0.2086088259022571</v>
       </c>
       <c r="C87">
-        <v>-6564.419550293553</v>
+        <v>-6733.688002426319</v>
       </c>
       <c r="D87">
-        <v>3799.900449706447</v>
+        <v>3763.723997573681</v>
       </c>
       <c r="E87">
-        <v>11165.22</v>
+        <v>11298.312</v>
       </c>
       <c r="F87">
-        <v>11312.82</v>
+        <v>11445.912</v>
       </c>
       <c r="G87">
         <v>948.5</v>
@@ -9498,37 +9498,37 @@
         <v>981.6</v>
       </c>
       <c r="M87">
-        <v>2271.614256</v>
+        <v>2298.3391296</v>
       </c>
       <c r="N87">
-        <v>-1290.014256</v>
+        <v>-1316.7391296</v>
       </c>
       <c r="O87">
-        <v>-283.80313632</v>
+        <v>-289.682608512</v>
       </c>
       <c r="P87">
-        <v>-1006.21111968</v>
+        <v>-1027.056521088</v>
       </c>
       <c r="Q87">
-        <v>-962.51111968</v>
+        <v>-983.356521088</v>
       </c>
       <c r="R87">
-        <v>5.666666666666666</v>
+        <v>6.142857142857142</v>
       </c>
       <c r="S87">
-        <v>0.3506972969566515</v>
+        <v>0.372475675310698</v>
       </c>
       <c r="T87">
-        <v>7.041508012855691</v>
+        <v>7.544472870916812</v>
       </c>
       <c r="U87">
         <v>0.2008</v>
       </c>
       <c r="V87">
-        <v>0.09506543614507058</v>
+        <v>0.09396002409687208</v>
       </c>
       <c r="W87">
-        <v>0.1817108604220698</v>
+        <v>0.1819328271613481</v>
       </c>
       <c r="X87" t="inlineStr">
         <is>
@@ -9536,7 +9536,7 @@
         </is>
       </c>
       <c r="Y87">
-        <v>0.4321156188412298</v>
+        <v>0.4270910186221458</v>
       </c>
       <c r="Z87">
         <v>0</v>
@@ -9544,22 +9544,22 @@
     </row>
     <row r="88">
       <c r="A88">
-        <v>0.86</v>
+        <v>0.87</v>
       </c>
       <c r="B88">
-        <v>0.2086088259022571</v>
+        <v>0.2101588259022571</v>
       </c>
       <c r="C88">
-        <v>-6733.688002426319</v>
+        <v>-6902.274124291785</v>
       </c>
       <c r="D88">
-        <v>3763.723997573681</v>
+        <v>3728.229875708216</v>
       </c>
       <c r="E88">
-        <v>11298.312</v>
+        <v>11431.404</v>
       </c>
       <c r="F88">
-        <v>11445.912</v>
+        <v>11579.004</v>
       </c>
       <c r="G88">
         <v>948.5</v>
@@ -9580,37 +9580,37 @@
         <v>981.6</v>
       </c>
       <c r="M88">
-        <v>2298.3391296</v>
+        <v>2325.0640032</v>
       </c>
       <c r="N88">
-        <v>-1316.7391296</v>
+        <v>-1343.4640032</v>
       </c>
       <c r="O88">
-        <v>-289.682608512</v>
+        <v>-295.562080704</v>
       </c>
       <c r="P88">
-        <v>-1027.056521088</v>
+        <v>-1047.901922496</v>
       </c>
       <c r="Q88">
-        <v>-983.356521088</v>
+        <v>-1004.201922496</v>
       </c>
       <c r="R88">
-        <v>6.142857142857142</v>
+        <v>6.692307692307692</v>
       </c>
       <c r="S88">
-        <v>0.372475675310698</v>
+        <v>0.3976045734115209</v>
       </c>
       <c r="T88">
-        <v>7.544472870916812</v>
+        <v>8.124816937910413</v>
       </c>
       <c r="U88">
         <v>0.2008</v>
       </c>
       <c r="V88">
-        <v>0.09396002409687208</v>
+        <v>0.09288002381989653</v>
       </c>
       <c r="W88">
-        <v>0.1819328271613481</v>
+        <v>0.1821496912169648</v>
       </c>
       <c r="X88" t="inlineStr">
         <is>
@@ -9618,7 +9618,7 @@
         </is>
       </c>
       <c r="Y88">
-        <v>0.4270910186221458</v>
+        <v>0.4221819264540752</v>
       </c>
       <c r="Z88">
         <v>0</v>
@@ -9626,22 +9626,22 @@
     </row>
     <row r="89">
       <c r="A89">
-        <v>0.87</v>
+        <v>0.88</v>
       </c>
       <c r="B89">
-        <v>0.2101588259022571</v>
+        <v>0.2117088259022571</v>
       </c>
       <c r="C89">
-        <v>-6902.274124291785</v>
+        <v>-7070.197039861956</v>
       </c>
       <c r="D89">
-        <v>3728.229875708216</v>
+        <v>3693.398960138045</v>
       </c>
       <c r="E89">
-        <v>11431.404</v>
+        <v>11564.496</v>
       </c>
       <c r="F89">
-        <v>11579.004</v>
+        <v>11712.096</v>
       </c>
       <c r="G89">
         <v>948.5</v>
@@ -9662,37 +9662,37 @@
         <v>981.6</v>
       </c>
       <c r="M89">
-        <v>2325.0640032</v>
+        <v>2351.7888768</v>
       </c>
       <c r="N89">
-        <v>-1343.4640032</v>
+        <v>-1370.1888768</v>
       </c>
       <c r="O89">
-        <v>-295.562080704</v>
+        <v>-301.4415528960001</v>
       </c>
       <c r="P89">
-        <v>-1047.901922496</v>
+        <v>-1068.747323904</v>
       </c>
       <c r="Q89">
-        <v>-1004.201922496</v>
+        <v>-1025.047323904</v>
       </c>
       <c r="R89">
-        <v>6.692307692307692</v>
+        <v>7.333333333333334</v>
       </c>
       <c r="S89">
-        <v>0.3976045734115209</v>
+        <v>0.4269216211958144</v>
       </c>
       <c r="T89">
-        <v>8.124816937910413</v>
+        <v>8.801885016069615</v>
       </c>
       <c r="U89">
         <v>0.2008</v>
       </c>
       <c r="V89">
-        <v>0.09288002381989653</v>
+        <v>0.09182456900376135</v>
       </c>
       <c r="W89">
-        <v>0.1821496912169648</v>
+        <v>0.1823616265440447</v>
       </c>
       <c r="X89" t="inlineStr">
         <is>
@@ -9700,7 +9700,7 @@
         </is>
       </c>
       <c r="Y89">
-        <v>0.4221819264540752</v>
+        <v>0.4173844045625515</v>
       </c>
       <c r="Z89">
         <v>0</v>
@@ -9708,22 +9708,22 @@
     </row>
     <row r="90">
       <c r="A90">
-        <v>0.88</v>
+        <v>0.89</v>
       </c>
       <c r="B90">
-        <v>0.2117088259022571</v>
+        <v>0.2132588259022571</v>
       </c>
       <c r="C90">
-        <v>-7070.197039861956</v>
+        <v>-7237.475165062398</v>
       </c>
       <c r="D90">
-        <v>3693.398960138045</v>
+        <v>3659.212834937602</v>
       </c>
       <c r="E90">
-        <v>11564.496</v>
+        <v>11697.588</v>
       </c>
       <c r="F90">
-        <v>11712.096</v>
+        <v>11845.188</v>
       </c>
       <c r="G90">
         <v>948.5</v>
@@ -9744,37 +9744,37 @@
         <v>981.6</v>
       </c>
       <c r="M90">
-        <v>2351.7888768</v>
+        <v>2378.5137504</v>
       </c>
       <c r="N90">
-        <v>-1370.1888768</v>
+        <v>-1396.9137504</v>
       </c>
       <c r="O90">
-        <v>-301.4415528960001</v>
+        <v>-307.321025088</v>
       </c>
       <c r="P90">
-        <v>-1068.747323904</v>
+        <v>-1089.592725312</v>
       </c>
       <c r="Q90">
-        <v>-1025.047323904</v>
+        <v>-1045.892725312</v>
       </c>
       <c r="R90">
-        <v>7.333333333333334</v>
+        <v>8.090909090909092</v>
       </c>
       <c r="S90">
-        <v>0.4269216211958144</v>
+        <v>0.4615690413045248</v>
       </c>
       <c r="T90">
-        <v>8.801885016069615</v>
+        <v>9.602056381166854</v>
       </c>
       <c r="U90">
         <v>0.2008</v>
       </c>
       <c r="V90">
-        <v>0.09182456900376135</v>
+        <v>0.09079283227338202</v>
       </c>
       <c r="W90">
-        <v>0.1823616265440447</v>
+        <v>0.1825687992795049</v>
       </c>
       <c r="X90" t="inlineStr">
         <is>
@@ -9782,7 +9782,7 @@
         </is>
       </c>
       <c r="Y90">
-        <v>0.4173844045625515</v>
+        <v>0.4126946921517364</v>
       </c>
       <c r="Z90">
         <v>0</v>
@@ -9790,22 +9790,22 @@
     </row>
     <row r="91">
       <c r="A91">
-        <v>0.89</v>
+        <v>0.9</v>
       </c>
       <c r="B91">
-        <v>0.2132588259022571</v>
+        <v>0.2148088259022571</v>
       </c>
       <c r="C91">
-        <v>-7237.475165062398</v>
+        <v>-7404.126240240126</v>
       </c>
       <c r="D91">
-        <v>3659.212834937602</v>
+        <v>3625.653759759874</v>
       </c>
       <c r="E91">
-        <v>11697.588</v>
+        <v>11830.68</v>
       </c>
       <c r="F91">
-        <v>11845.188</v>
+        <v>11978.28</v>
       </c>
       <c r="G91">
         <v>948.5</v>
@@ -9826,37 +9826,37 @@
         <v>981.6</v>
       </c>
       <c r="M91">
-        <v>2378.5137504</v>
+        <v>2405.238624</v>
       </c>
       <c r="N91">
-        <v>-1396.9137504</v>
+        <v>-1423.638624</v>
       </c>
       <c r="O91">
-        <v>-307.321025088</v>
+        <v>-313.20049728</v>
       </c>
       <c r="P91">
-        <v>-1089.592725312</v>
+        <v>-1110.43812672</v>
       </c>
       <c r="Q91">
-        <v>-1045.892725312</v>
+        <v>-1066.73812672</v>
       </c>
       <c r="R91">
-        <v>8.090909090909092</v>
+        <v>9.000000000000002</v>
       </c>
       <c r="S91">
-        <v>0.4615690413045248</v>
+        <v>0.5031459454349774</v>
       </c>
       <c r="T91">
-        <v>9.602056381166854</v>
+        <v>10.56226201928354</v>
       </c>
       <c r="U91">
         <v>0.2008</v>
       </c>
       <c r="V91">
-        <v>0.09079283227338202</v>
+        <v>0.08978402302589998</v>
       </c>
       <c r="W91">
-        <v>0.1825687992795049</v>
+        <v>0.1827713681763993</v>
       </c>
       <c r="X91" t="inlineStr">
         <is>
@@ -9864,7 +9864,7 @@
         </is>
       </c>
       <c r="Y91">
-        <v>0.4126946921517364</v>
+        <v>0.4081091955722727</v>
       </c>
       <c r="Z91">
         <v>0</v>
@@ -9872,22 +9872,22 @@
     </row>
     <row r="92">
       <c r="A92">
-        <v>0.9</v>
+        <v>0.91</v>
       </c>
       <c r="B92">
-        <v>0.2148088259022571</v>
+        <v>0.2163588259022571</v>
       </c>
       <c r="C92">
-        <v>-7404.126240240126</v>
+        <v>-7570.167360861118</v>
       </c>
       <c r="D92">
-        <v>3625.653759759874</v>
+        <v>3592.704639138884</v>
       </c>
       <c r="E92">
-        <v>11830.68</v>
+        <v>11963.772</v>
       </c>
       <c r="F92">
-        <v>11978.28</v>
+        <v>12111.372</v>
       </c>
       <c r="G92">
         <v>948.5</v>
@@ -9908,37 +9908,37 @@
         <v>981.6</v>
       </c>
       <c r="M92">
-        <v>2405.238624</v>
+        <v>2431.9634976</v>
       </c>
       <c r="N92">
-        <v>-1423.638624</v>
+        <v>-1450.3634976</v>
       </c>
       <c r="O92">
-        <v>-313.20049728</v>
+        <v>-319.0799694720001</v>
       </c>
       <c r="P92">
-        <v>-1110.43812672</v>
+        <v>-1131.283528128</v>
       </c>
       <c r="Q92">
-        <v>-1066.73812672</v>
+        <v>-1087.583528128</v>
       </c>
       <c r="R92">
-        <v>9.000000000000002</v>
+        <v>10.11111111111111</v>
       </c>
       <c r="S92">
-        <v>0.5031459454349774</v>
+        <v>0.5539621615944192</v>
       </c>
       <c r="T92">
-        <v>10.56226201928354</v>
+        <v>11.73584668809282</v>
       </c>
       <c r="U92">
         <v>0.2008</v>
       </c>
       <c r="V92">
-        <v>0.08978402302589998</v>
+        <v>0.08879738541023076</v>
       </c>
       <c r="W92">
-        <v>0.1827713681763993</v>
+        <v>0.1829694850096257</v>
       </c>
       <c r="X92" t="inlineStr">
         <is>
@@ -9946,7 +9946,7 @@
         </is>
       </c>
       <c r="Y92">
-        <v>0.4081091955722727</v>
+        <v>0.4036244791374125</v>
       </c>
       <c r="Z92">
         <v>0</v>
@@ -9954,22 +9954,22 @@
     </row>
     <row r="93">
       <c r="A93">
-        <v>0.91</v>
+        <v>0.92</v>
       </c>
       <c r="B93">
-        <v>0.2163588259022571</v>
+        <v>0.2179088259022571</v>
       </c>
       <c r="C93">
-        <v>-7570.167360861118</v>
+        <v>-7735.615006549084</v>
       </c>
       <c r="D93">
-        <v>3592.704639138884</v>
+        <v>3560.348993450918</v>
       </c>
       <c r="E93">
-        <v>11963.772</v>
+        <v>12096.864</v>
       </c>
       <c r="F93">
-        <v>12111.372</v>
+        <v>12244.464</v>
       </c>
       <c r="G93">
         <v>948.5</v>
@@ -9990,37 +9990,37 @@
         <v>981.6</v>
       </c>
       <c r="M93">
-        <v>2431.9634976</v>
+        <v>2458.6883712</v>
       </c>
       <c r="N93">
-        <v>-1450.3634976</v>
+        <v>-1477.0883712</v>
       </c>
       <c r="O93">
-        <v>-319.0799694720001</v>
+        <v>-324.9594416640001</v>
       </c>
       <c r="P93">
-        <v>-1131.283528128</v>
+        <v>-1152.128929536</v>
       </c>
       <c r="Q93">
-        <v>-1087.583528128</v>
+        <v>-1108.428929536</v>
       </c>
       <c r="R93">
-        <v>10.11111111111111</v>
+        <v>11.50000000000001</v>
       </c>
       <c r="S93">
-        <v>0.5539621615944192</v>
+        <v>0.617482431793722</v>
       </c>
       <c r="T93">
-        <v>11.73584668809282</v>
+        <v>13.20282752410443</v>
       </c>
       <c r="U93">
         <v>0.2008</v>
       </c>
       <c r="V93">
-        <v>0.08879738541023076</v>
+        <v>0.08783219643838042</v>
       </c>
       <c r="W93">
-        <v>0.1829694850096257</v>
+        <v>0.1831632949551732</v>
       </c>
       <c r="X93" t="inlineStr">
         <is>
@@ -10028,7 +10028,7 @@
         </is>
       </c>
       <c r="Y93">
-        <v>0.4036244791374125</v>
+        <v>0.3992372565380927</v>
       </c>
       <c r="Z93">
         <v>0</v>
@@ -10036,22 +10036,22 @@
     </row>
     <row r="94">
       <c r="A94">
-        <v>0.92</v>
+        <v>0.93</v>
       </c>
       <c r="B94">
-        <v>0.2179088259022571</v>
+        <v>0.2194588259022571</v>
       </c>
       <c r="C94">
-        <v>-7735.615006549084</v>
+        <v>-7900.48506856912</v>
       </c>
       <c r="D94">
-        <v>3560.348993450918</v>
+        <v>3528.57093143088</v>
       </c>
       <c r="E94">
-        <v>12096.864</v>
+        <v>12229.956</v>
       </c>
       <c r="F94">
-        <v>12244.464</v>
+        <v>12377.556</v>
       </c>
       <c r="G94">
         <v>948.5</v>
@@ -10072,37 +10072,37 @@
         <v>981.6</v>
       </c>
       <c r="M94">
-        <v>2458.6883712</v>
+        <v>2485.4132448</v>
       </c>
       <c r="N94">
-        <v>-1477.0883712</v>
+        <v>-1503.8132448</v>
       </c>
       <c r="O94">
-        <v>-324.9594416640001</v>
+        <v>-330.838913856</v>
       </c>
       <c r="P94">
-        <v>-1152.128929536</v>
+        <v>-1172.974330944</v>
       </c>
       <c r="Q94">
-        <v>-1108.428929536</v>
+        <v>-1129.274330944</v>
       </c>
       <c r="R94">
-        <v>11.50000000000001</v>
+        <v>13.2857142857143</v>
       </c>
       <c r="S94">
-        <v>0.617482431793722</v>
+        <v>0.6991513506213966</v>
       </c>
       <c r="T94">
-        <v>13.20282752410443</v>
+        <v>15.08894574183364</v>
       </c>
       <c r="U94">
         <v>0.2008</v>
       </c>
       <c r="V94">
-        <v>0.08783219643838042</v>
+        <v>0.08688776421861288</v>
       </c>
       <c r="W94">
-        <v>0.1831632949551732</v>
+        <v>0.1833529369449025</v>
       </c>
       <c r="X94" t="inlineStr">
         <is>
@@ -10110,7 +10110,7 @@
         </is>
       </c>
       <c r="Y94">
-        <v>0.3992372565380927</v>
+        <v>0.3949443828118767</v>
       </c>
       <c r="Z94">
         <v>0</v>
@@ -10118,22 +10118,22 @@
     </row>
     <row r="95">
       <c r="A95">
-        <v>0.93</v>
+        <v>0.9400000000000001</v>
       </c>
       <c r="B95">
-        <v>0.2194588259022571</v>
+        <v>0.2210088259022571</v>
       </c>
       <c r="C95">
-        <v>-7900.48506856912</v>
+        <v>-8064.792875852532</v>
       </c>
       <c r="D95">
-        <v>3528.57093143088</v>
+        <v>3497.355124147468</v>
       </c>
       <c r="E95">
-        <v>12229.956</v>
+        <v>12363.048</v>
       </c>
       <c r="F95">
-        <v>12377.556</v>
+        <v>12510.648</v>
       </c>
       <c r="G95">
         <v>948.5</v>
@@ -10154,37 +10154,37 @@
         <v>981.6</v>
       </c>
       <c r="M95">
-        <v>2485.4132448</v>
+        <v>2512.1381184</v>
       </c>
       <c r="N95">
-        <v>-1503.8132448</v>
+        <v>-1530.5381184</v>
       </c>
       <c r="O95">
-        <v>-330.838913856</v>
+        <v>-336.7183860480001</v>
       </c>
       <c r="P95">
-        <v>-1172.974330944</v>
+        <v>-1193.819732352</v>
       </c>
       <c r="Q95">
-        <v>-1129.274330944</v>
+        <v>-1150.119732352</v>
       </c>
       <c r="R95">
-        <v>13.2857142857143</v>
+        <v>15.66666666666668</v>
       </c>
       <c r="S95">
-        <v>0.6991513506213966</v>
+        <v>0.8080432423916294</v>
       </c>
       <c r="T95">
-        <v>15.08894574183364</v>
+        <v>17.60377003213924</v>
       </c>
       <c r="U95">
         <v>0.2008</v>
       </c>
       <c r="V95">
-        <v>0.08688776421861288</v>
+        <v>0.0859634263013936</v>
       </c>
       <c r="W95">
-        <v>0.1833529369449025</v>
+        <v>0.1835385439986802</v>
       </c>
       <c r="X95" t="inlineStr">
         <is>
@@ -10192,7 +10192,7 @@
         </is>
       </c>
       <c r="Y95">
-        <v>0.3949443828118767</v>
+        <v>0.3907428468245163</v>
       </c>
       <c r="Z95">
         <v>0</v>
@@ -10200,22 +10200,22 @@
     </row>
     <row r="96">
       <c r="A96">
-        <v>0.9400000000000001</v>
+        <v>0.9500000000000001</v>
       </c>
       <c r="B96">
-        <v>0.2210088259022571</v>
+        <v>0.2225588259022571</v>
       </c>
       <c r="C96">
-        <v>-8064.792875852532</v>
+        <v>-8228.553219652385</v>
       </c>
       <c r="D96">
-        <v>3497.355124147468</v>
+        <v>3466.686780347616</v>
       </c>
       <c r="E96">
-        <v>12363.048</v>
+        <v>12496.14</v>
       </c>
       <c r="F96">
-        <v>12510.648</v>
+        <v>12643.74</v>
       </c>
       <c r="G96">
         <v>948.5</v>
@@ -10236,37 +10236,37 @@
         <v>981.6</v>
       </c>
       <c r="M96">
-        <v>2512.1381184</v>
+        <v>2538.862992</v>
       </c>
       <c r="N96">
-        <v>-1530.5381184</v>
+        <v>-1557.262992</v>
       </c>
       <c r="O96">
-        <v>-336.7183860480001</v>
+        <v>-342.5978582400001</v>
       </c>
       <c r="P96">
-        <v>-1193.819732352</v>
+        <v>-1214.66513376</v>
       </c>
       <c r="Q96">
-        <v>-1150.119732352</v>
+        <v>-1170.96513376</v>
       </c>
       <c r="R96">
-        <v>15.66666666666668</v>
+        <v>19.00000000000003</v>
       </c>
       <c r="S96">
-        <v>0.8080432423916294</v>
+        <v>0.9604918908699558</v>
       </c>
       <c r="T96">
-        <v>17.60377003213924</v>
+        <v>21.12452403856711</v>
       </c>
       <c r="U96">
         <v>0.2008</v>
       </c>
       <c r="V96">
-        <v>0.0859634263013936</v>
+        <v>0.08505854812979997</v>
       </c>
       <c r="W96">
-        <v>0.1835385439986802</v>
+        <v>0.1837202435355362</v>
       </c>
       <c r="X96" t="inlineStr">
         <is>
@@ -10274,7 +10274,7 @@
         </is>
       </c>
       <c r="Y96">
-        <v>0.3907428468245163</v>
+        <v>0.3866297642263635</v>
       </c>
       <c r="Z96">
         <v>0</v>
@@ -10282,22 +10282,22 @@
     </row>
     <row r="97">
       <c r="A97">
-        <v>0.9500000000000001</v>
+        <v>0.9600000000000001</v>
       </c>
       <c r="B97">
-        <v>0.2225588259022571</v>
+        <v>0.2241088259022571</v>
       </c>
       <c r="C97">
-        <v>-8228.553219652385</v>
+        <v>-8391.780376913106</v>
       </c>
       <c r="D97">
-        <v>3466.686780347616</v>
+        <v>3436.551623086896</v>
       </c>
       <c r="E97">
-        <v>12496.14</v>
+        <v>12629.232</v>
       </c>
       <c r="F97">
-        <v>12643.74</v>
+        <v>12776.832</v>
       </c>
       <c r="G97">
         <v>948.5</v>
@@ -10318,37 +10318,37 @@
         <v>981.6</v>
       </c>
       <c r="M97">
-        <v>2538.862992</v>
+        <v>2565.5878656</v>
       </c>
       <c r="N97">
-        <v>-1557.262992</v>
+        <v>-1583.987865600001</v>
       </c>
       <c r="O97">
-        <v>-342.5978582400001</v>
+        <v>-348.4773304320001</v>
       </c>
       <c r="P97">
-        <v>-1214.66513376</v>
+        <v>-1235.510535168</v>
       </c>
       <c r="Q97">
-        <v>-1170.96513376</v>
+        <v>-1191.810535168001</v>
       </c>
       <c r="R97">
-        <v>19.00000000000003</v>
+        <v>24.00000000000005</v>
       </c>
       <c r="S97">
-        <v>0.9604918908699558</v>
+        <v>1.189164863587445</v>
       </c>
       <c r="T97">
-        <v>21.12452403856711</v>
+        <v>26.40565504820889</v>
       </c>
       <c r="U97">
         <v>0.2008</v>
       </c>
       <c r="V97">
-        <v>0.08505854812979997</v>
+        <v>0.08417252158678122</v>
       </c>
       <c r="W97">
-        <v>0.1837202435355362</v>
+        <v>0.1838981576653743</v>
       </c>
       <c r="X97" t="inlineStr">
         <is>
@@ -10356,7 +10356,7 @@
         </is>
       </c>
       <c r="Y97">
-        <v>0.3866297642263635</v>
+        <v>0.3826023708490055</v>
       </c>
       <c r="Z97">
         <v>0</v>
@@ -10364,22 +10364,22 @@
     </row>
     <row r="98">
       <c r="A98">
-        <v>0.96</v>
+        <v>0.97</v>
       </c>
       <c r="B98">
-        <v>0.2241088259022571</v>
+        <v>0.2256588259022571</v>
       </c>
       <c r="C98">
-        <v>-8391.780376913104</v>
+        <v>-8554.48813243171</v>
       </c>
       <c r="D98">
-        <v>3436.551623086896</v>
+        <v>3406.93586756829</v>
       </c>
       <c r="E98">
-        <v>12629.232</v>
+        <v>12762.324</v>
       </c>
       <c r="F98">
-        <v>12776.832</v>
+        <v>12909.924</v>
       </c>
       <c r="G98">
         <v>948.5</v>
@@ -10400,37 +10400,37 @@
         <v>981.6</v>
       </c>
       <c r="M98">
-        <v>2565.5878656</v>
+        <v>2592.3127392</v>
       </c>
       <c r="N98">
-        <v>-1583.9878656</v>
+        <v>-1610.7127392</v>
       </c>
       <c r="O98">
-        <v>-348.477330432</v>
+        <v>-354.3568026240001</v>
       </c>
       <c r="P98">
-        <v>-1235.510535168</v>
+        <v>-1256.355936576</v>
       </c>
       <c r="Q98">
-        <v>-1191.810535168</v>
+        <v>-1212.655936576</v>
       </c>
       <c r="R98">
-        <v>23.99999999999998</v>
+        <v>32.33333333333331</v>
       </c>
       <c r="S98">
-        <v>1.189164863587442</v>
+        <v>1.570286484783256</v>
       </c>
       <c r="T98">
-        <v>26.40565504820882</v>
+        <v>35.20754006427843</v>
       </c>
       <c r="U98">
         <v>0.2008</v>
       </c>
       <c r="V98">
-        <v>0.08417252158678123</v>
+        <v>0.08330476363227833</v>
       </c>
       <c r="W98">
-        <v>0.1838981576653743</v>
+        <v>0.1840724034626385</v>
       </c>
       <c r="X98" t="inlineStr">
         <is>
@@ -10438,7 +10438,7 @@
         </is>
       </c>
       <c r="Y98">
-        <v>0.3826023708490056</v>
+        <v>0.378658016510356</v>
       </c>
       <c r="Z98">
         <v>0</v>
@@ -10446,22 +10446,22 @@
     </row>
     <row r="99">
       <c r="A99">
-        <v>0.97</v>
+        <v>0.98</v>
       </c>
       <c r="B99">
-        <v>0.2256588259022571</v>
+        <v>0.2272088259022571</v>
       </c>
       <c r="C99">
-        <v>-8554.48813243171</v>
+        <v>-8716.689799882928</v>
       </c>
       <c r="D99">
-        <v>3406.93586756829</v>
+        <v>3377.826200117071</v>
       </c>
       <c r="E99">
-        <v>12762.324</v>
+        <v>12895.416</v>
       </c>
       <c r="F99">
-        <v>12909.924</v>
+        <v>13043.016</v>
       </c>
       <c r="G99">
         <v>948.5</v>
@@ -10482,37 +10482,37 @@
         <v>981.6</v>
       </c>
       <c r="M99">
-        <v>2592.3127392</v>
+        <v>2619.0376128</v>
       </c>
       <c r="N99">
-        <v>-1610.7127392</v>
+        <v>-1637.4376128</v>
       </c>
       <c r="O99">
-        <v>-354.3568026240001</v>
+        <v>-360.236274816</v>
       </c>
       <c r="P99">
-        <v>-1256.355936576</v>
+        <v>-1277.201337984</v>
       </c>
       <c r="Q99">
-        <v>-1212.655936576</v>
+        <v>-1233.501337984</v>
       </c>
       <c r="R99">
-        <v>32.33333333333331</v>
+        <v>48.99999999999996</v>
       </c>
       <c r="S99">
-        <v>1.570286484783256</v>
+        <v>2.332529727174884</v>
       </c>
       <c r="T99">
-        <v>35.20754006427843</v>
+        <v>52.81131009641764</v>
       </c>
       <c r="U99">
         <v>0.2008</v>
       </c>
       <c r="V99">
-        <v>0.08330476363227833</v>
+        <v>0.08245471502378572</v>
       </c>
       <c r="W99">
-        <v>0.1840724034626385</v>
+        <v>0.1842430932232238</v>
       </c>
       <c r="X99" t="inlineStr">
         <is>
@@ -10520,7 +10520,7 @@
         </is>
       </c>
       <c r="Y99">
-        <v>0.378658016510356</v>
+        <v>0.3747941591990259</v>
       </c>
       <c r="Z99">
         <v>0</v>
@@ -10528,22 +10528,22 @@
     </row>
     <row r="100">
       <c r="A100">
-        <v>0.98</v>
+        <v>0.99</v>
       </c>
       <c r="B100">
-        <v>0.2272088259022571</v>
+        <v>0.2287588259022571</v>
       </c>
       <c r="C100">
-        <v>-8716.689799882928</v>
+        <v>-8878.398241775591</v>
       </c>
       <c r="D100">
-        <v>3377.826200117071</v>
+        <v>3349.20975822441</v>
       </c>
       <c r="E100">
-        <v>12895.416</v>
+        <v>13028.508</v>
       </c>
       <c r="F100">
-        <v>13043.016</v>
+        <v>13176.108</v>
       </c>
       <c r="G100">
         <v>948.5</v>
@@ -10564,37 +10564,37 @@
         <v>981.6</v>
       </c>
       <c r="M100">
-        <v>2619.0376128</v>
+        <v>2645.7624864</v>
       </c>
       <c r="N100">
-        <v>-1637.4376128</v>
+        <v>-1664.1624864</v>
       </c>
       <c r="O100">
-        <v>-360.236274816</v>
+        <v>-366.115747008</v>
       </c>
       <c r="P100">
-        <v>-1277.201337984</v>
+        <v>-1298.046739392</v>
       </c>
       <c r="Q100">
-        <v>-1233.501337984</v>
+        <v>-1254.346739392</v>
       </c>
       <c r="R100">
-        <v>48.99999999999996</v>
+        <v>98.99999999999991</v>
       </c>
       <c r="S100">
-        <v>2.332529727174884</v>
+        <v>4.619259454349768</v>
       </c>
       <c r="T100">
-        <v>52.81131009641764</v>
+        <v>105.6226201928353</v>
       </c>
       <c r="U100">
         <v>0.2008</v>
       </c>
       <c r="V100">
-        <v>0.08245471502378572</v>
+        <v>0.08162183911445453</v>
       </c>
       <c r="W100">
-        <v>0.1842430932232238</v>
+        <v>0.1844103347058175</v>
       </c>
       <c r="X100" t="inlineStr">
         <is>
@@ -10602,91 +10602,9 @@
         </is>
       </c>
       <c r="Y100">
-        <v>0.3747941591990259</v>
+        <v>0.371008359611157</v>
       </c>
       <c r="Z100">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101">
-        <v>0.99</v>
-      </c>
-      <c r="B101">
-        <v>0.2287588259022571</v>
-      </c>
-      <c r="C101">
-        <v>-8878.398241775591</v>
-      </c>
-      <c r="D101">
-        <v>3349.20975822441</v>
-      </c>
-      <c r="E101">
-        <v>13028.508</v>
-      </c>
-      <c r="F101">
-        <v>13176.108</v>
-      </c>
-      <c r="G101">
-        <v>948.5</v>
-      </c>
-      <c r="H101">
-        <v>13161.6</v>
-      </c>
-      <c r="I101">
-        <v>0</v>
-      </c>
-      <c r="J101">
-        <v>1025.3</v>
-      </c>
-      <c r="K101">
-        <v>43.69999999999993</v>
-      </c>
-      <c r="L101">
-        <v>981.6</v>
-      </c>
-      <c r="M101">
-        <v>2645.7624864</v>
-      </c>
-      <c r="N101">
-        <v>-1664.1624864</v>
-      </c>
-      <c r="O101">
-        <v>-366.115747008</v>
-      </c>
-      <c r="P101">
-        <v>-1298.046739392</v>
-      </c>
-      <c r="Q101">
-        <v>-1254.346739392</v>
-      </c>
-      <c r="R101">
-        <v>98.99999999999991</v>
-      </c>
-      <c r="S101">
-        <v>4.619259454349768</v>
-      </c>
-      <c r="T101">
-        <v>105.6226201928353</v>
-      </c>
-      <c r="U101">
-        <v>0.2008</v>
-      </c>
-      <c r="V101">
-        <v>0.08162183911445453</v>
-      </c>
-      <c r="W101">
-        <v>0.1844103347058175</v>
-      </c>
-      <c r="X101" t="inlineStr">
-        <is>
-          <t>C2/C</t>
-        </is>
-      </c>
-      <c r="Y101">
-        <v>0.371008359611157</v>
-      </c>
-      <c r="Z101">
         <v>0</v>
       </c>
     </row>
